--- a/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
+++ b/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\GranSuelo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0799EE-68FA-48AB-8B5F-593C60B3E1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A50C744-50D6-4346-A072-05BFD129E348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2760" yWindow="1320" windowWidth="20280" windowHeight="10920" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="99" r:id="rId1"/>
@@ -7948,23 +7948,144 @@
     <xf numFmtId="179" fontId="4" fillId="3" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="189" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7985,15 +8106,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -8006,116 +8118,31 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="189" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8127,23 +8154,185 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -8162,195 +8351,6 @@
     <xf numFmtId="167" fontId="17" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="162" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="183" fontId="4" fillId="3" borderId="77" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8456,26 +8456,19 @@
     <xf numFmtId="0" fontId="56" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8528,19 +8521,77 @@
     <xf numFmtId="172" fontId="54" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="73" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="73" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="99" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="81" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="75" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="76" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="77" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="77" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8598,57 +8649,6 @@
     </xf>
     <xf numFmtId="0" fontId="48" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="73" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="73" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="99" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="81" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="75" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="19" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="76" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="77" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="5" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="77" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="68" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -14103,8 +14103,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="720091" y="7441861"/>
-          <a:ext cx="5615156" cy="241150"/>
+          <a:off x="720091" y="7502821"/>
+          <a:ext cx="5780891" cy="252580"/>
           <a:chOff x="720091" y="7392875"/>
           <a:chExt cx="5647813" cy="243872"/>
         </a:xfrm>
@@ -16382,7 +16382,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16441,7 +16441,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -16560,7 +16560,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16611,7 +16611,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -16663,7 +16663,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -16695,7 +16695,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -21495,26 +21495,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E05DD21-D8C3-4D15-A974-96B5B103E5AF}">
   <dimension ref="A1:U67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="673" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="673" customWidth="1"/>
     <col min="2" max="2" width="2" style="673" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="673" customWidth="1"/>
-    <col min="4" max="4" width="1.140625" style="673" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="673" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="673" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="673" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="673" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="673" customWidth="1"/>
+    <col min="4" max="4" width="1.109375" style="673" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="673" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="673" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="673" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" style="673" customWidth="1"/>
     <col min="9" max="9" width="1" style="673" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" style="673" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="673" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="673" customWidth="1"/>
+    <col min="10" max="10" width="21.109375" style="673" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="673" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" style="673" customWidth="1"/>
     <col min="13" max="13" width="8" style="673" customWidth="1"/>
-    <col min="14" max="15" width="10.7109375" style="673" customWidth="1"/>
-    <col min="16" max="16384" width="10.28515625" style="673"/>
+    <col min="14" max="15" width="10.6640625" style="673" customWidth="1"/>
+    <col min="16" max="16384" width="10.33203125" style="673"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="668"/>
       <c r="B1" s="669"/>
       <c r="C1" s="669"/>
@@ -21527,7 +21527,7 @@
       <c r="J1" s="671"/>
       <c r="K1" s="672"/>
     </row>
-    <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="674"/>
       <c r="B2" s="285"/>
       <c r="C2" s="285"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="O2" s="757"/>
     </row>
-    <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="674"/>
       <c r="B3" s="285"/>
       <c r="C3" s="285"/>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="O3" s="758"/>
     </row>
-    <row r="4" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="674"/>
       <c r="B4" s="285"/>
       <c r="C4" s="285"/>
@@ -21572,7 +21572,7 @@
       </c>
       <c r="O4" s="758"/>
     </row>
-    <row r="5" spans="1:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="676"/>
       <c r="B5" s="677"/>
       <c r="C5" s="677"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="O5" s="758"/>
     </row>
-    <row r="6" spans="1:21" ht="8.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="8.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="564"/>
       <c r="B6" s="564"/>
       <c r="C6" s="564"/>
@@ -21605,45 +21605,45 @@
       <c r="N6" s="759"/>
       <c r="O6" s="760"/>
     </row>
-    <row r="7" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="814" t="s">
+    <row r="7" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="782" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="814"/>
-      <c r="C7" s="814"/>
-      <c r="D7" s="814"/>
-      <c r="E7" s="814"/>
-      <c r="F7" s="814"/>
-      <c r="G7" s="814"/>
-      <c r="H7" s="814"/>
-      <c r="I7" s="814"/>
-      <c r="J7" s="814"/>
-      <c r="K7" s="814"/>
+      <c r="B7" s="782"/>
+      <c r="C7" s="782"/>
+      <c r="D7" s="782"/>
+      <c r="E7" s="782"/>
+      <c r="F7" s="782"/>
+      <c r="G7" s="782"/>
+      <c r="H7" s="782"/>
+      <c r="I7" s="782"/>
+      <c r="J7" s="782"/>
+      <c r="K7" s="782"/>
       <c r="N7" s="291" t="s">
         <v>447</v>
       </c>
       <c r="O7" s="760"/>
     </row>
-    <row r="8" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="815" t="s">
+    <row r="8" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="783" t="s">
         <v>477</v>
       </c>
-      <c r="B8" s="815"/>
-      <c r="C8" s="815"/>
-      <c r="D8" s="815"/>
-      <c r="E8" s="815"/>
-      <c r="F8" s="815"/>
-      <c r="G8" s="815"/>
-      <c r="H8" s="815"/>
-      <c r="I8" s="815"/>
-      <c r="J8" s="815"/>
-      <c r="K8" s="815"/>
+      <c r="B8" s="783"/>
+      <c r="C8" s="783"/>
+      <c r="D8" s="783"/>
+      <c r="E8" s="783"/>
+      <c r="F8" s="783"/>
+      <c r="G8" s="783"/>
+      <c r="H8" s="783"/>
+      <c r="I8" s="783"/>
+      <c r="J8" s="783"/>
+      <c r="K8" s="783"/>
       <c r="N8" s="291" t="s">
         <v>550</v>
       </c>
       <c r="O8" s="761"/>
     </row>
-    <row r="9" spans="1:21" ht="9.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="9.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="534"/>
       <c r="B9" s="534"/>
       <c r="C9" s="534"/>
@@ -21660,21 +21660,21 @@
       </c>
       <c r="O9" s="760"/>
     </row>
-    <row r="10" spans="1:21" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="485"/>
       <c r="C10" s="485"/>
-      <c r="D10" s="816" t="s">
+      <c r="D10" s="784" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="817"/>
-      <c r="F10" s="816" t="s">
+      <c r="E10" s="785"/>
+      <c r="F10" s="784" t="s">
         <v>479</v>
       </c>
-      <c r="G10" s="817"/>
-      <c r="H10" s="816" t="s">
+      <c r="G10" s="785"/>
+      <c r="H10" s="784" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="817"/>
+      <c r="I10" s="785"/>
       <c r="J10" s="679" t="s">
         <v>467</v>
       </c>
@@ -21684,16 +21684,16 @@
       <c r="N10" s="759"/>
       <c r="O10" s="760"/>
     </row>
-    <row r="11" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="485"/>
       <c r="B11" s="485"/>
       <c r="C11" s="485"/>
-      <c r="D11" s="779"/>
-      <c r="E11" s="780"/>
-      <c r="F11" s="779"/>
-      <c r="G11" s="780"/>
-      <c r="H11" s="779"/>
-      <c r="I11" s="780"/>
+      <c r="D11" s="786"/>
+      <c r="E11" s="787"/>
+      <c r="F11" s="786"/>
+      <c r="G11" s="787"/>
+      <c r="H11" s="786"/>
+      <c r="I11" s="787"/>
       <c r="J11" s="682"/>
       <c r="K11" s="386"/>
       <c r="L11" s="681"/>
@@ -21703,7 +21703,7 @@
       </c>
       <c r="O11" s="760"/>
     </row>
-    <row r="12" spans="1:21" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="485"/>
       <c r="B12" s="288"/>
       <c r="C12" s="292"/>
@@ -21722,20 +21722,20 @@
       </c>
       <c r="O12" s="761"/>
     </row>
-    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="818" t="s">
+    <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="788" t="s">
         <v>480</v>
       </c>
-      <c r="B13" s="819"/>
-      <c r="C13" s="819"/>
-      <c r="D13" s="819"/>
-      <c r="E13" s="819"/>
-      <c r="F13" s="819"/>
-      <c r="G13" s="819"/>
-      <c r="H13" s="819"/>
-      <c r="I13" s="819"/>
-      <c r="J13" s="819"/>
-      <c r="K13" s="820"/>
+      <c r="B13" s="789"/>
+      <c r="C13" s="789"/>
+      <c r="D13" s="789"/>
+      <c r="E13" s="789"/>
+      <c r="F13" s="789"/>
+      <c r="G13" s="789"/>
+      <c r="H13" s="789"/>
+      <c r="I13" s="789"/>
+      <c r="J13" s="789"/>
+      <c r="K13" s="790"/>
       <c r="L13" s="681"/>
       <c r="M13" s="681"/>
       <c r="N13" s="291" t="s">
@@ -21743,26 +21743,26 @@
       </c>
       <c r="O13" s="761"/>
     </row>
-    <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="821" t="s">
+    <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="791" t="s">
         <v>481</v>
       </c>
-      <c r="B14" s="822"/>
-      <c r="C14" s="822"/>
-      <c r="D14" s="822"/>
-      <c r="E14" s="822"/>
-      <c r="F14" s="822"/>
-      <c r="G14" s="822"/>
-      <c r="H14" s="822"/>
-      <c r="I14" s="822"/>
-      <c r="J14" s="822"/>
-      <c r="K14" s="823"/>
+      <c r="B14" s="792"/>
+      <c r="C14" s="792"/>
+      <c r="D14" s="792"/>
+      <c r="E14" s="792"/>
+      <c r="F14" s="792"/>
+      <c r="G14" s="792"/>
+      <c r="H14" s="792"/>
+      <c r="I14" s="792"/>
+      <c r="J14" s="792"/>
+      <c r="K14" s="793"/>
       <c r="L14" s="681"/>
       <c r="M14" s="681"/>
       <c r="N14" s="759"/>
       <c r="O14" s="760"/>
     </row>
-    <row r="15" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M15" s="684"/>
       <c r="N15" s="291" t="s">
         <v>551</v>
@@ -21775,22 +21775,22 @@
       <c r="T15" s="684"/>
       <c r="U15" s="684"/>
     </row>
-    <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="804" t="s">
+    <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="794" t="s">
         <v>482</v>
       </c>
-      <c r="B16" s="805"/>
-      <c r="C16" s="806"/>
-      <c r="E16" s="824" t="s">
+      <c r="B16" s="795"/>
+      <c r="C16" s="796"/>
+      <c r="E16" s="797" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="825"/>
-      <c r="G16" s="825"/>
-      <c r="H16" s="826"/>
-      <c r="J16" s="804" t="s">
+      <c r="F16" s="798"/>
+      <c r="G16" s="798"/>
+      <c r="H16" s="799"/>
+      <c r="J16" s="794" t="s">
         <v>483</v>
       </c>
-      <c r="K16" s="806"/>
+      <c r="K16" s="796"/>
       <c r="M16" s="684"/>
       <c r="N16" s="291" t="s">
         <v>245</v>
@@ -21802,20 +21802,20 @@
       <c r="T16" s="686"/>
       <c r="U16" s="686"/>
     </row>
-    <row r="17" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="687" t="s">
         <v>484</v>
       </c>
-      <c r="B17" s="799"/>
-      <c r="C17" s="800"/>
+      <c r="B17" s="778"/>
+      <c r="C17" s="779"/>
       <c r="E17" s="688" t="s">
         <v>485</v>
       </c>
       <c r="F17" s="689"/>
       <c r="G17" s="690"/>
       <c r="H17" s="691"/>
-      <c r="J17" s="812"/>
-      <c r="K17" s="813"/>
+      <c r="J17" s="780"/>
+      <c r="K17" s="781"/>
       <c r="M17" s="684"/>
       <c r="N17" s="291" t="s">
         <v>552</v>
@@ -21827,12 +21827,12 @@
       <c r="T17" s="686"/>
       <c r="U17" s="686"/>
     </row>
-    <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="687" t="s">
         <v>486</v>
       </c>
-      <c r="B18" s="799"/>
-      <c r="C18" s="800"/>
+      <c r="B18" s="778"/>
+      <c r="C18" s="779"/>
       <c r="E18" s="688" t="s">
         <v>487</v>
       </c>
@@ -21848,17 +21848,17 @@
       <c r="T18" s="686"/>
       <c r="U18" s="686"/>
     </row>
-    <row r="19" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E19" s="688" t="s">
         <v>488</v>
       </c>
       <c r="F19" s="689"/>
       <c r="G19" s="690"/>
       <c r="H19" s="694"/>
-      <c r="J19" s="782" t="s">
+      <c r="J19" s="804" t="s">
         <v>489</v>
       </c>
-      <c r="K19" s="783"/>
+      <c r="K19" s="805"/>
       <c r="M19" s="684"/>
       <c r="N19" s="692"/>
       <c r="O19" s="685"/>
@@ -21868,12 +21868,12 @@
       <c r="T19" s="686"/>
       <c r="U19" s="686"/>
     </row>
-    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="789" t="s">
+    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="806" t="s">
         <v>490</v>
       </c>
-      <c r="B20" s="790"/>
-      <c r="C20" s="791"/>
+      <c r="B20" s="807"/>
+      <c r="C20" s="808"/>
       <c r="E20" s="695" t="s">
         <v>491</v>
       </c>
@@ -21893,12 +21893,12 @@
       <c r="T20" s="686"/>
       <c r="U20" s="686"/>
     </row>
-    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="687" t="s">
         <v>492</v>
       </c>
-      <c r="B21" s="801"/>
-      <c r="C21" s="802"/>
+      <c r="B21" s="809"/>
+      <c r="C21" s="810"/>
       <c r="E21" s="700"/>
       <c r="F21" s="700"/>
       <c r="G21" s="700"/>
@@ -21915,18 +21915,18 @@
       <c r="T21" s="686"/>
       <c r="U21" s="686"/>
     </row>
-    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="687" t="s">
         <v>494</v>
       </c>
-      <c r="B22" s="801"/>
-      <c r="C22" s="802"/>
-      <c r="E22" s="782" t="s">
+      <c r="B22" s="809"/>
+      <c r="C22" s="810"/>
+      <c r="E22" s="804" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="803"/>
-      <c r="G22" s="803"/>
-      <c r="H22" s="783"/>
+      <c r="F22" s="811"/>
+      <c r="G22" s="811"/>
+      <c r="H22" s="805"/>
       <c r="I22" s="701"/>
       <c r="J22" s="486" t="s">
         <v>370</v>
@@ -21941,7 +21941,7 @@
       <c r="T22" s="686"/>
       <c r="U22" s="686"/>
     </row>
-    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E23" s="688" t="s">
         <v>495</v>
       </c>
@@ -21961,12 +21961,12 @@
       <c r="T23" s="686"/>
       <c r="U23" s="686"/>
     </row>
-    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="804" t="s">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="794" t="s">
         <v>497</v>
       </c>
-      <c r="B24" s="805"/>
-      <c r="C24" s="806"/>
+      <c r="B24" s="795"/>
+      <c r="C24" s="796"/>
       <c r="E24" s="688" t="s">
         <v>498</v>
       </c>
@@ -21986,7 +21986,7 @@
       <c r="T24" s="686"/>
       <c r="U24" s="686"/>
     </row>
-    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="705" t="s">
         <v>500</v>
       </c>
@@ -22011,7 +22011,7 @@
       <c r="T25" s="686"/>
       <c r="U25" s="686"/>
     </row>
-    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="705" t="s">
         <v>502</v>
       </c>
@@ -22036,7 +22036,7 @@
       <c r="T26" s="686"/>
       <c r="U26" s="686"/>
     </row>
-    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="705" t="s">
         <v>505</v>
       </c>
@@ -22056,7 +22056,7 @@
       <c r="T27" s="686"/>
       <c r="U27" s="686"/>
     </row>
-    <row r="28" spans="1:21" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="684"/>
       <c r="B28" s="686"/>
       <c r="C28" s="710"/>
@@ -22071,7 +22071,7 @@
       <c r="T28" s="686"/>
       <c r="U28" s="686"/>
     </row>
-    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="712" t="s">
         <v>507</v>
       </c>
@@ -22090,7 +22090,7 @@
       <c r="T29" s="686"/>
       <c r="U29" s="686"/>
     </row>
-    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="713" t="s">
         <v>508</v>
       </c>
@@ -22114,12 +22114,12 @@
       <c r="T30" s="686"/>
       <c r="U30" s="686"/>
     </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="705" t="s">
         <v>510</v>
       </c>
-      <c r="B31" s="807"/>
-      <c r="C31" s="807"/>
+      <c r="B31" s="812"/>
+      <c r="C31" s="812"/>
       <c r="E31" s="688" t="s">
         <v>511</v>
       </c>
@@ -22138,12 +22138,12 @@
       <c r="T31" s="686"/>
       <c r="U31" s="686"/>
     </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="705" t="s">
         <v>512</v>
       </c>
-      <c r="B32" s="807"/>
-      <c r="C32" s="807"/>
+      <c r="B32" s="812"/>
+      <c r="C32" s="812"/>
       <c r="E32" s="688" t="s">
         <v>513</v>
       </c>
@@ -22162,7 +22162,7 @@
       <c r="T32" s="686"/>
       <c r="U32" s="686"/>
     </row>
-    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E33" s="688" t="s">
         <v>514</v>
       </c>
@@ -22181,18 +22181,18 @@
       <c r="T33" s="686"/>
       <c r="U33" s="686"/>
     </row>
-    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="789" t="s">
+    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="806" t="s">
         <v>515</v>
       </c>
-      <c r="B34" s="790"/>
-      <c r="C34" s="791"/>
-      <c r="E34" s="808" t="s">
+      <c r="B34" s="807"/>
+      <c r="C34" s="808"/>
+      <c r="E34" s="813" t="s">
         <v>516</v>
       </c>
-      <c r="F34" s="809"/>
-      <c r="G34" s="795"/>
-      <c r="H34" s="796"/>
+      <c r="F34" s="814"/>
+      <c r="G34" s="800"/>
+      <c r="H34" s="801"/>
       <c r="I34" s="717"/>
       <c r="J34" s="718" t="s">
         <v>517</v>
@@ -22206,16 +22206,16 @@
       <c r="T34" s="686"/>
       <c r="U34" s="686"/>
     </row>
-    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="720" t="s">
         <v>518</v>
       </c>
       <c r="B35" s="700"/>
       <c r="C35" s="721"/>
-      <c r="E35" s="810"/>
-      <c r="F35" s="811"/>
-      <c r="G35" s="797"/>
-      <c r="H35" s="798"/>
+      <c r="E35" s="815"/>
+      <c r="F35" s="816"/>
+      <c r="G35" s="802"/>
+      <c r="H35" s="803"/>
       <c r="J35" s="722" t="s">
         <v>519</v>
       </c>
@@ -22228,7 +22228,7 @@
       <c r="T35" s="686"/>
       <c r="U35" s="686"/>
     </row>
-    <row r="36" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="724"/>
       <c r="B36" s="696"/>
       <c r="C36" s="725"/>
@@ -22238,25 +22238,25 @@
       <c r="L36" s="681"/>
       <c r="P36" s="684"/>
     </row>
-    <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="789" t="s">
+    <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="806" t="s">
         <v>520</v>
       </c>
-      <c r="B37" s="790"/>
-      <c r="C37" s="791"/>
-      <c r="E37" s="792" t="s">
+      <c r="B37" s="807"/>
+      <c r="C37" s="808"/>
+      <c r="E37" s="824" t="s">
         <v>521</v>
       </c>
-      <c r="F37" s="793"/>
-      <c r="G37" s="793"/>
-      <c r="H37" s="793"/>
-      <c r="I37" s="794"/>
-      <c r="K37" s="778" t="s">
+      <c r="F37" s="825"/>
+      <c r="G37" s="825"/>
+      <c r="H37" s="825"/>
+      <c r="I37" s="826"/>
+      <c r="K37" s="817" t="s">
         <v>522</v>
       </c>
       <c r="L37" s="681"/>
     </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="728" t="s">
         <v>518</v>
       </c>
@@ -22264,18 +22264,18 @@
       <c r="E38" s="730" t="s">
         <v>548</v>
       </c>
-      <c r="F38" s="779" t="s">
+      <c r="F38" s="786" t="s">
         <v>523</v>
       </c>
-      <c r="G38" s="780"/>
-      <c r="H38" s="779" t="s">
+      <c r="G38" s="787"/>
+      <c r="H38" s="786" t="s">
         <v>524</v>
       </c>
-      <c r="I38" s="780"/>
-      <c r="K38" s="778"/>
+      <c r="I38" s="787"/>
+      <c r="K38" s="817"/>
       <c r="L38" s="681"/>
     </row>
-    <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="724"/>
       <c r="B39" s="696"/>
       <c r="C39" s="725"/>
@@ -22284,37 +22284,37 @@
       <c r="K39" s="731"/>
       <c r="L39" s="681"/>
     </row>
-    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="732" t="s">
         <v>525</v>
       </c>
       <c r="C40" s="733" t="s">
         <v>526</v>
       </c>
-      <c r="D40" s="782" t="s">
+      <c r="D40" s="804" t="s">
         <v>527</v>
       </c>
-      <c r="E40" s="783"/>
+      <c r="E40" s="805"/>
       <c r="I40" s="734" t="s">
         <v>528</v>
       </c>
       <c r="L40" s="681"/>
     </row>
-    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="732" t="s">
         <v>529</v>
       </c>
       <c r="C41" s="733" t="s">
         <v>530</v>
       </c>
-      <c r="D41" s="782" t="s">
+      <c r="D41" s="804" t="s">
         <v>366</v>
       </c>
-      <c r="E41" s="783"/>
+      <c r="E41" s="805"/>
       <c r="J41" s="735"/>
       <c r="L41" s="681"/>
     </row>
-    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="736" t="s">
         <v>531</v>
       </c>
@@ -22330,7 +22330,7 @@
       <c r="K42" s="740"/>
       <c r="L42" s="681"/>
     </row>
-    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="736" t="s">
         <v>532</v>
       </c>
@@ -22340,7 +22340,7 @@
       <c r="D43" s="738"/>
       <c r="E43" s="739"/>
     </row>
-    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="736" t="s">
         <v>533</v>
       </c>
@@ -22350,7 +22350,7 @@
       <c r="D44" s="738"/>
       <c r="E44" s="739"/>
     </row>
-    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="736" t="s">
         <v>534</v>
       </c>
@@ -22362,7 +22362,7 @@
       <c r="L45" s="681"/>
       <c r="M45" s="681"/>
     </row>
-    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="736" t="s">
         <v>535</v>
       </c>
@@ -22374,7 +22374,7 @@
       <c r="L46" s="681"/>
       <c r="M46" s="681"/>
     </row>
-    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="736" t="s">
         <v>536</v>
       </c>
@@ -22385,7 +22385,7 @@
       <c r="E47" s="739"/>
       <c r="L47" s="681"/>
     </row>
-    <row r="48" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="736" t="s">
         <v>431</v>
       </c>
@@ -22397,7 +22397,7 @@
       <c r="L48" s="681"/>
       <c r="M48" s="681"/>
     </row>
-    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="266"/>
       <c r="C49" s="741"/>
       <c r="D49" s="742"/>
@@ -22408,7 +22408,7 @@
       <c r="L49" s="681"/>
       <c r="M49" s="681"/>
     </row>
-    <row r="50" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="388" t="s">
         <v>232</v>
       </c>
@@ -22417,18 +22417,18 @@
       </c>
       <c r="D50" s="738"/>
       <c r="E50" s="745"/>
-      <c r="G50" s="784" t="s">
+      <c r="G50" s="819" t="s">
         <v>538</v>
       </c>
-      <c r="H50" s="785"/>
-      <c r="I50" s="784" t="s">
+      <c r="H50" s="820"/>
+      <c r="I50" s="819" t="s">
         <v>539</v>
       </c>
-      <c r="J50" s="785"/>
+      <c r="J50" s="820"/>
       <c r="L50" s="681"/>
       <c r="M50" s="681"/>
     </row>
-    <row r="51" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="388" t="s">
         <v>238</v>
       </c>
@@ -22441,12 +22441,12 @@
         <v>540</v>
       </c>
       <c r="H51" s="747"/>
-      <c r="I51" s="786"/>
-      <c r="J51" s="787"/>
+      <c r="I51" s="821"/>
+      <c r="J51" s="822"/>
       <c r="L51" s="681"/>
       <c r="M51" s="681"/>
     </row>
-    <row r="52" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="388" t="s">
         <v>541</v>
       </c>
@@ -22459,12 +22459,12 @@
         <v>542</v>
       </c>
       <c r="H52" s="747"/>
-      <c r="I52" s="786"/>
-      <c r="J52" s="787"/>
+      <c r="I52" s="821"/>
+      <c r="J52" s="822"/>
       <c r="L52" s="681"/>
       <c r="M52" s="681"/>
     </row>
-    <row r="53" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="388" t="s">
         <v>239</v>
       </c>
@@ -22476,7 +22476,7 @@
       <c r="L53" s="681"/>
       <c r="M53" s="681"/>
     </row>
-    <row r="54" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="388" t="s">
         <v>241</v>
       </c>
@@ -22489,7 +22489,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="388" t="s">
         <v>240</v>
       </c>
@@ -22502,7 +22502,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="388" t="s">
         <v>242</v>
       </c>
@@ -22518,7 +22518,7 @@
       <c r="L56" s="681"/>
       <c r="M56" s="681"/>
     </row>
-    <row r="57" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="388" t="s">
         <v>544</v>
       </c>
@@ -22539,19 +22539,19 @@
       <c r="Q57" s="752"/>
       <c r="R57" s="752"/>
     </row>
-    <row r="58" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O58" s="753"/>
       <c r="P58" s="754"/>
       <c r="R58" s="749"/>
     </row>
-    <row r="59" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L59" s="681"/>
       <c r="M59" s="681"/>
       <c r="O59" s="753"/>
       <c r="P59" s="754"/>
       <c r="R59" s="755"/>
     </row>
-    <row r="60" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="756"/>
       <c r="B60" s="740"/>
       <c r="C60" s="740"/>
@@ -22566,7 +22566,7 @@
       <c r="L60" s="681"/>
       <c r="M60" s="681"/>
     </row>
-    <row r="61" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="260" t="s">
         <v>23</v>
       </c>
@@ -22583,24 +22583,24 @@
       <c r="L61" s="681"/>
       <c r="M61" s="681"/>
     </row>
-    <row r="62" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="425" t="s">
         <v>545</v>
       </c>
       <c r="B62" s="485"/>
       <c r="C62" s="485"/>
       <c r="D62" s="485"/>
-      <c r="E62" s="788"/>
-      <c r="F62" s="788"/>
-      <c r="G62" s="788"/>
-      <c r="H62" s="788"/>
-      <c r="I62" s="788"/>
-      <c r="J62" s="788"/>
+      <c r="E62" s="823"/>
+      <c r="F62" s="823"/>
+      <c r="G62" s="823"/>
+      <c r="H62" s="823"/>
+      <c r="I62" s="823"/>
+      <c r="J62" s="823"/>
       <c r="K62" s="740"/>
       <c r="L62" s="681"/>
       <c r="M62" s="681"/>
     </row>
-    <row r="63" spans="1:18" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" ht="1.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="740"/>
       <c r="C63" s="740"/>
       <c r="D63" s="740"/>
@@ -22614,30 +22614,30 @@
       <c r="L63" s="681"/>
       <c r="M63" s="681"/>
     </row>
-    <row r="64" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="260"/>
       <c r="F64" s="260" t="s">
         <v>546</v>
       </c>
       <c r="G64" s="260"/>
     </row>
-    <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="781" t="s">
+    <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="818" t="s">
         <v>547</v>
       </c>
-      <c r="B65" s="781"/>
-      <c r="C65" s="781"/>
-      <c r="D65" s="781"/>
-      <c r="E65" s="781"/>
-      <c r="F65" s="781"/>
-      <c r="G65" s="781"/>
-      <c r="H65" s="781"/>
-      <c r="I65" s="781"/>
-      <c r="J65" s="781"/>
-      <c r="K65" s="781"/>
-    </row>
-    <row r="66" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B65" s="818"/>
+      <c r="C65" s="818"/>
+      <c r="D65" s="818"/>
+      <c r="E65" s="818"/>
+      <c r="F65" s="818"/>
+      <c r="G65" s="818"/>
+      <c r="H65" s="818"/>
+      <c r="I65" s="818"/>
+      <c r="J65" s="818"/>
+      <c r="K65" s="818"/>
+    </row>
+    <row r="66" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="mqr63IQ4uQSmuncQM74KKqreM+dJvBPMH/ZdDqLebBarXv1cvTyz63VMrZPdfVOpcKJhhuXCDbf46NC8PIfxYQ==" saltValue="L8E06HI4mJ1F5rF2xz8KsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
@@ -22645,6 +22645,32 @@
     <protectedRange sqref="C10:C11 C62" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="41">
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="E37:I37"/>
+    <mergeCell ref="G34:H35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:F35"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="A7:K7"/>
@@ -22660,32 +22686,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G34:H35"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="E34:F35"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="E37:I37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -22701,38 +22701,38 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:AF94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="284" customWidth="1"/>
-    <col min="2" max="2" width="1.7109375" style="284" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" style="284" customWidth="1"/>
-    <col min="4" max="4" width="1.42578125" style="284" customWidth="1"/>
-    <col min="5" max="5" width="3.28515625" style="284" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="284" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="284" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" style="284" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="284" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="284" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" style="284" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="284" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="284" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" style="284" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="284" customWidth="1"/>
+    <col min="4" max="4" width="1.44140625" style="284" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" style="284" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" style="284" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="284" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" style="284" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="284" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="284" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="284" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="284" customWidth="1"/>
     <col min="13" max="13" width="1" style="284" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="284" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" style="284" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" style="284" customWidth="1"/>
+    <col min="15" max="15" width="6.44140625" style="284" customWidth="1"/>
     <col min="16" max="16" width="8" style="284" customWidth="1"/>
-    <col min="17" max="19" width="14.7109375" style="284" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="284" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="284" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="284" customWidth="1"/>
-    <col min="24" max="24" width="17.7109375" style="284" customWidth="1"/>
+    <col min="17" max="19" width="14.6640625" style="284" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" style="284" customWidth="1"/>
+    <col min="21" max="22" width="14.6640625" style="284" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" style="284" customWidth="1"/>
+    <col min="24" max="24" width="17.6640625" style="284" customWidth="1"/>
     <col min="25" max="25" width="19" style="284" customWidth="1"/>
-    <col min="26" max="27" width="11.42578125" style="284" customWidth="1"/>
-    <col min="28" max="29" width="10.7109375" style="284" customWidth="1"/>
-    <col min="30" max="30" width="12.42578125" style="284" customWidth="1"/>
-    <col min="31" max="32" width="10.7109375" style="284" customWidth="1"/>
-    <col min="33" max="16384" width="10.28515625" style="284"/>
+    <col min="26" max="27" width="11.44140625" style="284" customWidth="1"/>
+    <col min="28" max="29" width="10.6640625" style="284" customWidth="1"/>
+    <col min="30" max="30" width="12.44140625" style="284" customWidth="1"/>
+    <col min="31" max="32" width="10.6640625" style="284" customWidth="1"/>
+    <col min="33" max="16384" width="10.33203125" style="284"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="285"/>
       <c r="B1" s="285"/>
       <c r="C1" s="285"/>
@@ -22758,7 +22758,7 @@
       <c r="Y1" s="473"/>
       <c r="Z1" s="473"/>
     </row>
-    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="285"/>
       <c r="B2" s="285"/>
       <c r="C2" s="285"/>
@@ -22783,7 +22783,7 @@
       <c r="T2" s="279"/>
       <c r="U2" s="279"/>
     </row>
-    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="285"/>
       <c r="B3" s="285"/>
       <c r="C3" s="285"/>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="2.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="285"/>
       <c r="B4" s="285"/>
       <c r="C4" s="285"/>
@@ -22835,7 +22835,7 @@
       <c r="T4" s="279"/>
       <c r="U4" s="279"/>
     </row>
-    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="564"/>
       <c r="B5" s="564"/>
       <c r="C5" s="564"/>
@@ -22850,14 +22850,14 @@
       <c r="L5" s="564"/>
       <c r="M5" s="564"/>
       <c r="N5" s="564"/>
-      <c r="Q5" s="844" t="s">
+      <c r="Q5" s="872" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="845"/>
-      <c r="S5" s="845"/>
-      <c r="T5" s="845"/>
-      <c r="U5" s="845"/>
-      <c r="V5" s="846"/>
+      <c r="R5" s="873"/>
+      <c r="S5" s="873"/>
+      <c r="T5" s="873"/>
+      <c r="U5" s="873"/>
+      <c r="V5" s="874"/>
       <c r="X5" s="474" t="s">
         <v>370</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="564"/>
       <c r="B6" s="564"/>
       <c r="C6" s="564"/>
@@ -22917,23 +22917,23 @@
         <v>366</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="814" t="s">
+    <row r="7" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="782" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="814"/>
-      <c r="C7" s="814"/>
-      <c r="D7" s="814"/>
-      <c r="E7" s="814"/>
-      <c r="F7" s="814"/>
-      <c r="G7" s="814"/>
-      <c r="H7" s="814"/>
-      <c r="I7" s="814"/>
-      <c r="J7" s="814"/>
-      <c r="K7" s="814"/>
-      <c r="L7" s="814"/>
-      <c r="M7" s="814"/>
-      <c r="N7" s="814"/>
+      <c r="B7" s="782"/>
+      <c r="C7" s="782"/>
+      <c r="D7" s="782"/>
+      <c r="E7" s="782"/>
+      <c r="F7" s="782"/>
+      <c r="G7" s="782"/>
+      <c r="H7" s="782"/>
+      <c r="I7" s="782"/>
+      <c r="J7" s="782"/>
+      <c r="K7" s="782"/>
+      <c r="L7" s="782"/>
+      <c r="M7" s="782"/>
+      <c r="N7" s="782"/>
       <c r="Q7" s="478" t="s">
         <v>422</v>
       </c>
@@ -22971,23 +22971,23 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="856">
+    <row r="8" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="884">
         <v>0</v>
       </c>
-      <c r="B8" s="856"/>
-      <c r="C8" s="856"/>
-      <c r="D8" s="856"/>
-      <c r="E8" s="856"/>
-      <c r="F8" s="856"/>
-      <c r="G8" s="856"/>
-      <c r="H8" s="856"/>
-      <c r="I8" s="856"/>
-      <c r="J8" s="856"/>
-      <c r="K8" s="856"/>
-      <c r="L8" s="856"/>
-      <c r="M8" s="856"/>
-      <c r="N8" s="856"/>
+      <c r="B8" s="884"/>
+      <c r="C8" s="884"/>
+      <c r="D8" s="884"/>
+      <c r="E8" s="884"/>
+      <c r="F8" s="884"/>
+      <c r="G8" s="884"/>
+      <c r="H8" s="884"/>
+      <c r="I8" s="884"/>
+      <c r="J8" s="884"/>
+      <c r="K8" s="884"/>
+      <c r="L8" s="884"/>
+      <c r="M8" s="884"/>
+      <c r="N8" s="884"/>
       <c r="Q8" s="478" t="s">
         <v>423</v>
       </c>
@@ -23025,25 +23025,25 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="480" t="s">
         <v>464</v>
       </c>
       <c r="B9" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="858">
+      <c r="C9" s="886">
         <f>+FORMATO!O2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="858"/>
-      <c r="E9" s="858"/>
-      <c r="F9" s="858"/>
-      <c r="G9" s="858"/>
-      <c r="H9" s="858"/>
-      <c r="I9" s="858"/>
-      <c r="J9" s="858"/>
-      <c r="K9" s="858"/>
+      <c r="D9" s="886"/>
+      <c r="E9" s="886"/>
+      <c r="F9" s="886"/>
+      <c r="G9" s="886"/>
+      <c r="H9" s="886"/>
+      <c r="I9" s="886"/>
+      <c r="J9" s="886"/>
+      <c r="K9" s="886"/>
       <c r="L9" s="289" t="s">
         <v>31</v>
       </c>
@@ -23081,25 +23081,25 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="485" t="s">
         <v>249</v>
       </c>
       <c r="B10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="858">
+      <c r="C10" s="886">
         <f>+FORMATO!O3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="858"/>
-      <c r="E10" s="858"/>
-      <c r="F10" s="858"/>
-      <c r="G10" s="858"/>
-      <c r="H10" s="858"/>
-      <c r="I10" s="858"/>
-      <c r="J10" s="858"/>
-      <c r="K10" s="858"/>
+      <c r="D10" s="886"/>
+      <c r="E10" s="886"/>
+      <c r="F10" s="886"/>
+      <c r="G10" s="886"/>
+      <c r="H10" s="886"/>
+      <c r="I10" s="886"/>
+      <c r="J10" s="886"/>
+      <c r="K10" s="886"/>
       <c r="L10" s="764" t="s">
         <v>447</v>
       </c>
@@ -23120,25 +23120,25 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="485" t="s">
         <v>235</v>
       </c>
       <c r="B11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="858">
+      <c r="C11" s="886">
         <f>+FORMATO!O4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="858"/>
-      <c r="E11" s="858"/>
-      <c r="F11" s="858"/>
-      <c r="G11" s="858"/>
-      <c r="H11" s="858"/>
-      <c r="I11" s="858"/>
-      <c r="J11" s="858"/>
-      <c r="K11" s="858"/>
+      <c r="D11" s="886"/>
+      <c r="E11" s="886"/>
+      <c r="F11" s="886"/>
+      <c r="G11" s="886"/>
+      <c r="H11" s="886"/>
+      <c r="I11" s="886"/>
+      <c r="J11" s="886"/>
+      <c r="K11" s="886"/>
       <c r="L11" s="291" t="s">
         <v>466</v>
       </c>
@@ -23151,14 +23151,14 @@
       </c>
       <c r="O11" s="570"/>
       <c r="P11" s="570"/>
-      <c r="Q11" s="847" t="s">
+      <c r="Q11" s="875" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="857"/>
-      <c r="S11" s="857"/>
-      <c r="T11" s="857"/>
-      <c r="U11" s="857"/>
-      <c r="V11" s="848"/>
+      <c r="R11" s="885"/>
+      <c r="S11" s="885"/>
+      <c r="T11" s="885"/>
+      <c r="U11" s="885"/>
+      <c r="V11" s="876"/>
       <c r="X11" s="571" t="s">
         <v>198</v>
       </c>
@@ -23172,25 +23172,25 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="485" t="s">
         <v>236</v>
       </c>
       <c r="B12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="858">
+      <c r="C12" s="886">
         <f>+FORMATO!O5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="858"/>
-      <c r="E12" s="858"/>
-      <c r="F12" s="858"/>
-      <c r="G12" s="858"/>
-      <c r="H12" s="858"/>
-      <c r="I12" s="858"/>
-      <c r="J12" s="858"/>
-      <c r="K12" s="858"/>
+      <c r="D12" s="886"/>
+      <c r="E12" s="886"/>
+      <c r="F12" s="886"/>
+      <c r="G12" s="886"/>
+      <c r="H12" s="886"/>
+      <c r="I12" s="886"/>
+      <c r="J12" s="886"/>
+      <c r="K12" s="886"/>
       <c r="L12" s="764" t="s">
         <v>253</v>
       </c>
@@ -23229,7 +23229,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="487" t="s">
         <v>237</v>
       </c>
@@ -23275,23 +23275,23 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="849" t="s">
+    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="877" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="850"/>
-      <c r="C14" s="850"/>
-      <c r="D14" s="851"/>
-      <c r="E14" s="850"/>
-      <c r="F14" s="851"/>
-      <c r="G14" s="851"/>
-      <c r="H14" s="851"/>
-      <c r="I14" s="851"/>
-      <c r="J14" s="851"/>
-      <c r="K14" s="851"/>
-      <c r="L14" s="851"/>
-      <c r="M14" s="851"/>
-      <c r="N14" s="852"/>
+      <c r="B14" s="878"/>
+      <c r="C14" s="878"/>
+      <c r="D14" s="879"/>
+      <c r="E14" s="878"/>
+      <c r="F14" s="879"/>
+      <c r="G14" s="879"/>
+      <c r="H14" s="879"/>
+      <c r="I14" s="879"/>
+      <c r="J14" s="879"/>
+      <c r="K14" s="879"/>
+      <c r="L14" s="879"/>
+      <c r="M14" s="879"/>
+      <c r="N14" s="880"/>
       <c r="O14" s="570"/>
       <c r="P14" s="570"/>
       <c r="Q14" s="478" t="s">
@@ -23321,23 +23321,23 @@
         <v>442</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="853" t="s">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="881" t="s">
         <v>476</v>
       </c>
-      <c r="B15" s="854"/>
-      <c r="C15" s="854"/>
-      <c r="D15" s="854"/>
-      <c r="E15" s="854"/>
-      <c r="F15" s="854"/>
-      <c r="G15" s="854"/>
-      <c r="H15" s="854"/>
-      <c r="I15" s="854"/>
-      <c r="J15" s="854"/>
-      <c r="K15" s="854"/>
-      <c r="L15" s="854"/>
-      <c r="M15" s="854"/>
-      <c r="N15" s="855"/>
+      <c r="B15" s="882"/>
+      <c r="C15" s="882"/>
+      <c r="D15" s="882"/>
+      <c r="E15" s="882"/>
+      <c r="F15" s="882"/>
+      <c r="G15" s="882"/>
+      <c r="H15" s="882"/>
+      <c r="I15" s="882"/>
+      <c r="J15" s="882"/>
+      <c r="K15" s="882"/>
+      <c r="L15" s="882"/>
+      <c r="M15" s="882"/>
+      <c r="N15" s="883"/>
       <c r="O15" s="570"/>
       <c r="P15" s="570"/>
       <c r="V15" s="386"/>
@@ -23352,7 +23352,7 @@
       <c r="AA15" s="653"/>
       <c r="AB15" s="577"/>
     </row>
-    <row r="16" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="294"/>
       <c r="B16" s="414"/>
       <c r="C16" s="414"/>
@@ -23369,17 +23369,17 @@
       <c r="N16" s="298"/>
       <c r="O16" s="570"/>
       <c r="P16" s="570"/>
-      <c r="Q16" s="847" t="s">
+      <c r="Q16" s="875" t="s">
         <v>438</v>
       </c>
-      <c r="R16" s="857"/>
-      <c r="S16" s="857"/>
-      <c r="T16" s="857"/>
-      <c r="U16" s="857"/>
-      <c r="V16" s="848"/>
+      <c r="R16" s="885"/>
+      <c r="S16" s="885"/>
+      <c r="T16" s="885"/>
+      <c r="U16" s="885"/>
+      <c r="V16" s="876"/>
       <c r="W16" s="578"/>
     </row>
-    <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="299" t="s">
         <v>26</v>
       </c>
@@ -23411,17 +23411,17 @@
         <f>U17+(U17*$Z$14)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="865" t="s">
+      <c r="X17" s="857" t="s">
         <v>433</v>
       </c>
-      <c r="Y17" s="866"/>
-      <c r="Z17" s="866"/>
-      <c r="AA17" s="867"/>
+      <c r="Y17" s="858"/>
+      <c r="Z17" s="858"/>
+      <c r="AA17" s="859"/>
       <c r="AB17" s="599" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="303" t="s">
         <v>244</v>
       </c>
@@ -23474,7 +23474,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="303" t="s">
         <v>245</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="303" t="s">
         <v>25</v>
       </c>
@@ -23583,7 +23583,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="494" t="s">
         <v>246</v>
       </c>
@@ -23622,7 +23622,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="627"/>
       <c r="B22" s="417"/>
       <c r="C22" s="417"/>
@@ -23640,20 +23640,20 @@
       <c r="O22" s="570"/>
       <c r="P22" s="582"/>
     </row>
-    <row r="23" spans="1:32" ht="31.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="630"/>
       <c r="B23" s="621"/>
       <c r="C23" s="621"/>
       <c r="D23" s="621"/>
-      <c r="E23" s="870" t="s">
+      <c r="E23" s="862" t="s">
         <v>448</v>
       </c>
-      <c r="F23" s="876"/>
-      <c r="G23" s="876"/>
-      <c r="H23" s="876"/>
-      <c r="I23" s="876"/>
-      <c r="J23" s="871"/>
-      <c r="K23" s="868" t="s">
+      <c r="F23" s="868"/>
+      <c r="G23" s="868"/>
+      <c r="H23" s="868"/>
+      <c r="I23" s="868"/>
+      <c r="J23" s="863"/>
+      <c r="K23" s="860" t="s">
         <v>385</v>
       </c>
       <c r="L23" s="621"/>
@@ -23661,10 +23661,10 @@
       <c r="N23" s="307"/>
       <c r="O23" s="570"/>
       <c r="P23" s="583"/>
-      <c r="Q23" s="847" t="s">
+      <c r="Q23" s="875" t="s">
         <v>357</v>
       </c>
-      <c r="R23" s="848"/>
+      <c r="R23" s="876"/>
       <c r="S23" s="387" t="s">
         <v>356</v>
       </c>
@@ -23692,22 +23692,22 @@
       <c r="AE23" s="584"/>
       <c r="AF23" s="500"/>
     </row>
-    <row r="24" spans="1:32" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="630"/>
       <c r="B24" s="621"/>
       <c r="C24" s="621"/>
       <c r="D24" s="621"/>
-      <c r="E24" s="870" t="s">
+      <c r="E24" s="862" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="876"/>
-      <c r="G24" s="876"/>
-      <c r="H24" s="871"/>
-      <c r="I24" s="870" t="s">
+      <c r="F24" s="868"/>
+      <c r="G24" s="868"/>
+      <c r="H24" s="863"/>
+      <c r="I24" s="862" t="s">
         <v>457</v>
       </c>
-      <c r="J24" s="871"/>
-      <c r="K24" s="869"/>
+      <c r="J24" s="863"/>
+      <c r="K24" s="861"/>
       <c r="L24" s="621"/>
       <c r="M24" s="631"/>
       <c r="N24" s="307"/>
@@ -23751,21 +23751,21 @@
       <c r="AE24" s="584"/>
       <c r="AF24" s="500"/>
     </row>
-    <row r="25" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="632"/>
       <c r="B25" s="623"/>
       <c r="C25" s="623"/>
       <c r="D25" s="623"/>
-      <c r="E25" s="877" t="s">
+      <c r="E25" s="869" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="878"/>
-      <c r="G25" s="878"/>
-      <c r="H25" s="879"/>
-      <c r="I25" s="872" t="s">
+      <c r="F25" s="870"/>
+      <c r="G25" s="870"/>
+      <c r="H25" s="871"/>
+      <c r="I25" s="864" t="s">
         <v>449</v>
       </c>
-      <c r="J25" s="873"/>
+      <c r="J25" s="865"/>
       <c r="K25" s="617" t="e">
         <f>IF($I$66="Método A",FIXED(($W$25),0),FIXED(($W$25),1))</f>
         <v>#DIV/0!</v>
@@ -23782,7 +23782,7 @@
         <v>75</v>
       </c>
       <c r="S25" s="665">
-        <f>+FORMATO!E42</f>
+        <f>+FORMATO!D42</f>
         <v>0</v>
       </c>
       <c r="T25" s="523">
@@ -23807,21 +23807,21 @@
       <c r="AE25" s="584"/>
       <c r="AF25" s="500"/>
     </row>
-    <row r="26" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="632"/>
       <c r="B26" s="623"/>
       <c r="C26" s="623"/>
       <c r="D26" s="623"/>
-      <c r="E26" s="827" t="s">
+      <c r="E26" s="835" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="828"/>
-      <c r="G26" s="828"/>
-      <c r="H26" s="829"/>
-      <c r="I26" s="874" t="s">
+      <c r="F26" s="836"/>
+      <c r="G26" s="836"/>
+      <c r="H26" s="837"/>
+      <c r="I26" s="866" t="s">
         <v>450</v>
       </c>
-      <c r="J26" s="875"/>
+      <c r="J26" s="867"/>
       <c r="K26" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$26),0),FIXED(($W$26),1))</f>
         <v>#DIV/0!</v>
@@ -23863,21 +23863,21 @@
       <c r="AE26" s="584"/>
       <c r="AF26" s="500"/>
     </row>
-    <row r="27" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="634"/>
       <c r="B27" s="624"/>
       <c r="C27" s="624"/>
       <c r="D27" s="624"/>
-      <c r="E27" s="897" t="s">
+      <c r="E27" s="830" t="s">
         <v>353</v>
       </c>
-      <c r="F27" s="898"/>
-      <c r="G27" s="898"/>
-      <c r="H27" s="899"/>
-      <c r="I27" s="861" t="s">
+      <c r="F27" s="831"/>
+      <c r="G27" s="831"/>
+      <c r="H27" s="832"/>
+      <c r="I27" s="833" t="s">
         <v>451</v>
       </c>
-      <c r="J27" s="862"/>
+      <c r="J27" s="834"/>
       <c r="K27" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$27),0),FIXED(($W$27),1))</f>
         <v>#DIV/0!</v>
@@ -23919,21 +23919,21 @@
       <c r="AE27" s="584"/>
       <c r="AF27" s="500"/>
     </row>
-    <row r="28" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="632"/>
       <c r="B28" s="623"/>
       <c r="C28" s="623"/>
       <c r="D28" s="623"/>
-      <c r="E28" s="827" t="s">
+      <c r="E28" s="835" t="s">
         <v>352</v>
       </c>
-      <c r="F28" s="828"/>
-      <c r="G28" s="828"/>
-      <c r="H28" s="829"/>
-      <c r="I28" s="861" t="s">
+      <c r="F28" s="836"/>
+      <c r="G28" s="836"/>
+      <c r="H28" s="837"/>
+      <c r="I28" s="833" t="s">
         <v>452</v>
       </c>
-      <c r="J28" s="862"/>
+      <c r="J28" s="834"/>
       <c r="K28" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$28),0),FIXED(($W$28),1))</f>
         <v>#DIV/0!</v>
@@ -23975,21 +23975,21 @@
       <c r="AE28" s="584"/>
       <c r="AF28" s="500"/>
     </row>
-    <row r="29" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="632"/>
       <c r="B29" s="623"/>
       <c r="C29" s="623"/>
       <c r="D29" s="623"/>
-      <c r="E29" s="827" t="s">
+      <c r="E29" s="835" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="828"/>
-      <c r="G29" s="828"/>
-      <c r="H29" s="829"/>
-      <c r="I29" s="861" t="s">
+      <c r="F29" s="836"/>
+      <c r="G29" s="836"/>
+      <c r="H29" s="837"/>
+      <c r="I29" s="833" t="s">
         <v>453</v>
       </c>
-      <c r="J29" s="862"/>
+      <c r="J29" s="834"/>
       <c r="K29" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$29),0),FIXED(($W$29),1))</f>
         <v>#DIV/0!</v>
@@ -24031,21 +24031,21 @@
       <c r="AE29" s="584"/>
       <c r="AF29" s="500"/>
     </row>
-    <row r="30" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="632"/>
       <c r="B30" s="623"/>
       <c r="C30" s="623"/>
       <c r="D30" s="623"/>
-      <c r="E30" s="827" t="s">
+      <c r="E30" s="835" t="s">
         <v>355</v>
       </c>
-      <c r="F30" s="828"/>
-      <c r="G30" s="828"/>
-      <c r="H30" s="829"/>
-      <c r="I30" s="861" t="s">
+      <c r="F30" s="836"/>
+      <c r="G30" s="836"/>
+      <c r="H30" s="837"/>
+      <c r="I30" s="833" t="s">
         <v>454</v>
       </c>
-      <c r="J30" s="862"/>
+      <c r="J30" s="834"/>
       <c r="K30" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$30),0),FIXED(($W$30),1))</f>
         <v>#DIV/0!</v>
@@ -24087,21 +24087,21 @@
       <c r="AE30" s="584"/>
       <c r="AF30" s="500"/>
     </row>
-    <row r="31" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="632"/>
       <c r="B31" s="623"/>
       <c r="C31" s="623"/>
       <c r="D31" s="623"/>
-      <c r="E31" s="827" t="s">
+      <c r="E31" s="835" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="828"/>
-      <c r="G31" s="828"/>
-      <c r="H31" s="829"/>
-      <c r="I31" s="863" t="s">
+      <c r="F31" s="836"/>
+      <c r="G31" s="836"/>
+      <c r="H31" s="837"/>
+      <c r="I31" s="838" t="s">
         <v>455</v>
       </c>
-      <c r="J31" s="864"/>
+      <c r="J31" s="839"/>
       <c r="K31" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$31),0),FIXED(($W$31),1))</f>
         <v>#DIV/0!</v>
@@ -24147,21 +24147,21 @@
       <c r="AE31" s="584"/>
       <c r="AF31" s="500"/>
     </row>
-    <row r="32" spans="1:32" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="632"/>
       <c r="B32" s="623"/>
       <c r="C32" s="623"/>
       <c r="D32" s="623"/>
-      <c r="E32" s="827" t="s">
+      <c r="E32" s="835" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="828"/>
-      <c r="G32" s="828"/>
-      <c r="H32" s="829"/>
-      <c r="I32" s="863" t="s">
+      <c r="F32" s="836"/>
+      <c r="G32" s="836"/>
+      <c r="H32" s="837"/>
+      <c r="I32" s="838" t="s">
         <v>456</v>
       </c>
-      <c r="J32" s="864"/>
+      <c r="J32" s="839"/>
       <c r="K32" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$32),0),FIXED(($W$32),1))</f>
         <v>#DIV/0!</v>
@@ -24207,21 +24207,21 @@
       <c r="AE32" s="584"/>
       <c r="AF32" s="500"/>
     </row>
-    <row r="33" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="632"/>
       <c r="B33" s="623"/>
       <c r="C33" s="623"/>
       <c r="D33" s="623"/>
-      <c r="E33" s="827" t="s">
+      <c r="E33" s="835" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="828"/>
-      <c r="G33" s="828"/>
-      <c r="H33" s="829"/>
-      <c r="I33" s="859" t="s">
+      <c r="F33" s="836"/>
+      <c r="G33" s="836"/>
+      <c r="H33" s="837"/>
+      <c r="I33" s="840" t="s">
         <v>458</v>
       </c>
-      <c r="J33" s="860"/>
+      <c r="J33" s="841"/>
       <c r="K33" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$33),0),FIXED(($W$33),1))</f>
         <v>#DIV/0!</v>
@@ -24259,21 +24259,21 @@
       </c>
       <c r="X33" s="504"/>
     </row>
-    <row r="34" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="632"/>
       <c r="B34" s="623"/>
       <c r="C34" s="623"/>
       <c r="D34" s="623"/>
-      <c r="E34" s="827" t="s">
+      <c r="E34" s="835" t="s">
         <v>418</v>
       </c>
-      <c r="F34" s="828"/>
-      <c r="G34" s="828"/>
-      <c r="H34" s="829"/>
-      <c r="I34" s="859" t="s">
+      <c r="F34" s="836"/>
+      <c r="G34" s="836"/>
+      <c r="H34" s="837"/>
+      <c r="I34" s="840" t="s">
         <v>459</v>
       </c>
-      <c r="J34" s="860"/>
+      <c r="J34" s="841"/>
       <c r="K34" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$34),0),FIXED(($W$34),1))</f>
         <v>#DIV/0!</v>
@@ -24315,21 +24315,21 @@
       <c r="AD34" s="584"/>
       <c r="AE34" s="588"/>
     </row>
-    <row r="35" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="632"/>
       <c r="B35" s="623"/>
       <c r="C35" s="623"/>
       <c r="D35" s="623"/>
-      <c r="E35" s="827" t="s">
+      <c r="E35" s="835" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="828"/>
-      <c r="G35" s="828"/>
-      <c r="H35" s="829"/>
-      <c r="I35" s="859" t="s">
+      <c r="F35" s="836"/>
+      <c r="G35" s="836"/>
+      <c r="H35" s="837"/>
+      <c r="I35" s="840" t="s">
         <v>460</v>
       </c>
-      <c r="J35" s="860"/>
+      <c r="J35" s="841"/>
       <c r="K35" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$35),0),FIXED(($W$35),1))</f>
         <v>#DIV/0!</v>
@@ -24371,21 +24371,21 @@
       <c r="AD35" s="584"/>
       <c r="AE35" s="587"/>
     </row>
-    <row r="36" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="632"/>
       <c r="B36" s="623"/>
       <c r="C36" s="623"/>
       <c r="D36" s="623"/>
-      <c r="E36" s="827" t="s">
+      <c r="E36" s="835" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="828"/>
-      <c r="G36" s="828"/>
-      <c r="H36" s="829"/>
-      <c r="I36" s="859" t="s">
+      <c r="F36" s="836"/>
+      <c r="G36" s="836"/>
+      <c r="H36" s="837"/>
+      <c r="I36" s="840" t="s">
         <v>461</v>
       </c>
-      <c r="J36" s="860"/>
+      <c r="J36" s="841"/>
       <c r="K36" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$36),0),FIXED(($W$36),1))</f>
         <v>#DIV/0!</v>
@@ -24426,21 +24426,21 @@
       <c r="Z36" s="508"/>
       <c r="AA36" s="513"/>
     </row>
-    <row r="37" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="632"/>
       <c r="B37" s="623"/>
       <c r="C37" s="623"/>
       <c r="D37" s="623"/>
-      <c r="E37" s="827" t="s">
+      <c r="E37" s="835" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="828"/>
-      <c r="G37" s="828"/>
-      <c r="H37" s="829"/>
-      <c r="I37" s="859" t="s">
+      <c r="F37" s="836"/>
+      <c r="G37" s="836"/>
+      <c r="H37" s="837"/>
+      <c r="I37" s="840" t="s">
         <v>462</v>
       </c>
-      <c r="J37" s="860"/>
+      <c r="J37" s="841"/>
       <c r="K37" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$37),0),FIXED(($W$37),1))</f>
         <v>#DIV/0!</v>
@@ -24481,21 +24481,21 @@
       <c r="Z37" s="508"/>
       <c r="AA37" s="589"/>
     </row>
-    <row r="38" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="632"/>
       <c r="B38" s="623"/>
       <c r="C38" s="623"/>
       <c r="D38" s="623"/>
-      <c r="E38" s="830" t="s">
+      <c r="E38" s="892" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="831"/>
-      <c r="G38" s="831"/>
-      <c r="H38" s="832"/>
-      <c r="I38" s="838" t="s">
+      <c r="F38" s="893"/>
+      <c r="G38" s="893"/>
+      <c r="H38" s="894"/>
+      <c r="I38" s="898" t="s">
         <v>463</v>
       </c>
-      <c r="J38" s="839"/>
+      <c r="J38" s="899"/>
       <c r="K38" s="317" t="e">
         <f>IF($I$66="Método A",FIXED(($W$38),0),FIXED(($W$38),1))</f>
         <v>#DIV/0!</v>
@@ -24538,7 +24538,7 @@
       <c r="AC38" s="584"/>
       <c r="AD38" s="587"/>
     </row>
-    <row r="39" spans="1:31" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="637"/>
       <c r="B39" s="638"/>
       <c r="C39" s="638"/>
@@ -24589,7 +24589,7 @@
       <c r="AC39" s="513"/>
       <c r="AD39" s="513"/>
     </row>
-    <row r="40" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="637"/>
       <c r="B40" s="638"/>
       <c r="C40" s="638"/>
@@ -24611,7 +24611,7 @@
       <c r="AC40" s="513"/>
       <c r="AD40" s="513"/>
     </row>
-    <row r="41" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="637"/>
       <c r="B41" s="638"/>
       <c r="C41" s="638"/>
@@ -24628,18 +24628,18 @@
       <c r="N41" s="313"/>
       <c r="O41" s="570"/>
       <c r="P41" s="570"/>
-      <c r="Q41" s="880" t="s">
+      <c r="Q41" s="843" t="s">
         <v>420</v>
       </c>
-      <c r="R41" s="881"/>
-      <c r="S41" s="881"/>
-      <c r="T41" s="882"/>
+      <c r="R41" s="844"/>
+      <c r="S41" s="844"/>
+      <c r="T41" s="845"/>
       <c r="AA41" s="513"/>
       <c r="AB41" s="513"/>
       <c r="AC41" s="513"/>
       <c r="AD41" s="513"/>
     </row>
-    <row r="42" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="637"/>
       <c r="B42" s="638"/>
       <c r="C42" s="638"/>
@@ -24656,10 +24656,10 @@
       <c r="N42" s="313"/>
       <c r="O42" s="570"/>
       <c r="P42" s="570"/>
-      <c r="Q42" s="883"/>
-      <c r="R42" s="884"/>
-      <c r="S42" s="884"/>
-      <c r="T42" s="885"/>
+      <c r="Q42" s="846"/>
+      <c r="R42" s="847"/>
+      <c r="S42" s="847"/>
+      <c r="T42" s="848"/>
       <c r="U42" s="620"/>
       <c r="V42" s="620"/>
       <c r="AA42" s="513"/>
@@ -24667,7 +24667,7 @@
       <c r="AC42" s="513"/>
       <c r="AD42" s="513"/>
     </row>
-    <row r="43" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="637"/>
       <c r="B43" s="638"/>
       <c r="C43" s="638"/>
@@ -24684,10 +24684,10 @@
       <c r="N43" s="313"/>
       <c r="O43" s="570"/>
       <c r="P43" s="570"/>
-      <c r="Q43" s="886" t="s">
+      <c r="Q43" s="849" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="888" t="e">
+      <c r="R43" s="851" t="e">
         <f>$V$31</f>
         <v>#DIV/0!</v>
       </c>
@@ -24705,7 +24705,7 @@
       <c r="AC43" s="577"/>
       <c r="AD43" s="513"/>
     </row>
-    <row r="44" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="637"/>
       <c r="B44" s="638"/>
       <c r="C44" s="638"/>
@@ -24722,8 +24722,8 @@
       <c r="N44" s="313"/>
       <c r="O44" s="570"/>
       <c r="P44" s="570"/>
-      <c r="Q44" s="887"/>
-      <c r="R44" s="889"/>
+      <c r="Q44" s="850"/>
+      <c r="R44" s="852"/>
       <c r="S44" s="311" t="s">
         <v>36</v>
       </c>
@@ -24740,7 +24740,7 @@
       <c r="AC44" s="577"/>
       <c r="AD44" s="590"/>
     </row>
-    <row r="45" spans="1:31" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="637"/>
       <c r="B45" s="638"/>
       <c r="C45" s="638"/>
@@ -24757,10 +24757,10 @@
       <c r="N45" s="313"/>
       <c r="O45" s="570"/>
       <c r="P45" s="570"/>
-      <c r="Q45" s="890" t="s">
+      <c r="Q45" s="853" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="892" t="e">
+      <c r="R45" s="855" t="e">
         <f>100-(R43+R48)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24781,7 +24781,7 @@
       <c r="AC45" s="577"/>
       <c r="AD45" s="513"/>
     </row>
-    <row r="46" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="637"/>
       <c r="B46" s="638"/>
       <c r="C46" s="638"/>
@@ -24798,8 +24798,8 @@
       <c r="N46" s="313"/>
       <c r="O46" s="570"/>
       <c r="P46" s="570"/>
-      <c r="Q46" s="891"/>
-      <c r="R46" s="893"/>
+      <c r="Q46" s="854"/>
+      <c r="R46" s="856"/>
       <c r="S46" s="311" t="s">
         <v>38</v>
       </c>
@@ -24816,7 +24816,7 @@
       <c r="AC46" s="591"/>
       <c r="AD46" s="513"/>
     </row>
-    <row r="47" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="637"/>
       <c r="B47" s="638"/>
       <c r="C47" s="638"/>
@@ -24833,8 +24833,8 @@
       <c r="N47" s="313"/>
       <c r="O47" s="570"/>
       <c r="P47" s="570"/>
-      <c r="Q47" s="887"/>
-      <c r="R47" s="889"/>
+      <c r="Q47" s="850"/>
+      <c r="R47" s="852"/>
       <c r="S47" s="311" t="s">
         <v>36</v>
       </c>
@@ -24848,7 +24848,7 @@
       <c r="AC47" s="591"/>
       <c r="AD47" s="513"/>
     </row>
-    <row r="48" spans="1:31" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="637"/>
       <c r="B48" s="638"/>
       <c r="C48" s="638"/>
@@ -24884,7 +24884,7 @@
       <c r="AC48" s="513"/>
       <c r="AD48" s="513"/>
     </row>
-    <row r="49" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="637"/>
       <c r="B49" s="638"/>
       <c r="C49" s="638"/>
@@ -24912,7 +24912,7 @@
       <c r="AC49" s="513"/>
       <c r="AD49" s="513"/>
     </row>
-    <row r="50" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="637"/>
       <c r="B50" s="638"/>
       <c r="C50" s="638"/>
@@ -24940,7 +24940,7 @@
       <c r="AC50" s="513"/>
       <c r="AD50" s="513"/>
     </row>
-    <row r="51" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="637"/>
       <c r="B51" s="638"/>
       <c r="C51" s="638"/>
@@ -24972,7 +24972,7 @@
       <c r="AC51" s="513"/>
       <c r="AD51" s="513"/>
     </row>
-    <row r="52" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="637"/>
       <c r="B52" s="638"/>
       <c r="C52" s="638"/>
@@ -25004,7 +25004,7 @@
       <c r="AC52" s="513"/>
       <c r="AD52" s="513"/>
     </row>
-    <row r="53" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="637"/>
       <c r="B53" s="638"/>
       <c r="C53" s="638"/>
@@ -25036,7 +25036,7 @@
       <c r="AC53" s="513"/>
       <c r="AD53" s="513"/>
     </row>
-    <row r="54" spans="1:30" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="637"/>
       <c r="B54" s="638"/>
       <c r="C54" s="638"/>
@@ -25068,7 +25068,7 @@
       <c r="AC54" s="513"/>
       <c r="AD54" s="513"/>
     </row>
-    <row r="55" spans="1:30" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="637"/>
       <c r="B55" s="638"/>
       <c r="C55" s="638"/>
@@ -25100,7 +25100,7 @@
       <c r="AC55" s="513"/>
       <c r="AD55" s="513"/>
     </row>
-    <row r="56" spans="1:30" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="639"/>
       <c r="B56" s="640"/>
       <c r="C56" s="640"/>
@@ -25132,7 +25132,7 @@
       <c r="AC56" s="513"/>
       <c r="AD56" s="513"/>
     </row>
-    <row r="57" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="318"/>
       <c r="B57" s="318"/>
       <c r="C57" s="318"/>
@@ -25164,7 +25164,7 @@
       <c r="AC57" s="513"/>
       <c r="AD57" s="513"/>
     </row>
-    <row r="58" spans="1:30" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="305"/>
       <c r="B58" s="305"/>
       <c r="C58" s="305"/>
@@ -25196,7 +25196,7 @@
       <c r="AC58" s="513"/>
       <c r="AD58" s="513"/>
     </row>
-    <row r="59" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="319" t="s">
         <v>247</v>
       </c>
@@ -25230,7 +25230,7 @@
       <c r="AC59" s="513"/>
       <c r="AD59" s="513"/>
     </row>
-    <row r="60" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="319" t="s">
         <v>573</v>
       </c>
@@ -25264,7 +25264,7 @@
       <c r="AC60" s="513"/>
       <c r="AD60" s="513"/>
     </row>
-    <row r="61" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="305"/>
       <c r="B61" s="305"/>
       <c r="C61" s="305"/>
@@ -25296,7 +25296,7 @@
       <c r="AC61" s="513"/>
       <c r="AD61" s="513"/>
     </row>
-    <row r="62" spans="1:30" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:30" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="305"/>
       <c r="B62" s="305"/>
       <c r="C62" s="305"/>
@@ -25328,7 +25328,7 @@
       <c r="AC62" s="513"/>
       <c r="AD62" s="513"/>
     </row>
-    <row r="63" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="305"/>
       <c r="B63" s="305"/>
       <c r="C63" s="305"/>
@@ -25360,7 +25360,7 @@
       <c r="AC63" s="513"/>
       <c r="AD63" s="513"/>
     </row>
-    <row r="64" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:30" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="305"/>
       <c r="B64" s="305"/>
       <c r="C64" s="305"/>
@@ -25391,7 +25391,7 @@
       <c r="AC64" s="513"/>
       <c r="AD64" s="513"/>
     </row>
-    <row r="65" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="541" t="s">
         <v>371</v>
       </c>
@@ -25424,7 +25424,7 @@
       <c r="AC65" s="513"/>
       <c r="AD65" s="513"/>
     </row>
-    <row r="66" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="544" t="s">
         <v>394</v>
       </c>
@@ -25435,12 +25435,12 @@
       <c r="F66" s="306"/>
       <c r="G66" s="306"/>
       <c r="H66" s="306"/>
-      <c r="I66" s="834" t="str">
+      <c r="I66" s="888" t="str">
         <f>+R2</f>
         <v>-</v>
       </c>
-      <c r="J66" s="834"/>
-      <c r="K66" s="834"/>
+      <c r="J66" s="888"/>
+      <c r="K66" s="888"/>
       <c r="L66" s="421"/>
       <c r="M66" s="421"/>
       <c r="N66" s="545"/>
@@ -25461,7 +25461,7 @@
       <c r="AC66" s="513"/>
       <c r="AD66" s="513"/>
     </row>
-    <row r="67" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="544" t="s">
         <v>395</v>
       </c>
@@ -25472,11 +25472,11 @@
       <c r="F67" s="306"/>
       <c r="G67" s="306"/>
       <c r="H67" s="306"/>
-      <c r="I67" s="834" t="s">
+      <c r="I67" s="888" t="s">
         <v>442</v>
       </c>
-      <c r="J67" s="834"/>
-      <c r="K67" s="834"/>
+      <c r="J67" s="888"/>
+      <c r="K67" s="888"/>
       <c r="L67" s="421"/>
       <c r="M67" s="421"/>
       <c r="N67" s="545"/>
@@ -25497,7 +25497,7 @@
       <c r="AC67" s="513"/>
       <c r="AD67" s="513"/>
     </row>
-    <row r="68" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="544" t="s">
         <v>393</v>
       </c>
@@ -25508,11 +25508,11 @@
       <c r="F68" s="546"/>
       <c r="G68" s="546"/>
       <c r="H68" s="546"/>
-      <c r="I68" s="834" t="s">
+      <c r="I68" s="888" t="s">
         <v>442</v>
       </c>
-      <c r="J68" s="834"/>
-      <c r="K68" s="834"/>
+      <c r="J68" s="888"/>
+      <c r="K68" s="888"/>
       <c r="L68" s="421"/>
       <c r="M68" s="421"/>
       <c r="N68" s="545"/>
@@ -25533,7 +25533,7 @@
       <c r="AC68" s="513"/>
       <c r="AD68" s="513"/>
     </row>
-    <row r="69" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="544" t="s">
         <v>392</v>
       </c>
@@ -25544,11 +25544,11 @@
       <c r="F69" s="546"/>
       <c r="G69" s="546"/>
       <c r="H69" s="546"/>
-      <c r="I69" s="833" t="s">
+      <c r="I69" s="842" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="833"/>
-      <c r="K69" s="833"/>
+      <c r="J69" s="842"/>
+      <c r="K69" s="842"/>
       <c r="L69" s="421"/>
       <c r="M69" s="421"/>
       <c r="N69" s="545"/>
@@ -25569,7 +25569,7 @@
       <c r="AC69" s="513"/>
       <c r="AD69" s="513"/>
     </row>
-    <row r="70" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="544" t="s">
         <v>391</v>
       </c>
@@ -25580,11 +25580,11 @@
       <c r="F70" s="546"/>
       <c r="G70" s="546"/>
       <c r="H70" s="546"/>
-      <c r="I70" s="834" t="s">
+      <c r="I70" s="888" t="s">
         <v>442</v>
       </c>
-      <c r="J70" s="834"/>
-      <c r="K70" s="834"/>
+      <c r="J70" s="888"/>
+      <c r="K70" s="888"/>
       <c r="L70" s="421"/>
       <c r="M70" s="421"/>
       <c r="N70" s="545"/>
@@ -25605,7 +25605,7 @@
       <c r="AC70" s="513"/>
       <c r="AD70" s="513"/>
     </row>
-    <row r="71" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="544" t="s">
         <v>389</v>
       </c>
@@ -25616,11 +25616,11 @@
       <c r="F71" s="546"/>
       <c r="G71" s="546"/>
       <c r="H71" s="546"/>
-      <c r="I71" s="833" t="s">
+      <c r="I71" s="842" t="s">
         <v>252</v>
       </c>
-      <c r="J71" s="833"/>
-      <c r="K71" s="833"/>
+      <c r="J71" s="842"/>
+      <c r="K71" s="842"/>
       <c r="L71" s="421"/>
       <c r="M71" s="421"/>
       <c r="N71" s="545"/>
@@ -25641,7 +25641,7 @@
       <c r="AC71" s="513"/>
       <c r="AD71" s="513"/>
     </row>
-    <row r="72" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="544" t="s">
         <v>390</v>
       </c>
@@ -25652,11 +25652,11 @@
       <c r="F72" s="306"/>
       <c r="G72" s="306"/>
       <c r="H72" s="306"/>
-      <c r="I72" s="835" t="s">
+      <c r="I72" s="895" t="s">
         <v>442</v>
       </c>
-      <c r="J72" s="836"/>
-      <c r="K72" s="837"/>
+      <c r="J72" s="896"/>
+      <c r="K72" s="897"/>
       <c r="L72" s="319"/>
       <c r="M72" s="319"/>
       <c r="N72" s="547"/>
@@ -25677,7 +25677,7 @@
       <c r="AC72" s="513"/>
       <c r="AD72" s="513"/>
     </row>
-    <row r="73" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="548"/>
       <c r="B73" s="423"/>
       <c r="C73" s="423"/>
@@ -25708,7 +25708,7 @@
       <c r="AC73" s="513"/>
       <c r="AD73" s="513"/>
     </row>
-    <row r="74" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="550" t="s">
         <v>372</v>
       </c>
@@ -25742,7 +25742,7 @@
       <c r="AC74" s="513"/>
       <c r="AD74" s="513"/>
     </row>
-    <row r="75" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="544" t="s">
         <v>468</v>
       </c>
@@ -25752,14 +25752,14 @@
       <c r="E75" s="306"/>
       <c r="F75" s="306"/>
       <c r="H75" s="306"/>
-      <c r="I75" s="833"/>
-      <c r="J75" s="833"/>
-      <c r="K75" s="833"/>
-      <c r="L75" s="894">
+      <c r="I75" s="842"/>
+      <c r="J75" s="842"/>
+      <c r="K75" s="842"/>
+      <c r="L75" s="827">
         <v>0</v>
       </c>
-      <c r="M75" s="895"/>
-      <c r="N75" s="896"/>
+      <c r="M75" s="828"/>
+      <c r="N75" s="829"/>
       <c r="O75" s="570"/>
       <c r="P75" s="570"/>
       <c r="Q75" s="424"/>
@@ -25777,7 +25777,7 @@
       <c r="AC75" s="513"/>
       <c r="AD75" s="513"/>
     </row>
-    <row r="76" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="544" t="s">
         <v>396</v>
       </c>
@@ -25787,11 +25787,11 @@
       <c r="E76" s="306"/>
       <c r="F76" s="306"/>
       <c r="H76" s="306"/>
-      <c r="I76" s="834" t="s">
+      <c r="I76" s="888" t="s">
         <v>442</v>
       </c>
-      <c r="J76" s="834"/>
-      <c r="K76" s="834"/>
+      <c r="J76" s="888"/>
+      <c r="K76" s="888"/>
       <c r="L76" s="306"/>
       <c r="M76" s="306"/>
       <c r="N76" s="552"/>
@@ -25812,7 +25812,7 @@
       <c r="AC76" s="513"/>
       <c r="AD76" s="513"/>
     </row>
-    <row r="77" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="544" t="s">
         <v>465</v>
       </c>
@@ -25822,12 +25822,12 @@
       <c r="E77" s="306"/>
       <c r="F77" s="306"/>
       <c r="H77" s="306"/>
-      <c r="I77" s="841">
+      <c r="I77" s="889">
         <f>+FORMATO!H19</f>
         <v>0</v>
       </c>
-      <c r="J77" s="833"/>
-      <c r="K77" s="833"/>
+      <c r="J77" s="842"/>
+      <c r="K77" s="842"/>
       <c r="L77" s="306"/>
       <c r="M77" s="306"/>
       <c r="N77" s="552"/>
@@ -25848,7 +25848,7 @@
       <c r="AC77" s="513"/>
       <c r="AD77" s="513"/>
     </row>
-    <row r="78" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="544" t="s">
         <v>397</v>
       </c>
@@ -25858,12 +25858,12 @@
       <c r="E78" s="306"/>
       <c r="F78" s="306"/>
       <c r="H78" s="306"/>
-      <c r="I78" s="834">
+      <c r="I78" s="888">
         <f>+FORMATO!H20</f>
         <v>0</v>
       </c>
-      <c r="J78" s="834"/>
-      <c r="K78" s="834"/>
+      <c r="J78" s="888"/>
+      <c r="K78" s="888"/>
       <c r="L78" s="306"/>
       <c r="M78" s="306"/>
       <c r="N78" s="552"/>
@@ -25884,7 +25884,7 @@
       <c r="AC78" s="513"/>
       <c r="AD78" s="513"/>
     </row>
-    <row r="79" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="553"/>
       <c r="B79" s="554"/>
       <c r="C79" s="554"/>
@@ -25916,7 +25916,7 @@
       <c r="AC79" s="513"/>
       <c r="AD79" s="513"/>
     </row>
-    <row r="80" spans="1:30" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="320" t="s">
         <v>386</v>
       </c>
@@ -25950,23 +25950,23 @@
       <c r="AC80" s="513"/>
       <c r="AD80" s="513"/>
     </row>
-    <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="843" t="s">
+    <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="891" t="s">
         <v>568</v>
       </c>
-      <c r="B81" s="843"/>
-      <c r="C81" s="843"/>
-      <c r="D81" s="843"/>
-      <c r="E81" s="843"/>
-      <c r="F81" s="843"/>
-      <c r="G81" s="843"/>
-      <c r="H81" s="843"/>
-      <c r="I81" s="843"/>
-      <c r="J81" s="843"/>
-      <c r="K81" s="843"/>
-      <c r="L81" s="843"/>
-      <c r="M81" s="843"/>
-      <c r="N81" s="843"/>
+      <c r="B81" s="891"/>
+      <c r="C81" s="891"/>
+      <c r="D81" s="891"/>
+      <c r="E81" s="891"/>
+      <c r="F81" s="891"/>
+      <c r="G81" s="891"/>
+      <c r="H81" s="891"/>
+      <c r="I81" s="891"/>
+      <c r="J81" s="891"/>
+      <c r="K81" s="891"/>
+      <c r="L81" s="891"/>
+      <c r="M81" s="891"/>
+      <c r="N81" s="891"/>
       <c r="O81" s="426"/>
       <c r="P81" s="426"/>
       <c r="Q81" s="424"/>
@@ -25984,23 +25984,23 @@
       <c r="AC81" s="513"/>
       <c r="AD81" s="513"/>
     </row>
-    <row r="82" spans="1:30" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="842" t="s">
+    <row r="82" spans="1:30" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="890" t="s">
         <v>569</v>
       </c>
-      <c r="B82" s="842"/>
-      <c r="C82" s="842"/>
-      <c r="D82" s="842"/>
-      <c r="E82" s="842"/>
-      <c r="F82" s="842"/>
-      <c r="G82" s="842"/>
-      <c r="H82" s="842"/>
-      <c r="I82" s="842"/>
-      <c r="J82" s="842"/>
-      <c r="K82" s="842"/>
-      <c r="L82" s="842"/>
-      <c r="M82" s="842"/>
-      <c r="N82" s="842"/>
+      <c r="B82" s="890"/>
+      <c r="C82" s="890"/>
+      <c r="D82" s="890"/>
+      <c r="E82" s="890"/>
+      <c r="F82" s="890"/>
+      <c r="G82" s="890"/>
+      <c r="H82" s="890"/>
+      <c r="I82" s="890"/>
+      <c r="J82" s="890"/>
+      <c r="K82" s="890"/>
+      <c r="L82" s="890"/>
+      <c r="M82" s="890"/>
+      <c r="N82" s="890"/>
       <c r="Q82" s="424"/>
       <c r="R82" s="519"/>
       <c r="S82" s="519"/>
@@ -26016,23 +26016,23 @@
       <c r="AC82" s="513"/>
       <c r="AD82" s="513"/>
     </row>
-    <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="842" t="s">
+    <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="890" t="s">
         <v>570</v>
       </c>
-      <c r="B83" s="842"/>
-      <c r="C83" s="842"/>
-      <c r="D83" s="842"/>
-      <c r="E83" s="842"/>
-      <c r="F83" s="842"/>
-      <c r="G83" s="842"/>
-      <c r="H83" s="842"/>
-      <c r="I83" s="842"/>
-      <c r="J83" s="842"/>
-      <c r="K83" s="842"/>
-      <c r="L83" s="842"/>
-      <c r="M83" s="842"/>
-      <c r="N83" s="842"/>
+      <c r="B83" s="890"/>
+      <c r="C83" s="890"/>
+      <c r="D83" s="890"/>
+      <c r="E83" s="890"/>
+      <c r="F83" s="890"/>
+      <c r="G83" s="890"/>
+      <c r="H83" s="890"/>
+      <c r="I83" s="890"/>
+      <c r="J83" s="890"/>
+      <c r="K83" s="890"/>
+      <c r="L83" s="890"/>
+      <c r="M83" s="890"/>
+      <c r="N83" s="890"/>
       <c r="O83" s="428"/>
       <c r="P83" s="428"/>
       <c r="AA83" s="513"/>
@@ -26040,51 +26040,51 @@
       <c r="AC83" s="513"/>
       <c r="AD83" s="513"/>
     </row>
-    <row r="84" spans="1:30" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="842" t="s">
+    <row r="84" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="890" t="s">
         <v>571</v>
       </c>
-      <c r="B84" s="842"/>
-      <c r="C84" s="842"/>
-      <c r="D84" s="842"/>
-      <c r="E84" s="842"/>
-      <c r="F84" s="842"/>
-      <c r="G84" s="842"/>
-      <c r="H84" s="842"/>
-      <c r="I84" s="842"/>
-      <c r="J84" s="842"/>
-      <c r="K84" s="842"/>
-      <c r="L84" s="842"/>
-      <c r="M84" s="842"/>
-      <c r="N84" s="842"/>
+      <c r="B84" s="890"/>
+      <c r="C84" s="890"/>
+      <c r="D84" s="890"/>
+      <c r="E84" s="890"/>
+      <c r="F84" s="890"/>
+      <c r="G84" s="890"/>
+      <c r="H84" s="890"/>
+      <c r="I84" s="890"/>
+      <c r="J84" s="890"/>
+      <c r="K84" s="890"/>
+      <c r="L84" s="890"/>
+      <c r="M84" s="890"/>
+      <c r="N84" s="890"/>
       <c r="AA84" s="513"/>
       <c r="AB84" s="513"/>
       <c r="AC84" s="513"/>
       <c r="AD84" s="513"/>
     </row>
-    <row r="85" spans="1:30" ht="25.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="840" t="s">
+    <row r="85" spans="1:30" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="887" t="s">
         <v>572</v>
       </c>
-      <c r="B85" s="840"/>
-      <c r="C85" s="840"/>
-      <c r="D85" s="840"/>
-      <c r="E85" s="840"/>
-      <c r="F85" s="840"/>
-      <c r="G85" s="840"/>
-      <c r="H85" s="840"/>
-      <c r="I85" s="840"/>
-      <c r="J85" s="840"/>
-      <c r="K85" s="840"/>
-      <c r="L85" s="840"/>
-      <c r="M85" s="840"/>
-      <c r="N85" s="840"/>
+      <c r="B85" s="887"/>
+      <c r="C85" s="887"/>
+      <c r="D85" s="887"/>
+      <c r="E85" s="887"/>
+      <c r="F85" s="887"/>
+      <c r="G85" s="887"/>
+      <c r="H85" s="887"/>
+      <c r="I85" s="887"/>
+      <c r="J85" s="887"/>
+      <c r="K85" s="887"/>
+      <c r="L85" s="887"/>
+      <c r="M85" s="887"/>
+      <c r="N85" s="887"/>
       <c r="AA85" s="513"/>
       <c r="AB85" s="513"/>
       <c r="AC85" s="513"/>
       <c r="AD85" s="513"/>
     </row>
-    <row r="86" spans="1:30" ht="5.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:30" ht="5.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="427"/>
       <c r="B86" s="427"/>
       <c r="C86" s="427"/>
@@ -26096,7 +26096,7 @@
       <c r="AC86" s="513"/>
       <c r="AD86" s="513"/>
     </row>
-    <row r="87" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="521" t="s">
         <v>387</v>
       </c>
@@ -26118,7 +26118,7 @@
       <c r="AC87" s="513"/>
       <c r="AD87" s="513"/>
     </row>
-    <row r="88" spans="1:30" ht="43.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:30" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="427"/>
       <c r="H88" s="305"/>
       <c r="I88" s="305"/>
@@ -26134,7 +26134,7 @@
       <c r="AC88" s="513"/>
       <c r="AD88" s="513"/>
     </row>
-    <row r="89" spans="1:30" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:30" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="155"/>
       <c r="B89" s="155"/>
       <c r="C89" s="155"/>
@@ -26155,7 +26155,7 @@
       <c r="AC89" s="513"/>
       <c r="AD89" s="513"/>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="155"/>
       <c r="B90" s="155"/>
       <c r="C90" s="155"/>
@@ -26176,7 +26176,7 @@
       <c r="AC90" s="513"/>
       <c r="AD90" s="513"/>
     </row>
-    <row r="91" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="305"/>
       <c r="B91" s="305"/>
       <c r="C91" s="305"/>
@@ -26192,7 +26192,7 @@
       <c r="M91" s="305"/>
       <c r="N91" s="305"/>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="305"/>
       <c r="B92" s="305"/>
       <c r="C92" s="305"/>
@@ -26208,7 +26208,7 @@
       <c r="M92" s="305"/>
       <c r="N92" s="305"/>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="319" t="s">
         <v>230</v>
       </c>
@@ -26226,7 +26226,7 @@
       <c r="M93" s="305"/>
       <c r="N93" s="305"/>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="319" t="s">
         <v>573</v>
       </c>
@@ -26254,6 +26254,57 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="67">
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A15:N15"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="Q11:V11"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="Q41:T42"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="Q45:Q47"/>
+    <mergeCell ref="R45:R47"/>
     <mergeCell ref="L75:N75"/>
     <mergeCell ref="E27:H27"/>
     <mergeCell ref="I27:J27"/>
@@ -26270,57 +26321,6 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I71:K71"/>
     <mergeCell ref="I37:J37"/>
-    <mergeCell ref="Q41:T42"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="Q45:Q47"/>
-    <mergeCell ref="R45:R47"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="Q5:V5"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="Q16:V16"/>
-    <mergeCell ref="Q11:V11"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="A85:N85"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="A83:N83"/>
-    <mergeCell ref="A81:N81"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A84:N84"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="AA24">
@@ -26378,20 +26378,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K231"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.140625" style="276" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="276" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="276" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="276"/>
-    <col min="5" max="8" width="11.5703125" style="276" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" style="276" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" style="276" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="276" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="276"/>
+    <col min="1" max="1" width="24.109375" style="276" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="276" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="276" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="276"/>
+    <col min="5" max="8" width="11.5546875" style="276" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" style="276" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="276" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="276" customWidth="1"/>
+    <col min="12" max="16384" width="11.44140625" style="276"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="906"/>
       <c r="B1" s="907"/>
       <c r="C1" s="912" t="s">
@@ -26410,7 +26410,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="908"/>
       <c r="B2" s="909"/>
       <c r="C2" s="915"/>
@@ -26427,7 +26427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="908"/>
       <c r="B3" s="909"/>
       <c r="C3" s="915"/>
@@ -26444,7 +26444,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="910"/>
       <c r="B4" s="911"/>
       <c r="C4" s="918"/>
@@ -26461,7 +26461,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="343" t="s">
         <v>314</v>
       </c>
@@ -26478,7 +26478,7 @@
       <c r="J6" s="278"/>
       <c r="K6" s="277"/>
     </row>
-    <row r="7" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="343" t="s">
         <v>313</v>
       </c>
@@ -26495,7 +26495,7 @@
       <c r="J7" s="278"/>
       <c r="K7" s="277"/>
     </row>
-    <row r="8" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="343" t="s">
         <v>312</v>
       </c>
@@ -26512,7 +26512,7 @@
       <c r="J8" s="278"/>
       <c r="K8" s="277"/>
     </row>
-    <row r="9" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="346" t="s">
         <v>566</v>
       </c>
@@ -26529,7 +26529,7 @@
       <c r="J9" s="278"/>
       <c r="K9" s="277"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="143" t="s">
         <v>567</v>
       </c>
@@ -26541,7 +26541,7 @@
       <c r="G11" s="401"/>
       <c r="H11" s="401"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="143"/>
       <c r="B12" s="401"/>
       <c r="C12" s="401"/>
@@ -26551,7 +26551,7 @@
       <c r="G12" s="401"/>
       <c r="H12" s="401"/>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="615" t="s">
         <v>376</v>
       </c>
@@ -26565,7 +26565,7 @@
       <c r="G13" s="401"/>
       <c r="H13" s="401"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="613"/>
       <c r="B14" s="612"/>
       <c r="C14" s="613"/>
@@ -26575,7 +26575,7 @@
       <c r="G14" s="401"/>
       <c r="H14" s="401"/>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="614" t="s">
         <v>444</v>
       </c>
@@ -26587,7 +26587,7 @@
       <c r="G15" s="401"/>
       <c r="H15" s="401"/>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="614" t="s">
         <v>445</v>
       </c>
@@ -26599,7 +26599,7 @@
       <c r="G16" s="595"/>
       <c r="H16" s="401"/>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="614" t="s">
         <v>446</v>
       </c>
@@ -26611,7 +26611,7 @@
       <c r="G17" s="595"/>
       <c r="H17" s="401"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="401"/>
       <c r="B18" s="401"/>
       <c r="C18" s="401"/>
@@ -26621,7 +26621,7 @@
       <c r="G18" s="401"/>
       <c r="H18" s="401"/>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="615" t="s">
         <v>378</v>
       </c>
@@ -26633,7 +26633,7 @@
       <c r="G19" s="595"/>
       <c r="H19" s="401"/>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="401"/>
       <c r="B20" s="401"/>
       <c r="C20" s="401"/>
@@ -26643,7 +26643,7 @@
       <c r="G20" s="401"/>
       <c r="H20" s="401"/>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="616" t="s">
         <v>379</v>
       </c>
@@ -26655,7 +26655,7 @@
       <c r="G21" s="595"/>
       <c r="H21" s="401"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="616" t="s">
         <v>380</v>
       </c>
@@ -26667,7 +26667,7 @@
       <c r="G22" s="595"/>
       <c r="H22" s="401"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="401"/>
       <c r="B23" s="401"/>
       <c r="C23" s="401"/>
@@ -26677,7 +26677,7 @@
       <c r="G23" s="401"/>
       <c r="H23" s="401"/>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="143" t="s">
         <v>381</v>
       </c>
@@ -26689,7 +26689,7 @@
       <c r="G24" s="401"/>
       <c r="H24" s="401"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="401"/>
       <c r="B25" s="401"/>
       <c r="C25" s="401"/>
@@ -26699,7 +26699,7 @@
       <c r="G25" s="401"/>
       <c r="H25" s="401"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="401"/>
       <c r="B26" s="401"/>
       <c r="C26" s="401"/>
@@ -26709,7 +26709,7 @@
       <c r="G26" s="401"/>
       <c r="H26" s="401"/>
     </row>
-    <row r="27" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="401"/>
       <c r="B27" s="401"/>
       <c r="C27" s="401"/>
@@ -26719,7 +26719,7 @@
       <c r="G27" s="401"/>
       <c r="H27" s="401"/>
     </row>
-    <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="401"/>
       <c r="B28" s="401"/>
       <c r="C28" s="401"/>
@@ -26729,7 +26729,7 @@
       <c r="G28" s="401"/>
       <c r="H28" s="401"/>
     </row>
-    <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="401"/>
       <c r="B29" s="401"/>
       <c r="C29" s="401"/>
@@ -26739,7 +26739,7 @@
       <c r="G29" s="401"/>
       <c r="H29" s="401"/>
     </row>
-    <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="401"/>
       <c r="B30" s="401"/>
       <c r="C30" s="401"/>
@@ -26749,7 +26749,7 @@
       <c r="G30" s="401"/>
       <c r="H30" s="401"/>
     </row>
-    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="401"/>
       <c r="B31" s="401"/>
       <c r="C31" s="401"/>
@@ -26759,7 +26759,7 @@
       <c r="G31" s="401"/>
       <c r="H31" s="401"/>
     </row>
-    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="401"/>
       <c r="B32" s="401"/>
       <c r="C32" s="401"/>
@@ -26769,7 +26769,7 @@
       <c r="G32" s="401"/>
       <c r="H32" s="401"/>
     </row>
-    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="903" t="s">
         <v>309</v>
       </c>
@@ -26784,7 +26784,7 @@
       <c r="J34" s="904"/>
       <c r="K34" s="905"/>
     </row>
-    <row r="35" spans="1:11" ht="39.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="38.4" x14ac:dyDescent="0.25">
       <c r="A35" s="347" t="s">
         <v>308</v>
       </c>
@@ -26814,7 +26814,7 @@
       </c>
       <c r="J35" s="344"/>
     </row>
-    <row r="36" spans="1:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="344"/>
       <c r="B36" s="344"/>
       <c r="C36" s="344"/>
@@ -26826,7 +26826,7 @@
       <c r="I36" s="344"/>
       <c r="J36" s="344"/>
     </row>
-    <row r="37" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="378" t="s">
         <v>302</v>
       </c>
@@ -26849,7 +26849,7 @@
       </c>
       <c r="J37" s="344"/>
     </row>
-    <row r="38" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="453" t="s">
         <v>402</v>
       </c>
@@ -26877,7 +26877,7 @@
       <c r="I38" s="345"/>
       <c r="J38" s="344"/>
     </row>
-    <row r="39" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="354" t="s">
         <v>261</v>
       </c>
@@ -26899,7 +26899,7 @@
       <c r="I39" s="344"/>
       <c r="J39" s="344"/>
     </row>
-    <row r="40" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="354" t="s">
         <v>259</v>
       </c>
@@ -26931,7 +26931,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="354" t="s">
         <v>257</v>
       </c>
@@ -26963,7 +26963,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="348" t="s">
         <v>263</v>
       </c>
@@ -27001,7 +27001,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="354" t="s">
         <v>261</v>
       </c>
@@ -27033,7 +27033,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="354" t="s">
         <v>259</v>
       </c>
@@ -27062,7 +27062,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="354" t="s">
         <v>257</v>
       </c>
@@ -27084,7 +27084,7 @@
       <c r="I45" s="455"/>
       <c r="J45" s="456"/>
     </row>
-    <row r="46" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="348" t="s">
         <v>301</v>
       </c>
@@ -27108,7 +27108,7 @@
       </c>
       <c r="H46" s="344"/>
     </row>
-    <row r="47" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="354" t="s">
         <v>259</v>
       </c>
@@ -27128,7 +27128,7 @@
       <c r="G47" s="364"/>
       <c r="H47" s="345"/>
     </row>
-    <row r="48" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="367" t="s">
         <v>300</v>
       </c>
@@ -27155,8 +27155,8 @@
       <c r="I48" s="344"/>
       <c r="J48" s="344"/>
     </row>
-    <row r="49" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="378" t="s">
         <v>299</v>
       </c>
@@ -27179,7 +27179,7 @@
       </c>
       <c r="J50" s="344"/>
     </row>
-    <row r="51" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="450" t="s">
         <v>403</v>
       </c>
@@ -27207,7 +27207,7 @@
       <c r="I51" s="345"/>
       <c r="J51" s="344"/>
     </row>
-    <row r="52" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="354" t="s">
         <v>261</v>
       </c>
@@ -27229,7 +27229,7 @@
       <c r="I52" s="344"/>
       <c r="J52" s="344"/>
     </row>
-    <row r="53" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="354" t="s">
         <v>259</v>
       </c>
@@ -27261,7 +27261,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="354" t="s">
         <v>257</v>
       </c>
@@ -27293,7 +27293,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="348" t="s">
         <v>263</v>
       </c>
@@ -27331,7 +27331,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="354" t="s">
         <v>261</v>
       </c>
@@ -27363,7 +27363,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="354" t="s">
         <v>259</v>
       </c>
@@ -27392,7 +27392,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="354" t="s">
         <v>257</v>
       </c>
@@ -27414,7 +27414,7 @@
       <c r="I58" s="455"/>
       <c r="J58" s="456"/>
     </row>
-    <row r="59" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="348" t="s">
         <v>298</v>
       </c>
@@ -27438,7 +27438,7 @@
       </c>
       <c r="H59" s="344"/>
     </row>
-    <row r="60" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="354" t="s">
         <v>259</v>
       </c>
@@ -27458,7 +27458,7 @@
       <c r="G60" s="364"/>
       <c r="H60" s="345"/>
     </row>
-    <row r="61" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="367" t="s">
         <v>297</v>
       </c>
@@ -27485,8 +27485,8 @@
       <c r="I61" s="344"/>
       <c r="J61" s="344"/>
     </row>
-    <row r="62" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="378" t="s">
         <v>296</v>
       </c>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="J63" s="344"/>
     </row>
-    <row r="64" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="454" t="s">
         <v>404</v>
       </c>
@@ -27537,7 +27537,7 @@
       <c r="I64" s="345"/>
       <c r="J64" s="344"/>
     </row>
-    <row r="65" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="354" t="s">
         <v>261</v>
       </c>
@@ -27559,7 +27559,7 @@
       <c r="I65" s="344"/>
       <c r="J65" s="344"/>
     </row>
-    <row r="66" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="354" t="s">
         <v>259</v>
       </c>
@@ -27591,7 +27591,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="354" t="s">
         <v>257</v>
       </c>
@@ -27623,7 +27623,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="348" t="s">
         <v>263</v>
       </c>
@@ -27661,7 +27661,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="354" t="s">
         <v>261</v>
       </c>
@@ -27693,7 +27693,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="354" t="s">
         <v>259</v>
       </c>
@@ -27722,7 +27722,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="354" t="s">
         <v>257</v>
       </c>
@@ -27744,7 +27744,7 @@
       <c r="I71" s="455"/>
       <c r="J71" s="456"/>
     </row>
-    <row r="72" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="348" t="s">
         <v>295</v>
       </c>
@@ -27768,7 +27768,7 @@
       </c>
       <c r="H72" s="344"/>
     </row>
-    <row r="73" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="354" t="s">
         <v>259</v>
       </c>
@@ -27788,7 +27788,7 @@
       <c r="G73" s="364"/>
       <c r="H73" s="345"/>
     </row>
-    <row r="74" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="367" t="s">
         <v>294</v>
       </c>
@@ -27815,8 +27815,8 @@
       <c r="I74" s="344"/>
       <c r="J74" s="344"/>
     </row>
-    <row r="75" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="378" t="s">
         <v>293</v>
       </c>
@@ -27839,7 +27839,7 @@
       </c>
       <c r="J76" s="344"/>
     </row>
-    <row r="77" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="454" t="s">
         <v>405</v>
       </c>
@@ -27867,7 +27867,7 @@
       <c r="I77" s="345"/>
       <c r="J77" s="344"/>
     </row>
-    <row r="78" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="354" t="s">
         <v>261</v>
       </c>
@@ -27889,7 +27889,7 @@
       <c r="I78" s="344"/>
       <c r="J78" s="344"/>
     </row>
-    <row r="79" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="354" t="s">
         <v>259</v>
       </c>
@@ -27921,7 +27921,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="354" t="s">
         <v>257</v>
       </c>
@@ -27953,7 +27953,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="348" t="s">
         <v>263</v>
       </c>
@@ -27991,7 +27991,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="354" t="s">
         <v>261</v>
       </c>
@@ -28023,7 +28023,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="354" t="s">
         <v>259</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="354" t="s">
         <v>257</v>
       </c>
@@ -28074,7 +28074,7 @@
       <c r="I84" s="455"/>
       <c r="J84" s="456"/>
     </row>
-    <row r="85" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="348" t="s">
         <v>292</v>
       </c>
@@ -28098,7 +28098,7 @@
       </c>
       <c r="H85" s="344"/>
     </row>
-    <row r="86" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="354" t="s">
         <v>259</v>
       </c>
@@ -28118,7 +28118,7 @@
       <c r="G86" s="364"/>
       <c r="H86" s="345"/>
     </row>
-    <row r="87" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="367" t="s">
         <v>291</v>
       </c>
@@ -28145,8 +28145,8 @@
       <c r="I87" s="344"/>
       <c r="J87" s="344"/>
     </row>
-    <row r="88" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="378" t="s">
         <v>290</v>
       </c>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="J89" s="344"/>
     </row>
-    <row r="90" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="454" t="s">
         <v>406</v>
       </c>
@@ -28197,7 +28197,7 @@
       <c r="I90" s="345"/>
       <c r="J90" s="344"/>
     </row>
-    <row r="91" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="354" t="s">
         <v>261</v>
       </c>
@@ -28219,7 +28219,7 @@
       <c r="I91" s="344"/>
       <c r="J91" s="344"/>
     </row>
-    <row r="92" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="354" t="s">
         <v>259</v>
       </c>
@@ -28251,7 +28251,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="354" t="s">
         <v>257</v>
       </c>
@@ -28283,7 +28283,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="348" t="s">
         <v>263</v>
       </c>
@@ -28321,7 +28321,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="354" t="s">
         <v>261</v>
       </c>
@@ -28353,7 +28353,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="354" t="s">
         <v>259</v>
       </c>
@@ -28382,7 +28382,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="354" t="s">
         <v>257</v>
       </c>
@@ -28404,7 +28404,7 @@
       <c r="I97" s="455"/>
       <c r="J97" s="456"/>
     </row>
-    <row r="98" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="348" t="s">
         <v>289</v>
       </c>
@@ -28428,7 +28428,7 @@
       </c>
       <c r="H98" s="344"/>
     </row>
-    <row r="99" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="354" t="s">
         <v>259</v>
       </c>
@@ -28448,7 +28448,7 @@
       <c r="G99" s="364"/>
       <c r="H99" s="345"/>
     </row>
-    <row r="100" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="367" t="s">
         <v>288</v>
       </c>
@@ -28475,8 +28475,8 @@
       <c r="I100" s="344"/>
       <c r="J100" s="344"/>
     </row>
-    <row r="101" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="378" t="s">
         <v>287</v>
       </c>
@@ -28499,7 +28499,7 @@
       </c>
       <c r="J102" s="344"/>
     </row>
-    <row r="103" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="454" t="s">
         <v>407</v>
       </c>
@@ -28527,7 +28527,7 @@
       <c r="I103" s="345"/>
       <c r="J103" s="344"/>
     </row>
-    <row r="104" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="354" t="s">
         <v>261</v>
       </c>
@@ -28549,7 +28549,7 @@
       <c r="I104" s="344"/>
       <c r="J104" s="344"/>
     </row>
-    <row r="105" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="354" t="s">
         <v>259</v>
       </c>
@@ -28581,7 +28581,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="354" t="s">
         <v>257</v>
       </c>
@@ -28613,7 +28613,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="348" t="s">
         <v>263</v>
       </c>
@@ -28651,7 +28651,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="354" t="s">
         <v>261</v>
       </c>
@@ -28683,7 +28683,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="354" t="s">
         <v>259</v>
       </c>
@@ -28712,7 +28712,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="354" t="s">
         <v>257</v>
       </c>
@@ -28734,7 +28734,7 @@
       <c r="I110" s="455"/>
       <c r="J110" s="456"/>
     </row>
-    <row r="111" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="348" t="s">
         <v>286</v>
       </c>
@@ -28758,7 +28758,7 @@
       </c>
       <c r="H111" s="344"/>
     </row>
-    <row r="112" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="354" t="s">
         <v>259</v>
       </c>
@@ -28778,7 +28778,7 @@
       <c r="G112" s="364"/>
       <c r="H112" s="345"/>
     </row>
-    <row r="113" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="367" t="s">
         <v>285</v>
       </c>
@@ -28805,8 +28805,8 @@
       <c r="I113" s="344"/>
       <c r="J113" s="344"/>
     </row>
-    <row r="114" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="115" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="378" t="s">
         <v>284</v>
       </c>
@@ -28829,7 +28829,7 @@
       </c>
       <c r="J115" s="344"/>
     </row>
-    <row r="116" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="454" t="s">
         <v>408</v>
       </c>
@@ -28857,7 +28857,7 @@
       <c r="I116" s="345"/>
       <c r="J116" s="344"/>
     </row>
-    <row r="117" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="354" t="s">
         <v>261</v>
       </c>
@@ -28879,7 +28879,7 @@
       <c r="I117" s="344"/>
       <c r="J117" s="344"/>
     </row>
-    <row r="118" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="354" t="s">
         <v>259</v>
       </c>
@@ -28911,7 +28911,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="354" t="s">
         <v>257</v>
       </c>
@@ -28943,7 +28943,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="348" t="s">
         <v>263</v>
       </c>
@@ -28981,7 +28981,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="354" t="s">
         <v>261</v>
       </c>
@@ -29013,7 +29013,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="354" t="s">
         <v>259</v>
       </c>
@@ -29042,7 +29042,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="354" t="s">
         <v>257</v>
       </c>
@@ -29064,7 +29064,7 @@
       <c r="I123" s="455"/>
       <c r="J123" s="456"/>
     </row>
-    <row r="124" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="348" t="s">
         <v>283</v>
       </c>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="H124" s="344"/>
     </row>
-    <row r="125" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="354" t="s">
         <v>259</v>
       </c>
@@ -29108,7 +29108,7 @@
       <c r="G125" s="364"/>
       <c r="H125" s="345"/>
     </row>
-    <row r="126" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="367" t="s">
         <v>282</v>
       </c>
@@ -29135,13 +29135,13 @@
       <c r="I126" s="344"/>
       <c r="J126" s="344"/>
     </row>
-    <row r="127" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="285" t="str">
         <f>+A.Granul!R3</f>
         <v>-</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="378" t="s">
         <v>281</v>
       </c>
@@ -29164,7 +29164,7 @@
       </c>
       <c r="J128" s="344"/>
     </row>
-    <row r="129" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -29191,7 +29191,7 @@
       <c r="I129" s="464"/>
       <c r="J129" s="344"/>
     </row>
-    <row r="130" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="454" t="s">
         <v>409</v>
       </c>
@@ -29219,7 +29219,7 @@
       <c r="I130" s="345"/>
       <c r="J130" s="344"/>
     </row>
-    <row r="131" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="354" t="s">
         <v>261</v>
       </c>
@@ -29241,7 +29241,7 @@
       <c r="I131" s="344"/>
       <c r="J131" s="344"/>
     </row>
-    <row r="132" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="354" t="s">
         <v>259</v>
       </c>
@@ -29273,7 +29273,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="354" t="s">
         <v>257</v>
       </c>
@@ -29305,7 +29305,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="348" t="s">
         <v>263</v>
       </c>
@@ -29343,7 +29343,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="354" t="s">
         <v>261</v>
       </c>
@@ -29375,7 +29375,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="354" t="s">
         <v>259</v>
       </c>
@@ -29404,7 +29404,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="354" t="s">
         <v>257</v>
       </c>
@@ -29426,7 +29426,7 @@
       <c r="I137" s="455"/>
       <c r="J137" s="456"/>
     </row>
-    <row r="138" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="348" t="s">
         <v>280</v>
       </c>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="H138" s="344"/>
     </row>
-    <row r="139" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="354" t="s">
         <v>259</v>
       </c>
@@ -29470,7 +29470,7 @@
       <c r="G139" s="364"/>
       <c r="H139" s="345"/>
     </row>
-    <row r="140" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="367" t="s">
         <v>279</v>
       </c>
@@ -29497,8 +29497,8 @@
       <c r="I140" s="344"/>
       <c r="J140" s="344"/>
     </row>
-    <row r="141" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="142" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="378" t="s">
         <v>278</v>
       </c>
@@ -29521,7 +29521,7 @@
       </c>
       <c r="J142" s="344"/>
     </row>
-    <row r="143" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -29548,7 +29548,7 @@
       <c r="I143" s="464"/>
       <c r="J143" s="344"/>
     </row>
-    <row r="144" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="454" t="s">
         <v>410</v>
       </c>
@@ -29576,7 +29576,7 @@
       <c r="I144" s="345"/>
       <c r="J144" s="344"/>
     </row>
-    <row r="145" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="354" t="s">
         <v>261</v>
       </c>
@@ -29598,7 +29598,7 @@
       <c r="I145" s="344"/>
       <c r="J145" s="344"/>
     </row>
-    <row r="146" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="354" t="s">
         <v>259</v>
       </c>
@@ -29630,7 +29630,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="354" t="s">
         <v>257</v>
       </c>
@@ -29662,7 +29662,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="348" t="s">
         <v>263</v>
       </c>
@@ -29700,7 +29700,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="354" t="s">
         <v>261</v>
       </c>
@@ -29732,7 +29732,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="354" t="s">
         <v>259</v>
       </c>
@@ -29761,7 +29761,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="354" t="s">
         <v>257</v>
       </c>
@@ -29783,7 +29783,7 @@
       <c r="I151" s="455"/>
       <c r="J151" s="456"/>
     </row>
-    <row r="152" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="348" t="s">
         <v>277</v>
       </c>
@@ -29807,7 +29807,7 @@
       </c>
       <c r="H152" s="344"/>
     </row>
-    <row r="153" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="354" t="s">
         <v>259</v>
       </c>
@@ -29827,7 +29827,7 @@
       <c r="G153" s="364"/>
       <c r="H153" s="345"/>
     </row>
-    <row r="154" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="367" t="s">
         <v>276</v>
       </c>
@@ -29854,8 +29854,8 @@
       <c r="I154" s="344"/>
       <c r="J154" s="344"/>
     </row>
-    <row r="155" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="156" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="378" t="s">
         <v>275</v>
       </c>
@@ -29878,7 +29878,7 @@
       </c>
       <c r="J156" s="344"/>
     </row>
-    <row r="157" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -29905,7 +29905,7 @@
       <c r="I157" s="464"/>
       <c r="J157" s="344"/>
     </row>
-    <row r="158" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="454" t="s">
         <v>411</v>
       </c>
@@ -29933,7 +29933,7 @@
       <c r="I158" s="345"/>
       <c r="J158" s="344"/>
     </row>
-    <row r="159" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="354" t="s">
         <v>261</v>
       </c>
@@ -29955,7 +29955,7 @@
       <c r="I159" s="344"/>
       <c r="J159" s="344"/>
     </row>
-    <row r="160" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="354" t="s">
         <v>259</v>
       </c>
@@ -29987,7 +29987,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="354" t="s">
         <v>257</v>
       </c>
@@ -30019,7 +30019,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="348" t="s">
         <v>263</v>
       </c>
@@ -30057,7 +30057,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="354" t="s">
         <v>261</v>
       </c>
@@ -30089,7 +30089,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="354" t="s">
         <v>259</v>
       </c>
@@ -30118,7 +30118,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="354" t="s">
         <v>257</v>
       </c>
@@ -30140,7 +30140,7 @@
       <c r="I165" s="455"/>
       <c r="J165" s="456"/>
     </row>
-    <row r="166" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="348" t="s">
         <v>274</v>
       </c>
@@ -30164,7 +30164,7 @@
       </c>
       <c r="H166" s="344"/>
     </row>
-    <row r="167" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="354" t="s">
         <v>259</v>
       </c>
@@ -30184,7 +30184,7 @@
       <c r="G167" s="364"/>
       <c r="H167" s="345"/>
     </row>
-    <row r="168" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="367" t="s">
         <v>273</v>
       </c>
@@ -30211,8 +30211,8 @@
       <c r="I168" s="344"/>
       <c r="J168" s="344"/>
     </row>
-    <row r="169" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="170" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="378" t="s">
         <v>272</v>
       </c>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="J170" s="344"/>
     </row>
-    <row r="171" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -30262,7 +30262,7 @@
       <c r="I171" s="464"/>
       <c r="J171" s="344"/>
     </row>
-    <row r="172" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="454" t="s">
         <v>412</v>
       </c>
@@ -30290,7 +30290,7 @@
       <c r="I172" s="345"/>
       <c r="J172" s="344"/>
     </row>
-    <row r="173" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="354" t="s">
         <v>261</v>
       </c>
@@ -30312,7 +30312,7 @@
       <c r="I173" s="344"/>
       <c r="J173" s="344"/>
     </row>
-    <row r="174" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="354" t="s">
         <v>259</v>
       </c>
@@ -30344,7 +30344,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="354" t="s">
         <v>257</v>
       </c>
@@ -30376,7 +30376,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="348" t="s">
         <v>263</v>
       </c>
@@ -30414,7 +30414,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="354" t="s">
         <v>261</v>
       </c>
@@ -30446,7 +30446,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="354" t="s">
         <v>259</v>
       </c>
@@ -30475,7 +30475,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="354" t="s">
         <v>257</v>
       </c>
@@ -30497,7 +30497,7 @@
       <c r="I179" s="455"/>
       <c r="J179" s="456"/>
     </row>
-    <row r="180" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="348" t="s">
         <v>271</v>
       </c>
@@ -30521,7 +30521,7 @@
       </c>
       <c r="H180" s="344"/>
     </row>
-    <row r="181" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="354" t="s">
         <v>259</v>
       </c>
@@ -30541,7 +30541,7 @@
       <c r="G181" s="364"/>
       <c r="H181" s="345"/>
     </row>
-    <row r="182" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="367" t="s">
         <v>270</v>
       </c>
@@ -30568,8 +30568,8 @@
       <c r="I182" s="344"/>
       <c r="J182" s="344"/>
     </row>
-    <row r="183" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="184" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="378" t="s">
         <v>347</v>
       </c>
@@ -30592,7 +30592,7 @@
       </c>
       <c r="J184" s="344"/>
     </row>
-    <row r="185" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -30619,7 +30619,7 @@
       <c r="I185" s="464"/>
       <c r="J185" s="344"/>
     </row>
-    <row r="186" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="454" t="s">
         <v>413</v>
       </c>
@@ -30647,7 +30647,7 @@
       <c r="I186" s="345"/>
       <c r="J186" s="344"/>
     </row>
-    <row r="187" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="354" t="s">
         <v>261</v>
       </c>
@@ -30669,7 +30669,7 @@
       <c r="I187" s="344"/>
       <c r="J187" s="344"/>
     </row>
-    <row r="188" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="354" t="s">
         <v>259</v>
       </c>
@@ -30701,7 +30701,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="354" t="s">
         <v>257</v>
       </c>
@@ -30733,7 +30733,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="348" t="s">
         <v>263</v>
       </c>
@@ -30771,7 +30771,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="354" t="s">
         <v>261</v>
       </c>
@@ -30803,7 +30803,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="354" t="s">
         <v>259</v>
       </c>
@@ -30832,7 +30832,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="354" t="s">
         <v>257</v>
       </c>
@@ -30854,7 +30854,7 @@
       <c r="I193" s="455"/>
       <c r="J193" s="456"/>
     </row>
-    <row r="194" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="348" t="s">
         <v>348</v>
       </c>
@@ -30878,7 +30878,7 @@
       </c>
       <c r="H194" s="344"/>
     </row>
-    <row r="195" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="354" t="s">
         <v>259</v>
       </c>
@@ -30898,7 +30898,7 @@
       <c r="G195" s="364"/>
       <c r="H195" s="345"/>
     </row>
-    <row r="196" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="367" t="s">
         <v>349</v>
       </c>
@@ -30925,8 +30925,8 @@
       <c r="I196" s="344"/>
       <c r="J196" s="344"/>
     </row>
-    <row r="197" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="198" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="378" t="s">
         <v>269</v>
       </c>
@@ -30949,7 +30949,7 @@
       </c>
       <c r="J198" s="344"/>
     </row>
-    <row r="199" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -30976,7 +30976,7 @@
       <c r="I199" s="464"/>
       <c r="J199" s="344"/>
     </row>
-    <row r="200" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="373" t="s">
         <v>268</v>
       </c>
@@ -31004,7 +31004,7 @@
       <c r="I200" s="345"/>
       <c r="J200" s="344"/>
     </row>
-    <row r="201" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="354" t="s">
         <v>261</v>
       </c>
@@ -31026,7 +31026,7 @@
       <c r="I201" s="344"/>
       <c r="J201" s="344"/>
     </row>
-    <row r="202" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="354" t="s">
         <v>259</v>
       </c>
@@ -31058,7 +31058,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="354" t="s">
         <v>257</v>
       </c>
@@ -31090,7 +31090,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="348" t="s">
         <v>263</v>
       </c>
@@ -31128,7 +31128,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="354" t="s">
         <v>261</v>
       </c>
@@ -31160,7 +31160,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="354" t="s">
         <v>259</v>
       </c>
@@ -31189,7 +31189,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="354" t="s">
         <v>257</v>
       </c>
@@ -31211,7 +31211,7 @@
       <c r="I207" s="455"/>
       <c r="J207" s="456"/>
     </row>
-    <row r="208" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="348" t="s">
         <v>267</v>
       </c>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="H208" s="344"/>
     </row>
-    <row r="209" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="354" t="s">
         <v>259</v>
       </c>
@@ -31255,7 +31255,7 @@
       <c r="G209" s="364"/>
       <c r="H209" s="345"/>
     </row>
-    <row r="210" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="367" t="s">
         <v>266</v>
       </c>
@@ -31282,8 +31282,8 @@
       <c r="I210" s="344"/>
       <c r="J210" s="344"/>
     </row>
-    <row r="211" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="212" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="212" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="378" t="s">
         <v>265</v>
       </c>
@@ -31306,7 +31306,7 @@
       </c>
       <c r="J212" s="344"/>
     </row>
-    <row r="213" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="465" t="str">
         <f>IF($A$127="Fraccionada","% pasa tamiz No 4","")</f>
         <v/>
@@ -31333,7 +31333,7 @@
       <c r="I213" s="464"/>
       <c r="J213" s="344"/>
     </row>
-    <row r="214" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="454" t="s">
         <v>414</v>
       </c>
@@ -31361,7 +31361,7 @@
       <c r="I214" s="345"/>
       <c r="J214" s="344"/>
     </row>
-    <row r="215" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="354" t="s">
         <v>261</v>
       </c>
@@ -31383,7 +31383,7 @@
       <c r="I215" s="344"/>
       <c r="J215" s="344"/>
     </row>
-    <row r="216" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="354" t="s">
         <v>259</v>
       </c>
@@ -31415,7 +31415,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="354" t="s">
         <v>257</v>
       </c>
@@ -31447,7 +31447,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="348" t="s">
         <v>263</v>
       </c>
@@ -31485,7 +31485,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="354" t="s">
         <v>261</v>
       </c>
@@ -31517,7 +31517,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="354" t="s">
         <v>259</v>
       </c>
@@ -31546,7 +31546,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="354" t="s">
         <v>257</v>
       </c>
@@ -31568,7 +31568,7 @@
       <c r="I221" s="455"/>
       <c r="J221" s="456"/>
     </row>
-    <row r="222" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="348" t="s">
         <v>264</v>
       </c>
@@ -31592,7 +31592,7 @@
       </c>
       <c r="H222" s="344"/>
     </row>
-    <row r="223" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="354" t="s">
         <v>259</v>
       </c>
@@ -31612,7 +31612,7 @@
       <c r="G223" s="364"/>
       <c r="H223" s="345"/>
     </row>
-    <row r="224" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="367" t="s">
         <v>255</v>
       </c>
@@ -31639,7 +31639,7 @@
       <c r="I224" s="344"/>
       <c r="J224" s="344"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="771" t="s">
         <v>560</v>
       </c>
@@ -31657,7 +31657,7 @@
       </c>
       <c r="H227" s="925"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="401"/>
       <c r="B228" s="401"/>
       <c r="C228" s="401"/>
@@ -31667,7 +31667,7 @@
       <c r="G228" s="401"/>
       <c r="H228" s="401"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="773" t="s">
         <v>564</v>
       </c>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="H229" s="901"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="401"/>
       <c r="B230" s="401"/>
       <c r="C230" s="401"/>
@@ -31695,7 +31695,7 @@
       <c r="G230" s="401"/>
       <c r="H230" s="401"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B231" s="384"/>
     </row>
   </sheetData>
@@ -31720,27 +31720,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:AG63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="276"/>
-    <col min="2" max="2" width="11.42578125" style="276" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="276"/>
+    <col min="2" max="2" width="11.44140625" style="276" customWidth="1"/>
     <col min="3" max="3" width="12" style="276" customWidth="1"/>
-    <col min="4" max="8" width="11.42578125" style="276"/>
-    <col min="9" max="9" width="11.85546875" style="276" customWidth="1"/>
-    <col min="10" max="30" width="11.42578125" style="276"/>
-    <col min="31" max="32" width="9.42578125" style="276" customWidth="1"/>
-    <col min="33" max="39" width="12.28515625" style="276" customWidth="1"/>
-    <col min="40" max="40" width="4.140625" style="276" customWidth="1"/>
-    <col min="41" max="49" width="12.28515625" style="276" customWidth="1"/>
-    <col min="50" max="16384" width="11.42578125" style="276"/>
+    <col min="4" max="8" width="11.44140625" style="276"/>
+    <col min="9" max="9" width="11.88671875" style="276" customWidth="1"/>
+    <col min="10" max="30" width="11.44140625" style="276"/>
+    <col min="31" max="32" width="9.44140625" style="276" customWidth="1"/>
+    <col min="33" max="39" width="12.33203125" style="276" customWidth="1"/>
+    <col min="40" max="40" width="4.109375" style="276" customWidth="1"/>
+    <col min="41" max="49" width="12.33203125" style="276" customWidth="1"/>
+    <col min="50" max="16384" width="11.44140625" style="276"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C2" s="397" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="397"/>
       <c r="C6" s="397"/>
       <c r="D6" s="397"/>
@@ -31748,7 +31748,7 @@
       <c r="F6" s="397"/>
       <c r="G6" s="397"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="765" t="s">
         <v>553</v>
       </c>
@@ -31761,7 +31761,7 @@
       <c r="F7" s="328"/>
       <c r="G7" s="328"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="766" t="s">
         <v>343</v>
       </c>
@@ -31776,7 +31776,7 @@
       <c r="F8" s="328"/>
       <c r="G8" s="328"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="766" t="s">
         <v>554</v>
       </c>
@@ -31789,7 +31789,7 @@
       <c r="F9" s="328"/>
       <c r="G9" s="328"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="766" t="s">
         <v>257</v>
       </c>
@@ -31804,7 +31804,7 @@
       <c r="F10" s="328"/>
       <c r="G10" s="328"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="766" t="s">
         <v>557</v>
       </c>
@@ -31817,7 +31817,7 @@
       <c r="F11" s="328"/>
       <c r="G11" s="328"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="766" t="s">
         <v>559</v>
       </c>
@@ -31830,7 +31830,7 @@
       <c r="F12" s="328"/>
       <c r="G12" s="328"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="328"/>
       <c r="B13" s="329"/>
       <c r="C13" s="328"/>
@@ -31839,7 +31839,7 @@
       <c r="F13" s="328"/>
       <c r="G13" s="328"/>
     </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="324" t="s">
         <v>383</v>
       </c>
@@ -31865,7 +31865,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="645"/>
       <c r="B15" s="646"/>
       <c r="C15" s="430"/>
@@ -31875,7 +31875,7 @@
       <c r="G15" s="430"/>
       <c r="H15" s="430"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="645"/>
       <c r="B16" s="646"/>
       <c r="C16" s="430"/>
@@ -31885,7 +31885,7 @@
       <c r="G16" s="430"/>
       <c r="H16" s="430"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="328"/>
       <c r="B17" s="328"/>
       <c r="C17" s="328"/>
@@ -31894,7 +31894,7 @@
       <c r="F17" s="328"/>
       <c r="G17" s="328"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="331"/>
       <c r="B18" s="330" t="s">
         <v>342</v>
@@ -31918,8 +31918,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="398"/>
       <c r="B20" s="412" t="s">
         <v>341</v>
@@ -31938,7 +31938,7 @@
       <c r="N20" s="407"/>
       <c r="O20" s="328"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="399"/>
       <c r="E21" s="328"/>
       <c r="H21" s="403"/>
@@ -31952,7 +31952,7 @@
       <c r="N21" s="400"/>
       <c r="O21" s="328"/>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="399"/>
       <c r="C22" s="331">
         <f t="shared" ref="C22:H22" si="0">+C14</f>
@@ -31986,7 +31986,7 @@
       <c r="N22" s="400"/>
       <c r="O22" s="328"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="399"/>
       <c r="C23" s="325">
         <f t="shared" ref="C23:H23" si="1">C18</f>
@@ -32024,7 +32024,7 @@
       <c r="N23" s="400"/>
       <c r="O23" s="328"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="399"/>
       <c r="E24" s="401"/>
       <c r="H24" s="403"/>
@@ -32032,7 +32032,7 @@
       <c r="N24" s="400"/>
       <c r="O24" s="328"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="399"/>
       <c r="B25" s="411" t="s">
         <v>336</v>
@@ -32051,7 +32051,7 @@
       <c r="N25" s="400"/>
       <c r="O25" s="328"/>
     </row>
-    <row r="26" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="399"/>
       <c r="B26" s="446" t="str">
         <f>+A.Granul!R3</f>
@@ -32070,7 +32070,7 @@
       <c r="I26" s="399"/>
       <c r="N26" s="403"/>
     </row>
-    <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="399"/>
       <c r="B27" s="929" t="s">
         <v>398</v>
@@ -32098,7 +32098,7 @@
       <c r="M27" s="330"/>
       <c r="N27" s="403"/>
     </row>
-    <row r="28" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="399"/>
       <c r="B28" s="930"/>
       <c r="C28" s="932"/>
@@ -32121,7 +32121,7 @@
       </c>
       <c r="N28" s="403"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="399"/>
       <c r="B29" s="432" t="s">
         <v>382</v>
@@ -32155,7 +32155,7 @@
       </c>
       <c r="N29" s="403"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="399"/>
       <c r="B30" s="436" t="s">
         <v>331</v>
@@ -32189,7 +32189,7 @@
       </c>
       <c r="N30" s="403"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="399"/>
       <c r="B31" s="436" t="s">
         <v>330</v>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="N31" s="403"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="399"/>
       <c r="B32" s="436" t="s">
         <v>329</v>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="N32" s="403"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="399"/>
       <c r="B33" s="436" t="s">
         <v>32</v>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="N33" s="403"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="399"/>
       <c r="B34" s="436" t="s">
         <v>33</v>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="N34" s="403"/>
     </row>
-    <row r="35" spans="1:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="399"/>
       <c r="B35" s="438" t="s">
         <v>328</v>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="N35" s="403"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="399"/>
       <c r="B36" s="442" t="s">
         <v>327</v>
@@ -32393,7 +32393,7 @@
       </c>
       <c r="N36" s="403"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="399"/>
       <c r="B37" s="436" t="s">
         <v>326</v>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="N37" s="403"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="399"/>
       <c r="B38" s="436" t="s">
         <v>325</v>
@@ -32461,7 +32461,7 @@
       </c>
       <c r="N38" s="403"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="399"/>
       <c r="B39" s="436" t="s">
         <v>324</v>
@@ -32495,7 +32495,7 @@
       </c>
       <c r="N39" s="403"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="399"/>
       <c r="B40" s="436" t="s">
         <v>346</v>
@@ -32529,7 +32529,7 @@
       </c>
       <c r="N40" s="403"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="399"/>
       <c r="B41" s="436" t="s">
         <v>323</v>
@@ -32563,7 +32563,7 @@
       </c>
       <c r="N41" s="403"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="399"/>
       <c r="B42" s="436" t="s">
         <v>322</v>
@@ -32584,7 +32584,7 @@
       <c r="I42" s="399"/>
       <c r="N42" s="403"/>
     </row>
-    <row r="43" spans="1:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="399"/>
       <c r="B43" s="438" t="s">
         <v>332</v>
@@ -32605,7 +32605,7 @@
       <c r="I43" s="399"/>
       <c r="N43" s="403"/>
     </row>
-    <row r="44" spans="1:33" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="404"/>
       <c r="B44" s="405"/>
       <c r="C44" s="405"/>
@@ -32621,10 +32621,10 @@
       <c r="M44" s="405"/>
       <c r="N44" s="406"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="H45" s="327"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="926" t="s">
         <v>334</v>
       </c>
@@ -32661,7 +32661,7 @@
       <c r="AF46" s="394"/>
       <c r="AG46" s="394"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="276" t="s">
         <v>576</v>
       </c>
@@ -32700,7 +32700,7 @@
       <c r="AF47" s="394"/>
       <c r="AG47" s="394"/>
     </row>
-    <row r="49" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A49" s="395" t="s">
         <v>310</v>
       </c>
@@ -32711,7 +32711,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="396" t="s">
         <v>333</v>
       </c>
@@ -32722,7 +32722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="396" t="s">
         <v>331</v>
       </c>
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="396" t="s">
         <v>330</v>
       </c>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="396" t="s">
         <v>329</v>
       </c>
@@ -32755,7 +32755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="396" t="s">
         <v>32</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="396" t="s">
         <v>33</v>
       </c>
@@ -32777,7 +32777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="396" t="s">
         <v>328</v>
       </c>
@@ -32788,7 +32788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="396" t="s">
         <v>327</v>
       </c>
@@ -32799,7 +32799,7 @@
         <v>0.84524144608114071</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="396" t="s">
         <v>326</v>
       </c>
@@ -32810,7 +32810,7 @@
         <v>0.9432425243205943</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="396" t="s">
         <v>325</v>
       </c>
@@ -32821,7 +32821,7 @@
         <v>0.62373862032104566</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="396" t="s">
         <v>324</v>
       </c>
@@ -32832,7 +32832,7 @@
         <v>0.44347925869259897</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="396" t="s">
         <v>346</v>
       </c>
@@ -32843,7 +32843,7 @@
         <v>0.53492396576729018</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="396" t="s">
         <v>323</v>
       </c>
@@ -32854,7 +32854,7 @@
         <v>0.36241121553263428</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="396" t="s">
         <v>322</v>
       </c>
@@ -32886,21 +32886,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="141" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="141" customWidth="1"/>
     <col min="2" max="2" width="2" style="141" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="141" customWidth="1"/>
-    <col min="4" max="8" width="9.28515625" style="141" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="141" customWidth="1"/>
-    <col min="10" max="10" width="1.5703125" style="141" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" style="141" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="141" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="141" customWidth="1"/>
+    <col min="4" max="8" width="9.33203125" style="141" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="141" customWidth="1"/>
+    <col min="10" max="10" width="1.5546875" style="141" customWidth="1"/>
+    <col min="11" max="11" width="13.5546875" style="141" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" style="141" customWidth="1"/>
     <col min="13" max="13" width="8" style="141" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="141" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" style="141" customWidth="1"/>
-    <col min="16" max="22" width="10.7109375" style="141" customWidth="1"/>
-    <col min="23" max="16384" width="10.28515625" style="141"/>
+    <col min="14" max="14" width="12.6640625" style="141" customWidth="1"/>
+    <col min="15" max="15" width="10.88671875" style="141" customWidth="1"/>
+    <col min="16" max="22" width="10.6640625" style="141" customWidth="1"/>
+    <col min="23" max="16384" width="10.33203125" style="141"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
@@ -32963,7 +32963,7 @@
       <c r="J5" s="148"/>
       <c r="K5" s="149"/>
     </row>
-    <row r="6" spans="1:19" ht="15.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="150"/>
       <c r="B6" s="150"/>
       <c r="C6" s="150"/>
@@ -32976,7 +32976,7 @@
       <c r="J6" s="150"/>
       <c r="K6" s="150"/>
     </row>
-    <row r="7" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="150"/>
       <c r="B7" s="150"/>
       <c r="C7" s="150"/>
@@ -32989,39 +32989,39 @@
       <c r="J7" s="150"/>
       <c r="K7" s="150"/>
     </row>
-    <row r="8" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="958" t="s">
+    <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="936" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="958"/>
-      <c r="C8" s="958"/>
-      <c r="D8" s="958"/>
-      <c r="E8" s="958"/>
-      <c r="F8" s="958"/>
-      <c r="G8" s="958"/>
-      <c r="H8" s="958"/>
-      <c r="I8" s="958"/>
-      <c r="J8" s="958"/>
-      <c r="K8" s="958"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="959">
+      <c r="B8" s="936"/>
+      <c r="C8" s="936"/>
+      <c r="D8" s="936"/>
+      <c r="E8" s="936"/>
+      <c r="F8" s="936"/>
+      <c r="G8" s="936"/>
+      <c r="H8" s="936"/>
+      <c r="I8" s="936"/>
+      <c r="J8" s="936"/>
+      <c r="K8" s="936"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="937">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="959"/>
-      <c r="C9" s="959"/>
-      <c r="D9" s="959"/>
-      <c r="E9" s="959"/>
-      <c r="F9" s="959"/>
-      <c r="G9" s="959"/>
-      <c r="H9" s="959"/>
-      <c r="I9" s="959"/>
-      <c r="J9" s="959"/>
-      <c r="K9" s="959"/>
+      <c r="B9" s="937"/>
+      <c r="C9" s="937"/>
+      <c r="D9" s="937"/>
+      <c r="E9" s="937"/>
+      <c r="F9" s="937"/>
+      <c r="G9" s="937"/>
+      <c r="H9" s="937"/>
+      <c r="I9" s="937"/>
+      <c r="J9" s="937"/>
+      <c r="K9" s="937"/>
       <c r="O9" s="151"/>
     </row>
-    <row r="10" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="152"/>
       <c r="B10" s="152"/>
       <c r="C10" s="152"/>
@@ -33034,22 +33034,22 @@
       <c r="J10" s="152"/>
       <c r="K10" s="152"/>
     </row>
-    <row r="11" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="960">
+      <c r="C11" s="938">
         <f>+A.Granul!F10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="960"/>
-      <c r="E11" s="960"/>
-      <c r="F11" s="960"/>
-      <c r="G11" s="960"/>
-      <c r="H11" s="960"/>
+      <c r="D11" s="938"/>
+      <c r="E11" s="938"/>
+      <c r="F11" s="938"/>
+      <c r="G11" s="938"/>
+      <c r="H11" s="938"/>
       <c r="I11" s="153" t="s">
         <v>31</v>
       </c>
@@ -33063,22 +33063,22 @@
       <c r="M11" s="156"/>
       <c r="O11" s="157"/>
     </row>
-    <row r="12" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="960">
+      <c r="C12" s="938">
         <f>+A.Granul!F11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="960"/>
-      <c r="E12" s="960"/>
-      <c r="F12" s="960"/>
-      <c r="G12" s="960"/>
-      <c r="H12" s="960"/>
+      <c r="D12" s="938"/>
+      <c r="E12" s="938"/>
+      <c r="F12" s="938"/>
+      <c r="G12" s="938"/>
+      <c r="H12" s="938"/>
       <c r="I12" s="15" t="s">
         <v>19</v>
       </c>
@@ -33096,22 +33096,22 @@
       <c r="R12" s="160"/>
       <c r="S12" s="161"/>
     </row>
-    <row r="13" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="960">
+      <c r="C13" s="938">
         <f>+A.Granul!F12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="960"/>
-      <c r="E13" s="960"/>
-      <c r="F13" s="960"/>
-      <c r="G13" s="960"/>
-      <c r="H13" s="960"/>
+      <c r="D13" s="938"/>
+      <c r="E13" s="938"/>
+      <c r="F13" s="938"/>
+      <c r="G13" s="938"/>
+      <c r="H13" s="938"/>
       <c r="I13" s="15" t="s">
         <v>20</v>
       </c>
@@ -33125,10 +33125,10 @@
       <c r="M13" s="156"/>
       <c r="P13" s="159"/>
       <c r="Q13" s="159"/>
-      <c r="R13" s="957"/>
-      <c r="S13" s="957"/>
-    </row>
-    <row r="14" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R13" s="935"/>
+      <c r="S13" s="935"/>
+    </row>
+    <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="162"/>
@@ -33148,19 +33148,19 @@
       <c r="S14" s="164"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="943" t="s">
+      <c r="A15" s="940" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="944"/>
-      <c r="C15" s="944"/>
-      <c r="D15" s="944"/>
-      <c r="E15" s="944"/>
-      <c r="F15" s="944"/>
-      <c r="G15" s="944"/>
-      <c r="H15" s="944"/>
-      <c r="I15" s="944"/>
-      <c r="J15" s="944"/>
-      <c r="K15" s="945"/>
+      <c r="B15" s="941"/>
+      <c r="C15" s="941"/>
+      <c r="D15" s="941"/>
+      <c r="E15" s="941"/>
+      <c r="F15" s="941"/>
+      <c r="G15" s="941"/>
+      <c r="H15" s="941"/>
+      <c r="I15" s="941"/>
+      <c r="J15" s="941"/>
+      <c r="K15" s="942"/>
       <c r="L15" s="156"/>
       <c r="M15" s="156"/>
       <c r="P15" s="159"/>
@@ -33169,19 +33169,19 @@
       <c r="S15" s="164"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="946" t="s">
+      <c r="A16" s="943" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="947"/>
-      <c r="C16" s="947"/>
-      <c r="D16" s="947"/>
-      <c r="E16" s="947"/>
-      <c r="F16" s="947"/>
-      <c r="G16" s="947"/>
-      <c r="H16" s="947"/>
-      <c r="I16" s="947"/>
-      <c r="J16" s="947"/>
-      <c r="K16" s="948"/>
+      <c r="B16" s="944"/>
+      <c r="C16" s="944"/>
+      <c r="D16" s="944"/>
+      <c r="E16" s="944"/>
+      <c r="F16" s="944"/>
+      <c r="G16" s="944"/>
+      <c r="H16" s="944"/>
+      <c r="I16" s="944"/>
+      <c r="J16" s="944"/>
+      <c r="K16" s="945"/>
       <c r="L16" s="156"/>
       <c r="M16" s="156"/>
       <c r="P16" s="159"/>
@@ -33208,27 +33208,27 @@
       <c r="R17" s="164"/>
       <c r="S17" s="164"/>
     </row>
-    <row r="18" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="949" t="s">
+    <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="946" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="950"/>
-      <c r="C18" s="950"/>
-      <c r="D18" s="950"/>
-      <c r="E18" s="950"/>
-      <c r="F18" s="950"/>
-      <c r="G18" s="950"/>
-      <c r="H18" s="950"/>
-      <c r="I18" s="950"/>
-      <c r="J18" s="950"/>
-      <c r="K18" s="951"/>
+      <c r="B18" s="947"/>
+      <c r="C18" s="947"/>
+      <c r="D18" s="947"/>
+      <c r="E18" s="947"/>
+      <c r="F18" s="947"/>
+      <c r="G18" s="947"/>
+      <c r="H18" s="947"/>
+      <c r="I18" s="947"/>
+      <c r="J18" s="947"/>
+      <c r="K18" s="948"/>
       <c r="M18" s="156"/>
       <c r="P18" s="159"/>
       <c r="Q18" s="159"/>
       <c r="R18" s="168"/>
       <c r="S18" s="168"/>
     </row>
-    <row r="19" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="169" t="s">
         <v>24</v>
       </c>
@@ -33260,7 +33260,7 @@
       <c r="R19" s="168"/>
       <c r="S19" s="168"/>
     </row>
-    <row r="20" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="169" t="s">
         <v>28</v>
       </c>
@@ -33295,7 +33295,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="169" t="s">
         <v>25</v>
       </c>
@@ -33346,8 +33346,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="176"/>
-      <c r="I23" s="952"/>
-      <c r="J23" s="952"/>
+      <c r="I23" s="949"/>
+      <c r="J23" s="949"/>
       <c r="K23" s="177"/>
       <c r="L23" s="156"/>
       <c r="M23" s="178"/>
@@ -33355,41 +33355,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
-      <c r="D24" s="953" t="s">
+      <c r="D24" s="950" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="954"/>
-      <c r="F24" s="954"/>
-      <c r="G24" s="955" t="s">
+      <c r="E24" s="951"/>
+      <c r="F24" s="951"/>
+      <c r="G24" s="952" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="956"/>
-      <c r="I24" s="940"/>
-      <c r="J24" s="940"/>
+      <c r="H24" s="953"/>
+      <c r="I24" s="954"/>
+      <c r="J24" s="954"/>
       <c r="K24" s="181"/>
       <c r="L24" s="156"/>
       <c r="M24" s="182"/>
-      <c r="O24" s="935" t="s">
+      <c r="O24" s="955" t="s">
         <v>174</v>
       </c>
-      <c r="P24" s="936"/>
+      <c r="P24" s="956"/>
       <c r="Q24" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="935" t="s">
+      <c r="R24" s="955" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="937"/>
+      <c r="S24" s="957"/>
       <c r="T24" s="183" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
-      <c r="B25" s="938" t="s">
+      <c r="B25" s="958" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="939"/>
+      <c r="C25" s="959"/>
       <c r="D25" s="184" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -33410,8 +33410,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="940"/>
-      <c r="J25" s="940"/>
+      <c r="I25" s="954"/>
+      <c r="J25" s="954"/>
       <c r="K25" s="181"/>
       <c r="L25" s="156"/>
       <c r="M25" s="182"/>
@@ -33460,8 +33460,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="941"/>
-      <c r="J26" s="941"/>
+      <c r="I26" s="960"/>
+      <c r="J26" s="960"/>
       <c r="K26" s="194"/>
       <c r="L26" s="195"/>
       <c r="M26" s="182"/>
@@ -34076,7 +34076,7 @@
       <c r="P42" s="216"/>
       <c r="Q42" s="240"/>
     </row>
-    <row r="43" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="223" t="s">
         <v>22</v>
       </c>
@@ -34093,7 +34093,7 @@
       <c r="L43" s="156"/>
       <c r="M43" s="156"/>
     </row>
-    <row r="44" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="244"/>
       <c r="B44" s="224"/>
       <c r="C44" s="224"/>
@@ -34115,7 +34115,7 @@
         <v>24.296605773915516</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="245"/>
       <c r="B45" s="224"/>
       <c r="C45" s="224"/>
@@ -34139,7 +34139,7 @@
       <c r="P45"/>
       <c r="Q45"/>
     </row>
-    <row r="46" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="170"/>
       <c r="C46" s="170"/>
       <c r="D46" s="224"/>
@@ -34166,7 +34166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="246" t="s">
         <v>23</v>
       </c>
@@ -34198,7 +34198,7 @@
         <v>1.146128035678238</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="246" t="s">
         <v>193</v>
       </c>
@@ -34230,7 +34230,7 @@
         <v>25.943646996278545</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O49" s="275">
         <f>TREND(O48:Q48,O47:Q47,O45)</f>
         <v>24.296605773915516</v>
@@ -34239,34 +34239,33 @@
       <c r="Q49"/>
     </row>
     <row r="50" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="942" t="s">
+      <c r="A50" s="939" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="942"/>
-      <c r="C50" s="942"/>
-      <c r="D50" s="942"/>
-      <c r="E50" s="942"/>
-      <c r="F50" s="942"/>
-      <c r="G50" s="942"/>
-      <c r="H50" s="942"/>
-      <c r="I50" s="942"/>
-      <c r="J50" s="942"/>
-      <c r="K50" s="942"/>
-    </row>
-    <row r="51" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B50" s="939"/>
+      <c r="C50" s="939"/>
+      <c r="D50" s="939"/>
+      <c r="E50" s="939"/>
+      <c r="F50" s="939"/>
+      <c r="G50" s="939"/>
+      <c r="H50" s="939"/>
+      <c r="I50" s="939"/>
+      <c r="J50" s="939"/>
+      <c r="K50" s="939"/>
+    </row>
+    <row r="51" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C12:C14 C17" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -34275,11 +34274,12 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -34297,37 +34297,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" style="89" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="89" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="89" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" style="89"/>
-    <col min="6" max="6" width="32.85546875" style="89" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="89" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="89" customWidth="1"/>
-    <col min="9" max="15" width="11.42578125" style="89"/>
-    <col min="16" max="16" width="20.5703125" style="89" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="89" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="89"/>
+    <col min="1" max="1" width="20.5546875" style="89" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="89" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.44140625" style="89"/>
+    <col min="6" max="6" width="32.88671875" style="89" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="89" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="89" customWidth="1"/>
+    <col min="9" max="15" width="11.44140625" style="89"/>
+    <col min="16" max="16" width="20.5546875" style="89" customWidth="1"/>
+    <col min="17" max="17" width="13.44140625" style="89" customWidth="1"/>
+    <col min="18" max="16384" width="11.44140625" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="980" t="s">
+      <c r="B1" s="961" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="980"/>
-      <c r="D1" s="980"/>
-      <c r="E1" s="980"/>
-      <c r="F1" s="980"/>
-      <c r="G1" s="980"/>
-      <c r="H1" s="980"/>
+      <c r="C1" s="961"/>
+      <c r="D1" s="961"/>
+      <c r="E1" s="961"/>
+      <c r="F1" s="961"/>
+      <c r="G1" s="961"/>
+      <c r="H1" s="961"/>
       <c r="I1" s="94"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="94"/>
       <c r="B2" s="95"/>
       <c r="C2" s="95"/>
@@ -34342,7 +34342,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="94"/>
       <c r="B3" s="97" t="s">
         <v>99</v>
@@ -34370,7 +34370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="94"/>
       <c r="B4" s="97" t="s">
         <v>102</v>
@@ -34403,7 +34403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="94"/>
       <c r="B5" s="97" t="s">
         <v>106</v>
@@ -34426,7 +34426,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="94"/>
       <c r="B6" s="97" t="s">
         <v>108</v>
@@ -34449,7 +34449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="94"/>
       <c r="B7" s="94"/>
       <c r="C7" s="95"/>
@@ -34460,31 +34460,31 @@
       <c r="H7" s="94"/>
       <c r="I7" s="94"/>
     </row>
-    <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
-      <c r="B8" s="981" t="s">
+      <c r="B8" s="962" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="981"/>
-      <c r="D8" s="981"/>
+      <c r="C8" s="962"/>
+      <c r="D8" s="962"/>
       <c r="E8" s="103" t="s">
         <v>111</v>
       </c>
       <c r="F8" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="982" t="s">
+      <c r="G8" s="963" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="982"/>
+      <c r="H8" s="963"/>
       <c r="I8" s="94"/>
       <c r="L8" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="983" t="s">
+      <c r="M8" s="964" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="983"/>
+      <c r="N8" s="964"/>
       <c r="O8" s="248" t="s">
         <v>116</v>
       </c>
@@ -34495,15 +34495,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
-      <c r="B9" s="984" t="s">
+      <c r="B9" s="965" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="986" t="s">
+      <c r="C9" s="967" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="988" t="s">
+      <c r="D9" s="969" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="106" t="s">
@@ -34512,10 +34512,10 @@
       <c r="F9" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="989" t="s">
+      <c r="G9" s="970" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="990"/>
+      <c r="H9" s="971"/>
       <c r="I9" s="94"/>
       <c r="L9" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -34542,21 +34542,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
-      <c r="B10" s="984"/>
-      <c r="C10" s="986"/>
-      <c r="D10" s="988"/>
+      <c r="B10" s="965"/>
+      <c r="C10" s="967"/>
+      <c r="D10" s="969"/>
       <c r="E10" s="108" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="991" t="s">
+      <c r="G10" s="972" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="992"/>
+      <c r="H10" s="973"/>
       <c r="I10" s="94"/>
       <c r="L10" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -34579,11 +34579,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="984"/>
-      <c r="C11" s="986"/>
-      <c r="D11" s="988" t="s">
+      <c r="B11" s="965"/>
+      <c r="C11" s="967"/>
+      <c r="D11" s="969" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="108" t="s">
@@ -34595,7 +34595,7 @@
       <c r="G11" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="993" t="s">
+      <c r="H11" s="974" t="s">
         <v>132</v>
       </c>
       <c r="I11" s="94"/>
@@ -34614,11 +34614,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="94"/>
-      <c r="B12" s="984"/>
-      <c r="C12" s="987"/>
-      <c r="D12" s="988"/>
+      <c r="B12" s="965"/>
+      <c r="C12" s="968"/>
+      <c r="D12" s="969"/>
       <c r="E12" s="112" t="s">
         <v>133</v>
       </c>
@@ -34628,7 +34628,7 @@
       <c r="G12" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="994"/>
+      <c r="H12" s="975"/>
       <c r="I12" s="94"/>
       <c r="L12" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -34642,13 +34642,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="984"/>
-      <c r="C13" s="986" t="s">
+      <c r="B13" s="965"/>
+      <c r="C13" s="967" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="988" t="s">
+      <c r="D13" s="969" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="113" t="s">
@@ -34657,10 +34657,10 @@
       <c r="F13" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="995" t="s">
+      <c r="G13" s="976" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="996"/>
+      <c r="H13" s="977"/>
       <c r="I13" s="94"/>
       <c r="L13" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -34683,21 +34683,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="984"/>
-      <c r="C14" s="986"/>
-      <c r="D14" s="988"/>
+      <c r="B14" s="965"/>
+      <c r="C14" s="967"/>
+      <c r="D14" s="969"/>
       <c r="E14" s="113" t="s">
         <v>141</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="995" t="s">
+      <c r="G14" s="976" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="996"/>
+      <c r="H14" s="977"/>
       <c r="I14" s="94"/>
       <c r="L14" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -34720,11 +34720,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="94"/>
-      <c r="B15" s="984"/>
-      <c r="C15" s="986"/>
-      <c r="D15" s="988" t="s">
+      <c r="B15" s="965"/>
+      <c r="C15" s="967"/>
+      <c r="D15" s="969" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="113" t="s">
@@ -34736,7 +34736,7 @@
       <c r="G15" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="963" t="s">
+      <c r="H15" s="980" t="s">
         <v>148</v>
       </c>
       <c r="I15" s="94"/>
@@ -34755,11 +34755,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="94"/>
-      <c r="B16" s="985"/>
-      <c r="C16" s="986"/>
-      <c r="D16" s="988"/>
+      <c r="B16" s="966"/>
+      <c r="C16" s="967"/>
+      <c r="D16" s="969"/>
       <c r="E16" s="117" t="s">
         <v>149</v>
       </c>
@@ -34769,7 +34769,7 @@
       <c r="G16" s="114" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="964"/>
+      <c r="H16" s="981"/>
       <c r="I16" s="94"/>
       <c r="L16" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -34783,25 +34783,25 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="965" t="s">
+      <c r="B17" s="982" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="968" t="s">
+      <c r="C17" s="985" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="969"/>
+      <c r="D17" s="986"/>
       <c r="E17" s="118" t="s">
         <v>154</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="974" t="s">
+      <c r="G17" s="991" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="975"/>
+      <c r="H17" s="992"/>
       <c r="I17" s="94"/>
       <c r="L17" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -34815,19 +34815,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="94"/>
-      <c r="B18" s="966"/>
-      <c r="C18" s="970"/>
-      <c r="D18" s="971"/>
+      <c r="B18" s="983"/>
+      <c r="C18" s="987"/>
+      <c r="D18" s="988"/>
       <c r="E18" s="118" t="s">
         <v>157</v>
       </c>
       <c r="F18" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="976"/>
-      <c r="H18" s="977"/>
+      <c r="G18" s="993"/>
+      <c r="H18" s="994"/>
       <c r="I18" s="94"/>
       <c r="L18" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -34841,11 +34841,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="966"/>
-      <c r="C19" s="972"/>
-      <c r="D19" s="973"/>
+      <c r="B19" s="983"/>
+      <c r="C19" s="989"/>
+      <c r="D19" s="990"/>
       <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
@@ -34867,13 +34867,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="966"/>
-      <c r="C20" s="970" t="s">
+      <c r="B20" s="983"/>
+      <c r="C20" s="987" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="978"/>
+      <c r="D20" s="995"/>
       <c r="E20" s="122" t="s">
         <v>162</v>
       </c>
@@ -34895,11 +34895,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="94"/>
-      <c r="B21" s="966"/>
-      <c r="C21" s="970"/>
-      <c r="D21" s="978"/>
+      <c r="B21" s="983"/>
+      <c r="C21" s="987"/>
+      <c r="D21" s="995"/>
       <c r="E21" s="122" t="s">
         <v>164</v>
       </c>
@@ -34921,11 +34921,11 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="94"/>
-      <c r="B22" s="966"/>
-      <c r="C22" s="972"/>
-      <c r="D22" s="979"/>
+      <c r="B22" s="983"/>
+      <c r="C22" s="989"/>
+      <c r="D22" s="996"/>
       <c r="E22" s="124" t="s">
         <v>166</v>
       </c>
@@ -34947,13 +34947,13 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
-      <c r="B23" s="966"/>
-      <c r="C23" s="968" t="s">
+      <c r="B23" s="983"/>
+      <c r="C23" s="985" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="969"/>
+      <c r="D23" s="986"/>
       <c r="E23" s="125" t="s">
         <v>169</v>
       </c>
@@ -34975,9 +34975,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="94"/>
-      <c r="B24" s="967"/>
+      <c r="B24" s="984"/>
       <c r="C24" s="127"/>
       <c r="D24" s="128"/>
       <c r="E24" s="129"/>
@@ -34997,7 +34997,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="94"/>
       <c r="B25" s="131"/>
       <c r="C25" s="131"/>
@@ -35008,7 +35008,7 @@
       <c r="H25" s="94"/>
       <c r="I25" s="94"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="94"/>
       <c r="B26" s="131"/>
       <c r="C26" s="131"/>
@@ -35019,7 +35019,7 @@
       <c r="H26" s="94"/>
       <c r="I26" s="94"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="94"/>
       <c r="B27" s="94"/>
       <c r="C27" s="94"/>
@@ -35030,7 +35030,7 @@
       <c r="H27" s="94"/>
       <c r="I27" s="94"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="94"/>
       <c r="B28" s="94"/>
       <c r="C28" s="94"/>
@@ -35041,7 +35041,7 @@
       <c r="H28" s="94"/>
       <c r="I28" s="94"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="94"/>
       <c r="B29" s="94"/>
       <c r="C29" s="94"/>
@@ -35052,7 +35052,7 @@
       <c r="H29" s="94"/>
       <c r="I29" s="94"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="256" t="s">
         <v>223</v>
       </c>
@@ -35062,7 +35062,7 @@
       </c>
       <c r="F30" s="135"/>
     </row>
-    <row r="31" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="256" t="s">
         <v>224</v>
       </c>
@@ -35072,20 +35072,20 @@
       </c>
       <c r="F31" s="135"/>
     </row>
-    <row r="32" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="961" t="s">
+    <row r="32" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="978" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="962"/>
+      <c r="B32" s="979"/>
       <c r="F32" s="135"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J34" s="89" t="e">
         <f>Q9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="89" t="s">
         <v>201</v>
       </c>
@@ -35105,7 +35105,7 @@
         <v>3.1365222149583265</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="89" t="s">
         <v>202</v>
       </c>
@@ -35121,7 +35121,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="252" t="s">
         <v>204</v>
       </c>
@@ -35137,7 +35137,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="258" t="s">
         <v>122</v>
       </c>
@@ -35151,7 +35151,7 @@
       <c r="F41" s="260"/>
       <c r="G41" s="260"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="258" t="s">
         <v>125</v>
       </c>
@@ -35165,7 +35165,7 @@
       <c r="F42" s="260"/>
       <c r="G42" s="260"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="258" t="s">
         <v>205</v>
       </c>
@@ -35179,7 +35179,7 @@
       <c r="F43" s="260"/>
       <c r="G43" s="260"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="258" t="s">
         <v>206</v>
       </c>
@@ -35193,7 +35193,7 @@
       <c r="F44" s="260"/>
       <c r="G44" s="260"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="258" t="s">
         <v>207</v>
       </c>
@@ -35207,7 +35207,7 @@
       <c r="F45" s="260"/>
       <c r="G45" s="260"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="258" t="s">
         <v>208</v>
       </c>
@@ -35221,7 +35221,7 @@
       <c r="F46" s="260"/>
       <c r="G46" s="260"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="258" t="s">
         <v>133</v>
       </c>
@@ -35235,7 +35235,7 @@
       <c r="F47" s="260"/>
       <c r="G47" s="260"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="258" t="s">
         <v>209</v>
       </c>
@@ -35249,7 +35249,7 @@
       <c r="F48" s="260"/>
       <c r="G48" s="260"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="258" t="s">
         <v>129</v>
       </c>
@@ -35263,7 +35263,7 @@
       <c r="F49" s="260"/>
       <c r="G49" s="260"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="258" t="s">
         <v>138</v>
       </c>
@@ -35277,7 +35277,7 @@
       <c r="F50" s="260"/>
       <c r="G50" s="260"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="258" t="s">
         <v>141</v>
       </c>
@@ -35291,7 +35291,7 @@
       <c r="F51" s="260"/>
       <c r="G51" s="260"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="258" t="s">
         <v>210</v>
       </c>
@@ -35305,7 +35305,7 @@
       <c r="F52" s="260"/>
       <c r="G52" s="260"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="258" t="s">
         <v>211</v>
       </c>
@@ -35319,7 +35319,7 @@
       <c r="F53" s="260"/>
       <c r="G53" s="260"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="258" t="s">
         <v>212</v>
       </c>
@@ -35333,7 +35333,7 @@
       <c r="F54" s="260"/>
       <c r="G54" s="260"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="258" t="s">
         <v>213</v>
       </c>
@@ -35347,7 +35347,7 @@
       <c r="F55" s="260"/>
       <c r="G55" s="260"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="258" t="s">
         <v>149</v>
       </c>
@@ -35361,7 +35361,7 @@
       <c r="F56" s="260"/>
       <c r="G56" s="260"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="258" t="s">
         <v>214</v>
       </c>
@@ -35375,7 +35375,7 @@
       <c r="F57" s="260"/>
       <c r="G57" s="260"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="258" t="s">
         <v>145</v>
       </c>
@@ -35389,7 +35389,7 @@
       <c r="F58" s="260"/>
       <c r="G58" s="260"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="258" t="s">
         <v>157</v>
       </c>
@@ -35403,7 +35403,7 @@
       <c r="F59" s="260"/>
       <c r="G59" s="260"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="258" t="s">
         <v>215</v>
       </c>
@@ -35417,7 +35417,7 @@
       <c r="F60" s="260"/>
       <c r="G60" s="260"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="258" t="s">
         <v>154</v>
       </c>
@@ -35431,7 +35431,7 @@
       <c r="F61" s="260"/>
       <c r="G61" s="260"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="261" t="s">
         <v>216</v>
       </c>
@@ -35445,7 +35445,7 @@
       <c r="F62" s="260"/>
       <c r="G62" s="260"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="261" t="s">
         <v>217</v>
       </c>
@@ -35459,7 +35459,7 @@
       <c r="F63" s="260"/>
       <c r="G63" s="260"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="258" t="s">
         <v>164</v>
       </c>
@@ -35473,7 +35473,7 @@
       <c r="F64" s="260"/>
       <c r="G64" s="260"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="258" t="s">
         <v>218</v>
       </c>
@@ -35487,7 +35487,7 @@
       <c r="F65" s="260"/>
       <c r="G65" s="260"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="258" t="s">
         <v>162</v>
       </c>
@@ -35501,7 +35501,7 @@
       <c r="F66" s="260"/>
       <c r="G66" s="260"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="258" t="s">
         <v>219</v>
       </c>
@@ -35515,7 +35515,7 @@
       <c r="F67" s="260"/>
       <c r="G67" s="260"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="258" t="s">
         <v>220</v>
       </c>
@@ -35529,7 +35529,7 @@
       <c r="F68" s="260"/>
       <c r="G68" s="260"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="258" t="s">
         <v>169</v>
       </c>
@@ -35543,7 +35543,7 @@
       <c r="F69" s="260"/>
       <c r="G69" s="260"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="258" t="s">
         <v>221</v>
       </c>
@@ -35560,7 +35560,7 @@
       <c r="F70" s="264"/>
       <c r="G70" s="264"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="258" t="s">
         <v>221</v>
       </c>
@@ -35574,7 +35574,7 @@
       <c r="F71" s="260"/>
       <c r="G71" s="260"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="258" t="s">
         <v>221</v>
       </c>
@@ -35588,7 +35588,7 @@
       <c r="F72" s="260"/>
       <c r="G72" s="260"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="258" t="s">
         <v>221</v>
       </c>
@@ -35602,7 +35602,7 @@
       <c r="F73" s="260"/>
       <c r="G73" s="260"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="258" t="s">
         <v>222</v>
       </c>
@@ -35616,7 +35616,7 @@
       <c r="F74" s="260"/>
       <c r="G74" s="260"/>
     </row>
-    <row r="75" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="267"/>
       <c r="B75" s="268"/>
       <c r="C75" s="269"/>
@@ -35627,6 +35627,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -35643,13 +35650,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35660,17 +35660,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="89" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="89" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" style="89" customWidth="1"/>
-    <col min="4" max="15" width="7.85546875" style="89" customWidth="1"/>
-    <col min="16" max="17" width="11.5703125" style="22"/>
-    <col min="18" max="16384" width="11.5703125" style="89"/>
+    <col min="1" max="1" width="6.109375" style="89" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="89" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" style="89" customWidth="1"/>
+    <col min="4" max="15" width="7.88671875" style="89" customWidth="1"/>
+    <col min="16" max="17" width="11.5546875" style="22"/>
+    <col min="18" max="16384" width="11.5546875" style="89"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="21"/>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -35687,7 +35687,7 @@
       <c r="N1" s="21"/>
       <c r="O1" s="21"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="23"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -35705,7 +35705,7 @@
       <c r="O2" s="23"/>
       <c r="P2" s="24"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -35723,7 +35723,7 @@
       <c r="O3" s="23"/>
       <c r="P3" s="24"/>
     </row>
-    <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="1003" t="s">
         <v>42</v>
@@ -35746,7 +35746,7 @@
       <c r="N4" s="1007"/>
       <c r="O4" s="1008"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="21"/>
       <c r="B5" s="1009" t="s">
         <v>45</v>
@@ -35779,7 +35779,7 @@
       </c>
       <c r="O5" s="1025"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="21"/>
       <c r="B6" s="1011"/>
       <c r="C6" s="1012"/>
@@ -35812,7 +35812,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="21"/>
       <c r="B7" s="31"/>
       <c r="C7" s="32"/>
@@ -35829,7 +35829,7 @@
       <c r="N7" s="38"/>
       <c r="O7" s="41"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="21"/>
       <c r="B8" s="42" t="s">
         <v>61</v>
@@ -35848,7 +35848,7 @@
       <c r="N8" s="38"/>
       <c r="O8" s="41"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="21"/>
       <c r="B9" s="42" t="s">
         <v>62</v>
@@ -35867,7 +35867,7 @@
       <c r="N9" s="38"/>
       <c r="O9" s="41"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="43"/>
       <c r="C10" s="32"/>
@@ -35884,7 +35884,7 @@
       <c r="N10" s="38"/>
       <c r="O10" s="41"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="21"/>
       <c r="B11" s="44" t="s">
         <v>63</v>
@@ -35908,7 +35908,7 @@
       <c r="N11" s="38"/>
       <c r="O11" s="41"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="21"/>
       <c r="B12" s="44" t="s">
         <v>65</v>
@@ -35936,7 +35936,7 @@
       <c r="N12" s="38"/>
       <c r="O12" s="41"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="21"/>
       <c r="B13" s="44" t="s">
         <v>68</v>
@@ -35982,7 +35982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="21"/>
       <c r="B14" s="46"/>
       <c r="C14" s="47"/>
@@ -35999,7 +35999,7 @@
       <c r="N14" s="52"/>
       <c r="O14" s="55"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="21"/>
       <c r="B15" s="56"/>
       <c r="C15" s="57"/>
@@ -36016,7 +36016,7 @@
       <c r="N15" s="62"/>
       <c r="O15" s="65"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="21"/>
       <c r="B16" s="66" t="s">
         <v>74</v>
@@ -36035,7 +36035,7 @@
       <c r="N16" s="62"/>
       <c r="O16" s="65"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="21"/>
       <c r="B17" s="66" t="s">
         <v>75</v>
@@ -36054,7 +36054,7 @@
       <c r="N17" s="62"/>
       <c r="O17" s="65"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="21"/>
       <c r="B18" s="66" t="s">
         <v>76</v>
@@ -36073,7 +36073,7 @@
       <c r="N18" s="62"/>
       <c r="O18" s="65"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="21"/>
       <c r="B19" s="68"/>
       <c r="C19" s="67"/>
@@ -36090,7 +36090,7 @@
       <c r="N19" s="62"/>
       <c r="O19" s="65"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="21"/>
       <c r="B20" s="69" t="s">
         <v>77</v>
@@ -36130,7 +36130,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="21"/>
       <c r="B21" s="69" t="s">
         <v>80</v>
@@ -36176,7 +36176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="21"/>
       <c r="B22" s="70"/>
       <c r="C22" s="71" t="s">
@@ -36195,7 +36195,7 @@
       <c r="N22" s="76"/>
       <c r="O22" s="79"/>
     </row>
-    <row r="23" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21"/>
       <c r="B23" s="80" t="s">
         <v>86</v>
@@ -36235,7 +36235,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" ht="13.8" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21"/>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -36252,7 +36252,7 @@
       <c r="N24" s="21"/>
       <c r="O24" s="21"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="21"/>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -36269,7 +36269,7 @@
       <c r="N25" s="21"/>
       <c r="O25" s="21"/>
     </row>
-    <row r="26" spans="1:15" ht="18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -36291,7 +36291,7 @@
       <c r="N26" s="21"/>
       <c r="O26" s="21"/>
     </row>
-    <row r="27" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -36308,8 +36308,8 @@
       <c r="N27" s="21"/>
       <c r="O27" s="21"/>
     </row>
-    <row r="28" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="89" t="e">
         <f>IF(AND(C11&lt;=50,C12&lt;=30,C13&lt;=15,OR(C21&lt;=6,C21="NP"),C23&lt;=0),D6,"--")</f>
         <v>#DIV/0!</v>
@@ -36359,7 +36359,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="89" t="e">
         <f>IF(D29&lt;&gt;"--",D29,"")</f>
         <v>#DIV/0!</v>
@@ -36409,14 +36409,14 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="89" t="e">
         <f>+D30&amp;E30&amp;F30&amp;G30&amp;H30&amp;I30&amp;J30&amp;K30&amp;L30&amp;M30&amp;N30&amp;O30</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="89" t="s">
         <v>93</v>
       </c>
@@ -36425,7 +36425,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="89" t="s">
         <v>94</v>
       </c>
@@ -36434,7 +36434,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="91" t="s">
         <v>95</v>
       </c>
@@ -36443,7 +36443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="89" t="s">
         <v>96</v>
       </c>
@@ -36452,8 +36452,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="92" t="e">
         <f>0.2*D33+0.005*D33*D35+0.01*D34*D36</f>
         <v>#DIV/0!</v>
@@ -36467,9 +36467,9 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:15" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:15" ht="16.2" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:15" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -36486,7 +36486,7 @@
       <c r="N41" s="21"/>
       <c r="O41" s="21"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
@@ -36533,18 +36533,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A2:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1026" t="s">
         <v>10</v>
       </c>
@@ -36583,7 +36583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>4400</v>
       </c>
@@ -36629,7 +36629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="6" t="str">
@@ -36666,7 +36666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f>+B3+1</f>
         <v>4402</v>
@@ -36709,7 +36709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="6" t="str">
@@ -36746,7 +36746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f>+B5+1</f>
         <v>4404</v>
@@ -36789,7 +36789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="6" t="str">
@@ -36826,7 +36826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>

--- a/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
+++ b/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\GranSuelo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A50C744-50D6-4346-A072-05BFD129E348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF801408-7953-48AA-B302-714A567FF554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="1320" windowWidth="20280" windowHeight="10920" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="547" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="99" r:id="rId1"/>
@@ -7948,6 +7948,80 @@
     <xf numFmtId="179" fontId="4" fillId="3" borderId="99" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -7956,6 +8030,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7975,12 +8085,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -8005,15 +8109,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8023,100 +8118,217 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="77" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="95" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="97" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="84" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="155" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="157" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="188" fontId="17" fillId="0" borderId="86" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8139,218 +8351,6 @@
     <xf numFmtId="12" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="162" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="148" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="161" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="163" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="155" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="156" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="157" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="12" fontId="17" fillId="0" borderId="99" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="158" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="158" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="183" fontId="4" fillId="3" borderId="77" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8454,6 +8454,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="3" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="86" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="54" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -8470,77 +8542,62 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="83" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="86" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="82" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="91" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="96" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="54" fillId="3" borderId="1" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="95" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="55" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="77" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="56" fillId="3" borderId="97" xfId="4" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8592,63 +8649,6 @@
     </xf>
     <xf numFmtId="0" fontId="47" fillId="11" borderId="78" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="79" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="11" borderId="80" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="82" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="74" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="12" borderId="91" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="84" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="86" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="83" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="85" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="87" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="13" borderId="88" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="12" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="9" borderId="68" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -21606,38 +21606,38 @@
       <c r="O6" s="760"/>
     </row>
     <row r="7" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="782" t="s">
+      <c r="A7" s="814" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="782"/>
-      <c r="C7" s="782"/>
-      <c r="D7" s="782"/>
-      <c r="E7" s="782"/>
-      <c r="F7" s="782"/>
-      <c r="G7" s="782"/>
-      <c r="H7" s="782"/>
-      <c r="I7" s="782"/>
-      <c r="J7" s="782"/>
-      <c r="K7" s="782"/>
+      <c r="B7" s="814"/>
+      <c r="C7" s="814"/>
+      <c r="D7" s="814"/>
+      <c r="E7" s="814"/>
+      <c r="F7" s="814"/>
+      <c r="G7" s="814"/>
+      <c r="H7" s="814"/>
+      <c r="I7" s="814"/>
+      <c r="J7" s="814"/>
+      <c r="K7" s="814"/>
       <c r="N7" s="291" t="s">
         <v>447</v>
       </c>
       <c r="O7" s="760"/>
     </row>
     <row r="8" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="783" t="s">
+      <c r="A8" s="815" t="s">
         <v>477</v>
       </c>
-      <c r="B8" s="783"/>
-      <c r="C8" s="783"/>
-      <c r="D8" s="783"/>
-      <c r="E8" s="783"/>
-      <c r="F8" s="783"/>
-      <c r="G8" s="783"/>
-      <c r="H8" s="783"/>
-      <c r="I8" s="783"/>
-      <c r="J8" s="783"/>
-      <c r="K8" s="783"/>
+      <c r="B8" s="815"/>
+      <c r="C8" s="815"/>
+      <c r="D8" s="815"/>
+      <c r="E8" s="815"/>
+      <c r="F8" s="815"/>
+      <c r="G8" s="815"/>
+      <c r="H8" s="815"/>
+      <c r="I8" s="815"/>
+      <c r="J8" s="815"/>
+      <c r="K8" s="815"/>
       <c r="N8" s="291" t="s">
         <v>550</v>
       </c>
@@ -21663,18 +21663,18 @@
     <row r="10" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="485"/>
       <c r="C10" s="485"/>
-      <c r="D10" s="784" t="s">
+      <c r="D10" s="816" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="785"/>
-      <c r="F10" s="784" t="s">
+      <c r="E10" s="817"/>
+      <c r="F10" s="816" t="s">
         <v>479</v>
       </c>
-      <c r="G10" s="785"/>
-      <c r="H10" s="784" t="s">
+      <c r="G10" s="817"/>
+      <c r="H10" s="816" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="785"/>
+      <c r="I10" s="817"/>
       <c r="J10" s="679" t="s">
         <v>467</v>
       </c>
@@ -21688,12 +21688,12 @@
       <c r="A11" s="485"/>
       <c r="B11" s="485"/>
       <c r="C11" s="485"/>
-      <c r="D11" s="786"/>
-      <c r="E11" s="787"/>
-      <c r="F11" s="786"/>
-      <c r="G11" s="787"/>
-      <c r="H11" s="786"/>
-      <c r="I11" s="787"/>
+      <c r="D11" s="779"/>
+      <c r="E11" s="780"/>
+      <c r="F11" s="779"/>
+      <c r="G11" s="780"/>
+      <c r="H11" s="779"/>
+      <c r="I11" s="780"/>
       <c r="J11" s="682"/>
       <c r="K11" s="386"/>
       <c r="L11" s="681"/>
@@ -21723,19 +21723,19 @@
       <c r="O12" s="761"/>
     </row>
     <row r="13" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="788" t="s">
+      <c r="A13" s="818" t="s">
         <v>480</v>
       </c>
-      <c r="B13" s="789"/>
-      <c r="C13" s="789"/>
-      <c r="D13" s="789"/>
-      <c r="E13" s="789"/>
-      <c r="F13" s="789"/>
-      <c r="G13" s="789"/>
-      <c r="H13" s="789"/>
-      <c r="I13" s="789"/>
-      <c r="J13" s="789"/>
-      <c r="K13" s="790"/>
+      <c r="B13" s="819"/>
+      <c r="C13" s="819"/>
+      <c r="D13" s="819"/>
+      <c r="E13" s="819"/>
+      <c r="F13" s="819"/>
+      <c r="G13" s="819"/>
+      <c r="H13" s="819"/>
+      <c r="I13" s="819"/>
+      <c r="J13" s="819"/>
+      <c r="K13" s="820"/>
       <c r="L13" s="681"/>
       <c r="M13" s="681"/>
       <c r="N13" s="291" t="s">
@@ -21744,19 +21744,19 @@
       <c r="O13" s="761"/>
     </row>
     <row r="14" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="791" t="s">
+      <c r="A14" s="821" t="s">
         <v>481</v>
       </c>
-      <c r="B14" s="792"/>
-      <c r="C14" s="792"/>
-      <c r="D14" s="792"/>
-      <c r="E14" s="792"/>
-      <c r="F14" s="792"/>
-      <c r="G14" s="792"/>
-      <c r="H14" s="792"/>
-      <c r="I14" s="792"/>
-      <c r="J14" s="792"/>
-      <c r="K14" s="793"/>
+      <c r="B14" s="822"/>
+      <c r="C14" s="822"/>
+      <c r="D14" s="822"/>
+      <c r="E14" s="822"/>
+      <c r="F14" s="822"/>
+      <c r="G14" s="822"/>
+      <c r="H14" s="822"/>
+      <c r="I14" s="822"/>
+      <c r="J14" s="822"/>
+      <c r="K14" s="823"/>
       <c r="L14" s="681"/>
       <c r="M14" s="681"/>
       <c r="N14" s="759"/>
@@ -21776,21 +21776,21 @@
       <c r="U15" s="684"/>
     </row>
     <row r="16" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="794" t="s">
+      <c r="A16" s="804" t="s">
         <v>482</v>
       </c>
-      <c r="B16" s="795"/>
-      <c r="C16" s="796"/>
-      <c r="E16" s="797" t="s">
+      <c r="B16" s="805"/>
+      <c r="C16" s="806"/>
+      <c r="E16" s="824" t="s">
         <v>372</v>
       </c>
-      <c r="F16" s="798"/>
-      <c r="G16" s="798"/>
-      <c r="H16" s="799"/>
-      <c r="J16" s="794" t="s">
+      <c r="F16" s="825"/>
+      <c r="G16" s="825"/>
+      <c r="H16" s="826"/>
+      <c r="J16" s="804" t="s">
         <v>483</v>
       </c>
-      <c r="K16" s="796"/>
+      <c r="K16" s="806"/>
       <c r="M16" s="684"/>
       <c r="N16" s="291" t="s">
         <v>245</v>
@@ -21806,16 +21806,16 @@
       <c r="A17" s="687" t="s">
         <v>484</v>
       </c>
-      <c r="B17" s="778"/>
-      <c r="C17" s="779"/>
+      <c r="B17" s="799"/>
+      <c r="C17" s="800"/>
       <c r="E17" s="688" t="s">
         <v>485</v>
       </c>
       <c r="F17" s="689"/>
       <c r="G17" s="690"/>
       <c r="H17" s="691"/>
-      <c r="J17" s="780"/>
-      <c r="K17" s="781"/>
+      <c r="J17" s="812"/>
+      <c r="K17" s="813"/>
       <c r="M17" s="684"/>
       <c r="N17" s="291" t="s">
         <v>552</v>
@@ -21831,8 +21831,8 @@
       <c r="A18" s="687" t="s">
         <v>486</v>
       </c>
-      <c r="B18" s="778"/>
-      <c r="C18" s="779"/>
+      <c r="B18" s="799"/>
+      <c r="C18" s="800"/>
       <c r="E18" s="688" t="s">
         <v>487</v>
       </c>
@@ -21855,10 +21855,10 @@
       <c r="F19" s="689"/>
       <c r="G19" s="690"/>
       <c r="H19" s="694"/>
-      <c r="J19" s="804" t="s">
+      <c r="J19" s="782" t="s">
         <v>489</v>
       </c>
-      <c r="K19" s="805"/>
+      <c r="K19" s="783"/>
       <c r="M19" s="684"/>
       <c r="N19" s="692"/>
       <c r="O19" s="685"/>
@@ -21869,11 +21869,11 @@
       <c r="U19" s="686"/>
     </row>
     <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="806" t="s">
+      <c r="A20" s="789" t="s">
         <v>490</v>
       </c>
-      <c r="B20" s="807"/>
-      <c r="C20" s="808"/>
+      <c r="B20" s="790"/>
+      <c r="C20" s="791"/>
       <c r="E20" s="695" t="s">
         <v>491</v>
       </c>
@@ -21897,8 +21897,8 @@
       <c r="A21" s="687" t="s">
         <v>492</v>
       </c>
-      <c r="B21" s="809"/>
-      <c r="C21" s="810"/>
+      <c r="B21" s="801"/>
+      <c r="C21" s="802"/>
       <c r="E21" s="700"/>
       <c r="F21" s="700"/>
       <c r="G21" s="700"/>
@@ -21919,14 +21919,14 @@
       <c r="A22" s="687" t="s">
         <v>494</v>
       </c>
-      <c r="B22" s="809"/>
-      <c r="C22" s="810"/>
-      <c r="E22" s="804" t="s">
+      <c r="B22" s="801"/>
+      <c r="C22" s="802"/>
+      <c r="E22" s="782" t="s">
         <v>369</v>
       </c>
-      <c r="F22" s="811"/>
-      <c r="G22" s="811"/>
-      <c r="H22" s="805"/>
+      <c r="F22" s="803"/>
+      <c r="G22" s="803"/>
+      <c r="H22" s="783"/>
       <c r="I22" s="701"/>
       <c r="J22" s="486" t="s">
         <v>370</v>
@@ -21962,11 +21962,11 @@
       <c r="U23" s="686"/>
     </row>
     <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="794" t="s">
+      <c r="A24" s="804" t="s">
         <v>497</v>
       </c>
-      <c r="B24" s="795"/>
-      <c r="C24" s="796"/>
+      <c r="B24" s="805"/>
+      <c r="C24" s="806"/>
       <c r="E24" s="688" t="s">
         <v>498</v>
       </c>
@@ -22118,8 +22118,8 @@
       <c r="A31" s="705" t="s">
         <v>510</v>
       </c>
-      <c r="B31" s="812"/>
-      <c r="C31" s="812"/>
+      <c r="B31" s="807"/>
+      <c r="C31" s="807"/>
       <c r="E31" s="688" t="s">
         <v>511</v>
       </c>
@@ -22142,8 +22142,8 @@
       <c r="A32" s="705" t="s">
         <v>512</v>
       </c>
-      <c r="B32" s="812"/>
-      <c r="C32" s="812"/>
+      <c r="B32" s="807"/>
+      <c r="C32" s="807"/>
       <c r="E32" s="688" t="s">
         <v>513</v>
       </c>
@@ -22182,17 +22182,17 @@
       <c r="U33" s="686"/>
     </row>
     <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="806" t="s">
+      <c r="A34" s="789" t="s">
         <v>515</v>
       </c>
-      <c r="B34" s="807"/>
-      <c r="C34" s="808"/>
-      <c r="E34" s="813" t="s">
+      <c r="B34" s="790"/>
+      <c r="C34" s="791"/>
+      <c r="E34" s="808" t="s">
         <v>516</v>
       </c>
-      <c r="F34" s="814"/>
-      <c r="G34" s="800"/>
-      <c r="H34" s="801"/>
+      <c r="F34" s="809"/>
+      <c r="G34" s="795"/>
+      <c r="H34" s="796"/>
       <c r="I34" s="717"/>
       <c r="J34" s="718" t="s">
         <v>517</v>
@@ -22212,10 +22212,10 @@
       </c>
       <c r="B35" s="700"/>
       <c r="C35" s="721"/>
-      <c r="E35" s="815"/>
-      <c r="F35" s="816"/>
-      <c r="G35" s="802"/>
-      <c r="H35" s="803"/>
+      <c r="E35" s="810"/>
+      <c r="F35" s="811"/>
+      <c r="G35" s="797"/>
+      <c r="H35" s="798"/>
       <c r="J35" s="722" t="s">
         <v>519</v>
       </c>
@@ -22239,19 +22239,19 @@
       <c r="P36" s="684"/>
     </row>
     <row r="37" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="806" t="s">
+      <c r="A37" s="789" t="s">
         <v>520</v>
       </c>
-      <c r="B37" s="807"/>
-      <c r="C37" s="808"/>
-      <c r="E37" s="824" t="s">
+      <c r="B37" s="790"/>
+      <c r="C37" s="791"/>
+      <c r="E37" s="792" t="s">
         <v>521</v>
       </c>
-      <c r="F37" s="825"/>
-      <c r="G37" s="825"/>
-      <c r="H37" s="825"/>
-      <c r="I37" s="826"/>
-      <c r="K37" s="817" t="s">
+      <c r="F37" s="793"/>
+      <c r="G37" s="793"/>
+      <c r="H37" s="793"/>
+      <c r="I37" s="794"/>
+      <c r="K37" s="778" t="s">
         <v>522</v>
       </c>
       <c r="L37" s="681"/>
@@ -22264,15 +22264,15 @@
       <c r="E38" s="730" t="s">
         <v>548</v>
       </c>
-      <c r="F38" s="786" t="s">
+      <c r="F38" s="779" t="s">
         <v>523</v>
       </c>
-      <c r="G38" s="787"/>
-      <c r="H38" s="786" t="s">
+      <c r="G38" s="780"/>
+      <c r="H38" s="779" t="s">
         <v>524</v>
       </c>
-      <c r="I38" s="787"/>
-      <c r="K38" s="817"/>
+      <c r="I38" s="780"/>
+      <c r="K38" s="778"/>
       <c r="L38" s="681"/>
     </row>
     <row r="39" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -22291,10 +22291,10 @@
       <c r="C40" s="733" t="s">
         <v>526</v>
       </c>
-      <c r="D40" s="804" t="s">
+      <c r="D40" s="782" t="s">
         <v>527</v>
       </c>
-      <c r="E40" s="805"/>
+      <c r="E40" s="783"/>
       <c r="I40" s="734" t="s">
         <v>528</v>
       </c>
@@ -22307,10 +22307,10 @@
       <c r="C41" s="733" t="s">
         <v>530</v>
       </c>
-      <c r="D41" s="804" t="s">
+      <c r="D41" s="782" t="s">
         <v>366</v>
       </c>
-      <c r="E41" s="805"/>
+      <c r="E41" s="783"/>
       <c r="J41" s="735"/>
       <c r="L41" s="681"/>
     </row>
@@ -22417,14 +22417,14 @@
       </c>
       <c r="D50" s="738"/>
       <c r="E50" s="745"/>
-      <c r="G50" s="819" t="s">
+      <c r="G50" s="784" t="s">
         <v>538</v>
       </c>
-      <c r="H50" s="820"/>
-      <c r="I50" s="819" t="s">
+      <c r="H50" s="785"/>
+      <c r="I50" s="784" t="s">
         <v>539</v>
       </c>
-      <c r="J50" s="820"/>
+      <c r="J50" s="785"/>
       <c r="L50" s="681"/>
       <c r="M50" s="681"/>
     </row>
@@ -22441,8 +22441,8 @@
         <v>540</v>
       </c>
       <c r="H51" s="747"/>
-      <c r="I51" s="821"/>
-      <c r="J51" s="822"/>
+      <c r="I51" s="786"/>
+      <c r="J51" s="787"/>
       <c r="L51" s="681"/>
       <c r="M51" s="681"/>
     </row>
@@ -22459,8 +22459,8 @@
         <v>542</v>
       </c>
       <c r="H52" s="747"/>
-      <c r="I52" s="821"/>
-      <c r="J52" s="822"/>
+      <c r="I52" s="786"/>
+      <c r="J52" s="787"/>
       <c r="L52" s="681"/>
       <c r="M52" s="681"/>
     </row>
@@ -22590,12 +22590,12 @@
       <c r="B62" s="485"/>
       <c r="C62" s="485"/>
       <c r="D62" s="485"/>
-      <c r="E62" s="823"/>
-      <c r="F62" s="823"/>
-      <c r="G62" s="823"/>
-      <c r="H62" s="823"/>
-      <c r="I62" s="823"/>
-      <c r="J62" s="823"/>
+      <c r="E62" s="788"/>
+      <c r="F62" s="788"/>
+      <c r="G62" s="788"/>
+      <c r="H62" s="788"/>
+      <c r="I62" s="788"/>
+      <c r="J62" s="788"/>
       <c r="K62" s="740"/>
       <c r="L62" s="681"/>
       <c r="M62" s="681"/>
@@ -22622,19 +22622,19 @@
       <c r="G64" s="260"/>
     </row>
     <row r="65" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="818" t="s">
+      <c r="A65" s="781" t="s">
         <v>547</v>
       </c>
-      <c r="B65" s="818"/>
-      <c r="C65" s="818"/>
-      <c r="D65" s="818"/>
-      <c r="E65" s="818"/>
-      <c r="F65" s="818"/>
-      <c r="G65" s="818"/>
-      <c r="H65" s="818"/>
-      <c r="I65" s="818"/>
-      <c r="J65" s="818"/>
-      <c r="K65" s="818"/>
+      <c r="B65" s="781"/>
+      <c r="C65" s="781"/>
+      <c r="D65" s="781"/>
+      <c r="E65" s="781"/>
+      <c r="F65" s="781"/>
+      <c r="G65" s="781"/>
+      <c r="H65" s="781"/>
+      <c r="I65" s="781"/>
+      <c r="J65" s="781"/>
+      <c r="K65" s="781"/>
     </row>
     <row r="66" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="1:11" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22645,32 +22645,6 @@
     <protectedRange sqref="C10:C11 C62" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="41">
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="E37:I37"/>
-    <mergeCell ref="G34:H35"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="E34:F35"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="A7:K7"/>
@@ -22686,6 +22660,32 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G34:H35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="E34:F35"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="E37:I37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
@@ -22850,14 +22850,14 @@
       <c r="L5" s="564"/>
       <c r="M5" s="564"/>
       <c r="N5" s="564"/>
-      <c r="Q5" s="872" t="s">
+      <c r="Q5" s="844" t="s">
         <v>369</v>
       </c>
-      <c r="R5" s="873"/>
-      <c r="S5" s="873"/>
-      <c r="T5" s="873"/>
-      <c r="U5" s="873"/>
-      <c r="V5" s="874"/>
+      <c r="R5" s="845"/>
+      <c r="S5" s="845"/>
+      <c r="T5" s="845"/>
+      <c r="U5" s="845"/>
+      <c r="V5" s="846"/>
       <c r="X5" s="474" t="s">
         <v>370</v>
       </c>
@@ -22918,22 +22918,22 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="782" t="s">
+      <c r="A7" s="814" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="782"/>
-      <c r="C7" s="782"/>
-      <c r="D7" s="782"/>
-      <c r="E7" s="782"/>
-      <c r="F7" s="782"/>
-      <c r="G7" s="782"/>
-      <c r="H7" s="782"/>
-      <c r="I7" s="782"/>
-      <c r="J7" s="782"/>
-      <c r="K7" s="782"/>
-      <c r="L7" s="782"/>
-      <c r="M7" s="782"/>
-      <c r="N7" s="782"/>
+      <c r="B7" s="814"/>
+      <c r="C7" s="814"/>
+      <c r="D7" s="814"/>
+      <c r="E7" s="814"/>
+      <c r="F7" s="814"/>
+      <c r="G7" s="814"/>
+      <c r="H7" s="814"/>
+      <c r="I7" s="814"/>
+      <c r="J7" s="814"/>
+      <c r="K7" s="814"/>
+      <c r="L7" s="814"/>
+      <c r="M7" s="814"/>
+      <c r="N7" s="814"/>
       <c r="Q7" s="478" t="s">
         <v>422</v>
       </c>
@@ -22972,22 +22972,22 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="884">
+      <c r="A8" s="856">
         <v>0</v>
       </c>
-      <c r="B8" s="884"/>
-      <c r="C8" s="884"/>
-      <c r="D8" s="884"/>
-      <c r="E8" s="884"/>
-      <c r="F8" s="884"/>
-      <c r="G8" s="884"/>
-      <c r="H8" s="884"/>
-      <c r="I8" s="884"/>
-      <c r="J8" s="884"/>
-      <c r="K8" s="884"/>
-      <c r="L8" s="884"/>
-      <c r="M8" s="884"/>
-      <c r="N8" s="884"/>
+      <c r="B8" s="856"/>
+      <c r="C8" s="856"/>
+      <c r="D8" s="856"/>
+      <c r="E8" s="856"/>
+      <c r="F8" s="856"/>
+      <c r="G8" s="856"/>
+      <c r="H8" s="856"/>
+      <c r="I8" s="856"/>
+      <c r="J8" s="856"/>
+      <c r="K8" s="856"/>
+      <c r="L8" s="856"/>
+      <c r="M8" s="856"/>
+      <c r="N8" s="856"/>
       <c r="Q8" s="478" t="s">
         <v>423</v>
       </c>
@@ -23032,18 +23032,18 @@
       <c r="B9" s="287" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="886">
+      <c r="C9" s="858">
         <f>+FORMATO!O2</f>
         <v>0</v>
       </c>
-      <c r="D9" s="886"/>
-      <c r="E9" s="886"/>
-      <c r="F9" s="886"/>
-      <c r="G9" s="886"/>
-      <c r="H9" s="886"/>
-      <c r="I9" s="886"/>
-      <c r="J9" s="886"/>
-      <c r="K9" s="886"/>
+      <c r="D9" s="858"/>
+      <c r="E9" s="858"/>
+      <c r="F9" s="858"/>
+      <c r="G9" s="858"/>
+      <c r="H9" s="858"/>
+      <c r="I9" s="858"/>
+      <c r="J9" s="858"/>
+      <c r="K9" s="858"/>
       <c r="L9" s="289" t="s">
         <v>31</v>
       </c>
@@ -23088,18 +23088,18 @@
       <c r="B10" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="886">
+      <c r="C10" s="858">
         <f>+FORMATO!O3</f>
         <v>0</v>
       </c>
-      <c r="D10" s="886"/>
-      <c r="E10" s="886"/>
-      <c r="F10" s="886"/>
-      <c r="G10" s="886"/>
-      <c r="H10" s="886"/>
-      <c r="I10" s="886"/>
-      <c r="J10" s="886"/>
-      <c r="K10" s="886"/>
+      <c r="D10" s="858"/>
+      <c r="E10" s="858"/>
+      <c r="F10" s="858"/>
+      <c r="G10" s="858"/>
+      <c r="H10" s="858"/>
+      <c r="I10" s="858"/>
+      <c r="J10" s="858"/>
+      <c r="K10" s="858"/>
       <c r="L10" s="764" t="s">
         <v>447</v>
       </c>
@@ -23127,18 +23127,18 @@
       <c r="B11" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="886">
+      <c r="C11" s="858">
         <f>+FORMATO!O4</f>
         <v>0</v>
       </c>
-      <c r="D11" s="886"/>
-      <c r="E11" s="886"/>
-      <c r="F11" s="886"/>
-      <c r="G11" s="886"/>
-      <c r="H11" s="886"/>
-      <c r="I11" s="886"/>
-      <c r="J11" s="886"/>
-      <c r="K11" s="886"/>
+      <c r="D11" s="858"/>
+      <c r="E11" s="858"/>
+      <c r="F11" s="858"/>
+      <c r="G11" s="858"/>
+      <c r="H11" s="858"/>
+      <c r="I11" s="858"/>
+      <c r="J11" s="858"/>
+      <c r="K11" s="858"/>
       <c r="L11" s="291" t="s">
         <v>466</v>
       </c>
@@ -23151,14 +23151,14 @@
       </c>
       <c r="O11" s="570"/>
       <c r="P11" s="570"/>
-      <c r="Q11" s="875" t="s">
+      <c r="Q11" s="847" t="s">
         <v>40</v>
       </c>
-      <c r="R11" s="885"/>
-      <c r="S11" s="885"/>
-      <c r="T11" s="885"/>
-      <c r="U11" s="885"/>
-      <c r="V11" s="876"/>
+      <c r="R11" s="857"/>
+      <c r="S11" s="857"/>
+      <c r="T11" s="857"/>
+      <c r="U11" s="857"/>
+      <c r="V11" s="848"/>
       <c r="X11" s="571" t="s">
         <v>198</v>
       </c>
@@ -23179,18 +23179,18 @@
       <c r="B12" s="288" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="886">
+      <c r="C12" s="858">
         <f>+FORMATO!O5</f>
         <v>0</v>
       </c>
-      <c r="D12" s="886"/>
-      <c r="E12" s="886"/>
-      <c r="F12" s="886"/>
-      <c r="G12" s="886"/>
-      <c r="H12" s="886"/>
-      <c r="I12" s="886"/>
-      <c r="J12" s="886"/>
-      <c r="K12" s="886"/>
+      <c r="D12" s="858"/>
+      <c r="E12" s="858"/>
+      <c r="F12" s="858"/>
+      <c r="G12" s="858"/>
+      <c r="H12" s="858"/>
+      <c r="I12" s="858"/>
+      <c r="J12" s="858"/>
+      <c r="K12" s="858"/>
       <c r="L12" s="764" t="s">
         <v>253</v>
       </c>
@@ -23276,22 +23276,22 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="877" t="s">
+      <c r="A14" s="849" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="878"/>
-      <c r="C14" s="878"/>
-      <c r="D14" s="879"/>
-      <c r="E14" s="878"/>
-      <c r="F14" s="879"/>
-      <c r="G14" s="879"/>
-      <c r="H14" s="879"/>
-      <c r="I14" s="879"/>
-      <c r="J14" s="879"/>
-      <c r="K14" s="879"/>
-      <c r="L14" s="879"/>
-      <c r="M14" s="879"/>
-      <c r="N14" s="880"/>
+      <c r="B14" s="850"/>
+      <c r="C14" s="850"/>
+      <c r="D14" s="851"/>
+      <c r="E14" s="850"/>
+      <c r="F14" s="851"/>
+      <c r="G14" s="851"/>
+      <c r="H14" s="851"/>
+      <c r="I14" s="851"/>
+      <c r="J14" s="851"/>
+      <c r="K14" s="851"/>
+      <c r="L14" s="851"/>
+      <c r="M14" s="851"/>
+      <c r="N14" s="852"/>
       <c r="O14" s="570"/>
       <c r="P14" s="570"/>
       <c r="Q14" s="478" t="s">
@@ -23322,22 +23322,22 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="881" t="s">
+      <c r="A15" s="853" t="s">
         <v>476</v>
       </c>
-      <c r="B15" s="882"/>
-      <c r="C15" s="882"/>
-      <c r="D15" s="882"/>
-      <c r="E15" s="882"/>
-      <c r="F15" s="882"/>
-      <c r="G15" s="882"/>
-      <c r="H15" s="882"/>
-      <c r="I15" s="882"/>
-      <c r="J15" s="882"/>
-      <c r="K15" s="882"/>
-      <c r="L15" s="882"/>
-      <c r="M15" s="882"/>
-      <c r="N15" s="883"/>
+      <c r="B15" s="854"/>
+      <c r="C15" s="854"/>
+      <c r="D15" s="854"/>
+      <c r="E15" s="854"/>
+      <c r="F15" s="854"/>
+      <c r="G15" s="854"/>
+      <c r="H15" s="854"/>
+      <c r="I15" s="854"/>
+      <c r="J15" s="854"/>
+      <c r="K15" s="854"/>
+      <c r="L15" s="854"/>
+      <c r="M15" s="854"/>
+      <c r="N15" s="855"/>
       <c r="O15" s="570"/>
       <c r="P15" s="570"/>
       <c r="V15" s="386"/>
@@ -23369,14 +23369,14 @@
       <c r="N16" s="298"/>
       <c r="O16" s="570"/>
       <c r="P16" s="570"/>
-      <c r="Q16" s="875" t="s">
+      <c r="Q16" s="847" t="s">
         <v>438</v>
       </c>
-      <c r="R16" s="885"/>
-      <c r="S16" s="885"/>
-      <c r="T16" s="885"/>
-      <c r="U16" s="885"/>
-      <c r="V16" s="876"/>
+      <c r="R16" s="857"/>
+      <c r="S16" s="857"/>
+      <c r="T16" s="857"/>
+      <c r="U16" s="857"/>
+      <c r="V16" s="848"/>
       <c r="W16" s="578"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23411,12 +23411,12 @@
         <f>U17+(U17*$Z$14)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="857" t="s">
+      <c r="X17" s="865" t="s">
         <v>433</v>
       </c>
-      <c r="Y17" s="858"/>
-      <c r="Z17" s="858"/>
-      <c r="AA17" s="859"/>
+      <c r="Y17" s="866"/>
+      <c r="Z17" s="866"/>
+      <c r="AA17" s="867"/>
       <c r="AB17" s="599" t="s">
         <v>441</v>
       </c>
@@ -23645,15 +23645,15 @@
       <c r="B23" s="621"/>
       <c r="C23" s="621"/>
       <c r="D23" s="621"/>
-      <c r="E23" s="862" t="s">
+      <c r="E23" s="870" t="s">
         <v>448</v>
       </c>
-      <c r="F23" s="868"/>
-      <c r="G23" s="868"/>
-      <c r="H23" s="868"/>
-      <c r="I23" s="868"/>
-      <c r="J23" s="863"/>
-      <c r="K23" s="860" t="s">
+      <c r="F23" s="876"/>
+      <c r="G23" s="876"/>
+      <c r="H23" s="876"/>
+      <c r="I23" s="876"/>
+      <c r="J23" s="871"/>
+      <c r="K23" s="868" t="s">
         <v>385</v>
       </c>
       <c r="L23" s="621"/>
@@ -23661,10 +23661,10 @@
       <c r="N23" s="307"/>
       <c r="O23" s="570"/>
       <c r="P23" s="583"/>
-      <c r="Q23" s="875" t="s">
+      <c r="Q23" s="847" t="s">
         <v>357</v>
       </c>
-      <c r="R23" s="876"/>
+      <c r="R23" s="848"/>
       <c r="S23" s="387" t="s">
         <v>356</v>
       </c>
@@ -23697,17 +23697,17 @@
       <c r="B24" s="621"/>
       <c r="C24" s="621"/>
       <c r="D24" s="621"/>
-      <c r="E24" s="862" t="s">
+      <c r="E24" s="870" t="s">
         <v>358</v>
       </c>
-      <c r="F24" s="868"/>
-      <c r="G24" s="868"/>
-      <c r="H24" s="863"/>
-      <c r="I24" s="862" t="s">
+      <c r="F24" s="876"/>
+      <c r="G24" s="876"/>
+      <c r="H24" s="871"/>
+      <c r="I24" s="870" t="s">
         <v>457</v>
       </c>
-      <c r="J24" s="863"/>
-      <c r="K24" s="861"/>
+      <c r="J24" s="871"/>
+      <c r="K24" s="869"/>
       <c r="L24" s="621"/>
       <c r="M24" s="631"/>
       <c r="N24" s="307"/>
@@ -23756,16 +23756,16 @@
       <c r="B25" s="623"/>
       <c r="C25" s="623"/>
       <c r="D25" s="623"/>
-      <c r="E25" s="869" t="s">
+      <c r="E25" s="877" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="870"/>
-      <c r="G25" s="870"/>
-      <c r="H25" s="871"/>
-      <c r="I25" s="864" t="s">
+      <c r="F25" s="878"/>
+      <c r="G25" s="878"/>
+      <c r="H25" s="879"/>
+      <c r="I25" s="872" t="s">
         <v>449</v>
       </c>
-      <c r="J25" s="865"/>
+      <c r="J25" s="873"/>
       <c r="K25" s="617" t="e">
         <f>IF($I$66="Método A",FIXED(($W$25),0),FIXED(($W$25),1))</f>
         <v>#DIV/0!</v>
@@ -23812,16 +23812,16 @@
       <c r="B26" s="623"/>
       <c r="C26" s="623"/>
       <c r="D26" s="623"/>
-      <c r="E26" s="835" t="s">
+      <c r="E26" s="827" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="836"/>
-      <c r="G26" s="836"/>
-      <c r="H26" s="837"/>
-      <c r="I26" s="866" t="s">
+      <c r="F26" s="828"/>
+      <c r="G26" s="828"/>
+      <c r="H26" s="829"/>
+      <c r="I26" s="874" t="s">
         <v>450</v>
       </c>
-      <c r="J26" s="867"/>
+      <c r="J26" s="875"/>
       <c r="K26" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$26),0),FIXED(($W$26),1))</f>
         <v>#DIV/0!</v>
@@ -23838,7 +23838,7 @@
         <v>50</v>
       </c>
       <c r="S26" s="665">
-        <f>+FORMATO!E43</f>
+        <f>+FORMATO!D43</f>
         <v>0</v>
       </c>
       <c r="T26" s="523">
@@ -23868,16 +23868,16 @@
       <c r="B27" s="624"/>
       <c r="C27" s="624"/>
       <c r="D27" s="624"/>
-      <c r="E27" s="830" t="s">
+      <c r="E27" s="897" t="s">
         <v>353</v>
       </c>
-      <c r="F27" s="831"/>
-      <c r="G27" s="831"/>
-      <c r="H27" s="832"/>
-      <c r="I27" s="833" t="s">
+      <c r="F27" s="898"/>
+      <c r="G27" s="898"/>
+      <c r="H27" s="899"/>
+      <c r="I27" s="861" t="s">
         <v>451</v>
       </c>
-      <c r="J27" s="834"/>
+      <c r="J27" s="862"/>
       <c r="K27" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$27),0),FIXED(($W$27),1))</f>
         <v>#DIV/0!</v>
@@ -23894,7 +23894,7 @@
         <v>37.5</v>
       </c>
       <c r="S27" s="665">
-        <f>+FORMATO!E44</f>
+        <f>+FORMATO!D44</f>
         <v>0</v>
       </c>
       <c r="T27" s="523">
@@ -23924,16 +23924,16 @@
       <c r="B28" s="623"/>
       <c r="C28" s="623"/>
       <c r="D28" s="623"/>
-      <c r="E28" s="835" t="s">
+      <c r="E28" s="827" t="s">
         <v>352</v>
       </c>
-      <c r="F28" s="836"/>
-      <c r="G28" s="836"/>
-      <c r="H28" s="837"/>
-      <c r="I28" s="833" t="s">
+      <c r="F28" s="828"/>
+      <c r="G28" s="828"/>
+      <c r="H28" s="829"/>
+      <c r="I28" s="861" t="s">
         <v>452</v>
       </c>
-      <c r="J28" s="834"/>
+      <c r="J28" s="862"/>
       <c r="K28" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$28),0),FIXED(($W$28),1))</f>
         <v>#DIV/0!</v>
@@ -23950,7 +23950,7 @@
         <v>25</v>
       </c>
       <c r="S28" s="665">
-        <f>+FORMATO!E45</f>
+        <f>+FORMATO!D45</f>
         <v>0</v>
       </c>
       <c r="T28" s="523">
@@ -23980,16 +23980,16 @@
       <c r="B29" s="623"/>
       <c r="C29" s="623"/>
       <c r="D29" s="623"/>
-      <c r="E29" s="835" t="s">
+      <c r="E29" s="827" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="836"/>
-      <c r="G29" s="836"/>
-      <c r="H29" s="837"/>
-      <c r="I29" s="833" t="s">
+      <c r="F29" s="828"/>
+      <c r="G29" s="828"/>
+      <c r="H29" s="829"/>
+      <c r="I29" s="861" t="s">
         <v>453</v>
       </c>
-      <c r="J29" s="834"/>
+      <c r="J29" s="862"/>
       <c r="K29" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$29),0),FIXED(($W$29),1))</f>
         <v>#DIV/0!</v>
@@ -24006,7 +24006,7 @@
         <v>19</v>
       </c>
       <c r="S29" s="665">
-        <f>+FORMATO!E46</f>
+        <f>+FORMATO!D46</f>
         <v>0</v>
       </c>
       <c r="T29" s="523">
@@ -24036,16 +24036,16 @@
       <c r="B30" s="623"/>
       <c r="C30" s="623"/>
       <c r="D30" s="623"/>
-      <c r="E30" s="835" t="s">
+      <c r="E30" s="827" t="s">
         <v>355</v>
       </c>
-      <c r="F30" s="836"/>
-      <c r="G30" s="836"/>
-      <c r="H30" s="837"/>
-      <c r="I30" s="833" t="s">
+      <c r="F30" s="828"/>
+      <c r="G30" s="828"/>
+      <c r="H30" s="829"/>
+      <c r="I30" s="861" t="s">
         <v>454</v>
       </c>
-      <c r="J30" s="834"/>
+      <c r="J30" s="862"/>
       <c r="K30" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$30),0),FIXED(($W$30),1))</f>
         <v>#DIV/0!</v>
@@ -24062,7 +24062,7 @@
         <v>9.5</v>
       </c>
       <c r="S30" s="665">
-        <f>+FORMATO!E47</f>
+        <f>+FORMATO!D47</f>
         <v>0</v>
       </c>
       <c r="T30" s="523">
@@ -24092,16 +24092,16 @@
       <c r="B31" s="623"/>
       <c r="C31" s="623"/>
       <c r="D31" s="623"/>
-      <c r="E31" s="835" t="s">
+      <c r="E31" s="827" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="836"/>
-      <c r="G31" s="836"/>
-      <c r="H31" s="837"/>
-      <c r="I31" s="838" t="s">
+      <c r="F31" s="828"/>
+      <c r="G31" s="828"/>
+      <c r="H31" s="829"/>
+      <c r="I31" s="863" t="s">
         <v>455</v>
       </c>
-      <c r="J31" s="839"/>
+      <c r="J31" s="864"/>
       <c r="K31" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$31),0),FIXED(($W$31),1))</f>
         <v>#DIV/0!</v>
@@ -24118,7 +24118,7 @@
         <v>4.75</v>
       </c>
       <c r="S31" s="665">
-        <f>+FORMATO!E48</f>
+        <f>+FORMATO!D48</f>
         <v>0</v>
       </c>
       <c r="T31" s="523">
@@ -24152,16 +24152,16 @@
       <c r="B32" s="623"/>
       <c r="C32" s="623"/>
       <c r="D32" s="623"/>
-      <c r="E32" s="835" t="s">
+      <c r="E32" s="827" t="s">
         <v>232</v>
       </c>
-      <c r="F32" s="836"/>
-      <c r="G32" s="836"/>
-      <c r="H32" s="837"/>
-      <c r="I32" s="838" t="s">
+      <c r="F32" s="828"/>
+      <c r="G32" s="828"/>
+      <c r="H32" s="829"/>
+      <c r="I32" s="863" t="s">
         <v>456</v>
       </c>
-      <c r="J32" s="839"/>
+      <c r="J32" s="864"/>
       <c r="K32" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$32),0),FIXED(($W$32),1))</f>
         <v>#DIV/0!</v>
@@ -24178,7 +24178,7 @@
         <v>2</v>
       </c>
       <c r="S32" s="665">
-        <f>+FORMATO!E50</f>
+        <f>+FORMATO!D50</f>
         <v>0</v>
       </c>
       <c r="T32" s="523">
@@ -24212,16 +24212,16 @@
       <c r="B33" s="623"/>
       <c r="C33" s="623"/>
       <c r="D33" s="623"/>
-      <c r="E33" s="835" t="s">
+      <c r="E33" s="827" t="s">
         <v>238</v>
       </c>
-      <c r="F33" s="836"/>
-      <c r="G33" s="836"/>
-      <c r="H33" s="837"/>
-      <c r="I33" s="840" t="s">
+      <c r="F33" s="828"/>
+      <c r="G33" s="828"/>
+      <c r="H33" s="829"/>
+      <c r="I33" s="859" t="s">
         <v>458</v>
       </c>
-      <c r="J33" s="841"/>
+      <c r="J33" s="860"/>
       <c r="K33" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$33),0),FIXED(($W$33),1))</f>
         <v>#DIV/0!</v>
@@ -24238,7 +24238,7 @@
         <v>0.85</v>
       </c>
       <c r="S33" s="665">
-        <f>+FORMATO!E51</f>
+        <f>+FORMATO!D51</f>
         <v>0</v>
       </c>
       <c r="T33" s="523">
@@ -24264,16 +24264,16 @@
       <c r="B34" s="623"/>
       <c r="C34" s="623"/>
       <c r="D34" s="623"/>
-      <c r="E34" s="835" t="s">
+      <c r="E34" s="827" t="s">
         <v>418</v>
       </c>
-      <c r="F34" s="836"/>
-      <c r="G34" s="836"/>
-      <c r="H34" s="837"/>
-      <c r="I34" s="840" t="s">
+      <c r="F34" s="828"/>
+      <c r="G34" s="828"/>
+      <c r="H34" s="829"/>
+      <c r="I34" s="859" t="s">
         <v>459</v>
       </c>
-      <c r="J34" s="841"/>
+      <c r="J34" s="860"/>
       <c r="K34" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$34),0),FIXED(($W$34),1))</f>
         <v>#DIV/0!</v>
@@ -24290,7 +24290,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="S34" s="665">
-        <f>+FORMATO!E52</f>
+        <f>+FORMATO!D52</f>
         <v>0</v>
       </c>
       <c r="T34" s="523">
@@ -24320,16 +24320,16 @@
       <c r="B35" s="623"/>
       <c r="C35" s="623"/>
       <c r="D35" s="623"/>
-      <c r="E35" s="835" t="s">
+      <c r="E35" s="827" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="836"/>
-      <c r="G35" s="836"/>
-      <c r="H35" s="837"/>
-      <c r="I35" s="840" t="s">
+      <c r="F35" s="828"/>
+      <c r="G35" s="828"/>
+      <c r="H35" s="829"/>
+      <c r="I35" s="859" t="s">
         <v>460</v>
       </c>
-      <c r="J35" s="841"/>
+      <c r="J35" s="860"/>
       <c r="K35" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$35),0),FIXED(($W$35),1))</f>
         <v>#DIV/0!</v>
@@ -24346,7 +24346,7 @@
         <v>0.25</v>
       </c>
       <c r="S35" s="665">
-        <f>+FORMATO!E53</f>
+        <f>+FORMATO!D53</f>
         <v>0</v>
       </c>
       <c r="T35" s="523">
@@ -24376,16 +24376,16 @@
       <c r="B36" s="623"/>
       <c r="C36" s="623"/>
       <c r="D36" s="623"/>
-      <c r="E36" s="835" t="s">
+      <c r="E36" s="827" t="s">
         <v>241</v>
       </c>
-      <c r="F36" s="836"/>
-      <c r="G36" s="836"/>
-      <c r="H36" s="837"/>
-      <c r="I36" s="840" t="s">
+      <c r="F36" s="828"/>
+      <c r="G36" s="828"/>
+      <c r="H36" s="829"/>
+      <c r="I36" s="859" t="s">
         <v>461</v>
       </c>
-      <c r="J36" s="841"/>
+      <c r="J36" s="860"/>
       <c r="K36" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$36),0),FIXED(($W$36),1))</f>
         <v>#DIV/0!</v>
@@ -24402,7 +24402,7 @@
         <v>0.15</v>
       </c>
       <c r="S36" s="665">
-        <f>+FORMATO!E54</f>
+        <f>+FORMATO!D54</f>
         <v>0</v>
       </c>
       <c r="T36" s="523">
@@ -24431,16 +24431,16 @@
       <c r="B37" s="623"/>
       <c r="C37" s="623"/>
       <c r="D37" s="623"/>
-      <c r="E37" s="835" t="s">
+      <c r="E37" s="827" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="836"/>
-      <c r="G37" s="836"/>
-      <c r="H37" s="837"/>
-      <c r="I37" s="840" t="s">
+      <c r="F37" s="828"/>
+      <c r="G37" s="828"/>
+      <c r="H37" s="829"/>
+      <c r="I37" s="859" t="s">
         <v>462</v>
       </c>
-      <c r="J37" s="841"/>
+      <c r="J37" s="860"/>
       <c r="K37" s="618" t="e">
         <f>IF($I$66="Método A",FIXED(($W$37),0),FIXED(($W$37),1))</f>
         <v>#DIV/0!</v>
@@ -24457,7 +24457,7 @@
         <v>0.106</v>
       </c>
       <c r="S37" s="665">
-        <f>+FORMATO!E55</f>
+        <f>+FORMATO!D55</f>
         <v>0</v>
       </c>
       <c r="T37" s="523">
@@ -24486,16 +24486,16 @@
       <c r="B38" s="623"/>
       <c r="C38" s="623"/>
       <c r="D38" s="623"/>
-      <c r="E38" s="892" t="s">
+      <c r="E38" s="830" t="s">
         <v>242</v>
       </c>
-      <c r="F38" s="893"/>
-      <c r="G38" s="893"/>
-      <c r="H38" s="894"/>
-      <c r="I38" s="898" t="s">
+      <c r="F38" s="831"/>
+      <c r="G38" s="831"/>
+      <c r="H38" s="832"/>
+      <c r="I38" s="838" t="s">
         <v>463</v>
       </c>
-      <c r="J38" s="899"/>
+      <c r="J38" s="839"/>
       <c r="K38" s="317" t="e">
         <f>IF($I$66="Método A",FIXED(($W$38),0),FIXED(($W$38),1))</f>
         <v>#DIV/0!</v>
@@ -24512,7 +24512,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="S38" s="665">
-        <f>+FORMATO!E56</f>
+        <f>+FORMATO!D56</f>
         <v>0</v>
       </c>
       <c r="T38" s="523">
@@ -24562,7 +24562,7 @@
         <v>0.01</v>
       </c>
       <c r="S39" s="665">
-        <f>+FORMATO!E57</f>
+        <f>+FORMATO!D57</f>
         <v>0</v>
       </c>
       <c r="T39" s="523" t="b">
@@ -24628,12 +24628,12 @@
       <c r="N41" s="313"/>
       <c r="O41" s="570"/>
       <c r="P41" s="570"/>
-      <c r="Q41" s="843" t="s">
+      <c r="Q41" s="880" t="s">
         <v>420</v>
       </c>
-      <c r="R41" s="844"/>
-      <c r="S41" s="844"/>
-      <c r="T41" s="845"/>
+      <c r="R41" s="881"/>
+      <c r="S41" s="881"/>
+      <c r="T41" s="882"/>
       <c r="AA41" s="513"/>
       <c r="AB41" s="513"/>
       <c r="AC41" s="513"/>
@@ -24656,10 +24656,10 @@
       <c r="N42" s="313"/>
       <c r="O42" s="570"/>
       <c r="P42" s="570"/>
-      <c r="Q42" s="846"/>
-      <c r="R42" s="847"/>
-      <c r="S42" s="847"/>
-      <c r="T42" s="848"/>
+      <c r="Q42" s="883"/>
+      <c r="R42" s="884"/>
+      <c r="S42" s="884"/>
+      <c r="T42" s="885"/>
       <c r="U42" s="620"/>
       <c r="V42" s="620"/>
       <c r="AA42" s="513"/>
@@ -24684,10 +24684,10 @@
       <c r="N43" s="313"/>
       <c r="O43" s="570"/>
       <c r="P43" s="570"/>
-      <c r="Q43" s="849" t="s">
+      <c r="Q43" s="886" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="851" t="e">
+      <c r="R43" s="888" t="e">
         <f>$V$31</f>
         <v>#DIV/0!</v>
       </c>
@@ -24722,8 +24722,8 @@
       <c r="N44" s="313"/>
       <c r="O44" s="570"/>
       <c r="P44" s="570"/>
-      <c r="Q44" s="850"/>
-      <c r="R44" s="852"/>
+      <c r="Q44" s="887"/>
+      <c r="R44" s="889"/>
       <c r="S44" s="311" t="s">
         <v>36</v>
       </c>
@@ -24757,10 +24757,10 @@
       <c r="N45" s="313"/>
       <c r="O45" s="570"/>
       <c r="P45" s="570"/>
-      <c r="Q45" s="853" t="s">
+      <c r="Q45" s="890" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="855" t="e">
+      <c r="R45" s="892" t="e">
         <f>100-(R43+R48)</f>
         <v>#DIV/0!</v>
       </c>
@@ -24798,8 +24798,8 @@
       <c r="N46" s="313"/>
       <c r="O46" s="570"/>
       <c r="P46" s="570"/>
-      <c r="Q46" s="854"/>
-      <c r="R46" s="856"/>
+      <c r="Q46" s="891"/>
+      <c r="R46" s="893"/>
       <c r="S46" s="311" t="s">
         <v>38</v>
       </c>
@@ -24833,8 +24833,8 @@
       <c r="N47" s="313"/>
       <c r="O47" s="570"/>
       <c r="P47" s="570"/>
-      <c r="Q47" s="850"/>
-      <c r="R47" s="852"/>
+      <c r="Q47" s="887"/>
+      <c r="R47" s="889"/>
       <c r="S47" s="311" t="s">
         <v>36</v>
       </c>
@@ -25435,12 +25435,12 @@
       <c r="F66" s="306"/>
       <c r="G66" s="306"/>
       <c r="H66" s="306"/>
-      <c r="I66" s="888" t="str">
+      <c r="I66" s="834" t="str">
         <f>+R2</f>
         <v>-</v>
       </c>
-      <c r="J66" s="888"/>
-      <c r="K66" s="888"/>
+      <c r="J66" s="834"/>
+      <c r="K66" s="834"/>
       <c r="L66" s="421"/>
       <c r="M66" s="421"/>
       <c r="N66" s="545"/>
@@ -25472,11 +25472,11 @@
       <c r="F67" s="306"/>
       <c r="G67" s="306"/>
       <c r="H67" s="306"/>
-      <c r="I67" s="888" t="s">
+      <c r="I67" s="834" t="s">
         <v>442</v>
       </c>
-      <c r="J67" s="888"/>
-      <c r="K67" s="888"/>
+      <c r="J67" s="834"/>
+      <c r="K67" s="834"/>
       <c r="L67" s="421"/>
       <c r="M67" s="421"/>
       <c r="N67" s="545"/>
@@ -25508,11 +25508,11 @@
       <c r="F68" s="546"/>
       <c r="G68" s="546"/>
       <c r="H68" s="546"/>
-      <c r="I68" s="888" t="s">
+      <c r="I68" s="834" t="s">
         <v>442</v>
       </c>
-      <c r="J68" s="888"/>
-      <c r="K68" s="888"/>
+      <c r="J68" s="834"/>
+      <c r="K68" s="834"/>
       <c r="L68" s="421"/>
       <c r="M68" s="421"/>
       <c r="N68" s="545"/>
@@ -25544,11 +25544,11 @@
       <c r="F69" s="546"/>
       <c r="G69" s="546"/>
       <c r="H69" s="546"/>
-      <c r="I69" s="842" t="s">
+      <c r="I69" s="833" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="842"/>
-      <c r="K69" s="842"/>
+      <c r="J69" s="833"/>
+      <c r="K69" s="833"/>
       <c r="L69" s="421"/>
       <c r="M69" s="421"/>
       <c r="N69" s="545"/>
@@ -25580,11 +25580,11 @@
       <c r="F70" s="546"/>
       <c r="G70" s="546"/>
       <c r="H70" s="546"/>
-      <c r="I70" s="888" t="s">
+      <c r="I70" s="834" t="s">
         <v>442</v>
       </c>
-      <c r="J70" s="888"/>
-      <c r="K70" s="888"/>
+      <c r="J70" s="834"/>
+      <c r="K70" s="834"/>
       <c r="L70" s="421"/>
       <c r="M70" s="421"/>
       <c r="N70" s="545"/>
@@ -25616,11 +25616,11 @@
       <c r="F71" s="546"/>
       <c r="G71" s="546"/>
       <c r="H71" s="546"/>
-      <c r="I71" s="842" t="s">
+      <c r="I71" s="833" t="s">
         <v>252</v>
       </c>
-      <c r="J71" s="842"/>
-      <c r="K71" s="842"/>
+      <c r="J71" s="833"/>
+      <c r="K71" s="833"/>
       <c r="L71" s="421"/>
       <c r="M71" s="421"/>
       <c r="N71" s="545"/>
@@ -25652,11 +25652,11 @@
       <c r="F72" s="306"/>
       <c r="G72" s="306"/>
       <c r="H72" s="306"/>
-      <c r="I72" s="895" t="s">
+      <c r="I72" s="835" t="s">
         <v>442</v>
       </c>
-      <c r="J72" s="896"/>
-      <c r="K72" s="897"/>
+      <c r="J72" s="836"/>
+      <c r="K72" s="837"/>
       <c r="L72" s="319"/>
       <c r="M72" s="319"/>
       <c r="N72" s="547"/>
@@ -25752,14 +25752,14 @@
       <c r="E75" s="306"/>
       <c r="F75" s="306"/>
       <c r="H75" s="306"/>
-      <c r="I75" s="842"/>
-      <c r="J75" s="842"/>
-      <c r="K75" s="842"/>
-      <c r="L75" s="827">
+      <c r="I75" s="833"/>
+      <c r="J75" s="833"/>
+      <c r="K75" s="833"/>
+      <c r="L75" s="894">
         <v>0</v>
       </c>
-      <c r="M75" s="828"/>
-      <c r="N75" s="829"/>
+      <c r="M75" s="895"/>
+      <c r="N75" s="896"/>
       <c r="O75" s="570"/>
       <c r="P75" s="570"/>
       <c r="Q75" s="424"/>
@@ -25787,11 +25787,11 @@
       <c r="E76" s="306"/>
       <c r="F76" s="306"/>
       <c r="H76" s="306"/>
-      <c r="I76" s="888" t="s">
+      <c r="I76" s="834" t="s">
         <v>442</v>
       </c>
-      <c r="J76" s="888"/>
-      <c r="K76" s="888"/>
+      <c r="J76" s="834"/>
+      <c r="K76" s="834"/>
       <c r="L76" s="306"/>
       <c r="M76" s="306"/>
       <c r="N76" s="552"/>
@@ -25822,12 +25822,12 @@
       <c r="E77" s="306"/>
       <c r="F77" s="306"/>
       <c r="H77" s="306"/>
-      <c r="I77" s="889">
+      <c r="I77" s="841">
         <f>+FORMATO!H19</f>
         <v>0</v>
       </c>
-      <c r="J77" s="842"/>
-      <c r="K77" s="842"/>
+      <c r="J77" s="833"/>
+      <c r="K77" s="833"/>
       <c r="L77" s="306"/>
       <c r="M77" s="306"/>
       <c r="N77" s="552"/>
@@ -25858,12 +25858,12 @@
       <c r="E78" s="306"/>
       <c r="F78" s="306"/>
       <c r="H78" s="306"/>
-      <c r="I78" s="888">
+      <c r="I78" s="834">
         <f>+FORMATO!H20</f>
         <v>0</v>
       </c>
-      <c r="J78" s="888"/>
-      <c r="K78" s="888"/>
+      <c r="J78" s="834"/>
+      <c r="K78" s="834"/>
       <c r="L78" s="306"/>
       <c r="M78" s="306"/>
       <c r="N78" s="552"/>
@@ -25951,22 +25951,22 @@
       <c r="AD80" s="513"/>
     </row>
     <row r="81" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="891" t="s">
+      <c r="A81" s="843" t="s">
         <v>568</v>
       </c>
-      <c r="B81" s="891"/>
-      <c r="C81" s="891"/>
-      <c r="D81" s="891"/>
-      <c r="E81" s="891"/>
-      <c r="F81" s="891"/>
-      <c r="G81" s="891"/>
-      <c r="H81" s="891"/>
-      <c r="I81" s="891"/>
-      <c r="J81" s="891"/>
-      <c r="K81" s="891"/>
-      <c r="L81" s="891"/>
-      <c r="M81" s="891"/>
-      <c r="N81" s="891"/>
+      <c r="B81" s="843"/>
+      <c r="C81" s="843"/>
+      <c r="D81" s="843"/>
+      <c r="E81" s="843"/>
+      <c r="F81" s="843"/>
+      <c r="G81" s="843"/>
+      <c r="H81" s="843"/>
+      <c r="I81" s="843"/>
+      <c r="J81" s="843"/>
+      <c r="K81" s="843"/>
+      <c r="L81" s="843"/>
+      <c r="M81" s="843"/>
+      <c r="N81" s="843"/>
       <c r="O81" s="426"/>
       <c r="P81" s="426"/>
       <c r="Q81" s="424"/>
@@ -25985,22 +25985,22 @@
       <c r="AD81" s="513"/>
     </row>
     <row r="82" spans="1:30" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="890" t="s">
+      <c r="A82" s="842" t="s">
         <v>569</v>
       </c>
-      <c r="B82" s="890"/>
-      <c r="C82" s="890"/>
-      <c r="D82" s="890"/>
-      <c r="E82" s="890"/>
-      <c r="F82" s="890"/>
-      <c r="G82" s="890"/>
-      <c r="H82" s="890"/>
-      <c r="I82" s="890"/>
-      <c r="J82" s="890"/>
-      <c r="K82" s="890"/>
-      <c r="L82" s="890"/>
-      <c r="M82" s="890"/>
-      <c r="N82" s="890"/>
+      <c r="B82" s="842"/>
+      <c r="C82" s="842"/>
+      <c r="D82" s="842"/>
+      <c r="E82" s="842"/>
+      <c r="F82" s="842"/>
+      <c r="G82" s="842"/>
+      <c r="H82" s="842"/>
+      <c r="I82" s="842"/>
+      <c r="J82" s="842"/>
+      <c r="K82" s="842"/>
+      <c r="L82" s="842"/>
+      <c r="M82" s="842"/>
+      <c r="N82" s="842"/>
       <c r="Q82" s="424"/>
       <c r="R82" s="519"/>
       <c r="S82" s="519"/>
@@ -26017,22 +26017,22 @@
       <c r="AD82" s="513"/>
     </row>
     <row r="83" spans="1:30" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="890" t="s">
+      <c r="A83" s="842" t="s">
         <v>570</v>
       </c>
-      <c r="B83" s="890"/>
-      <c r="C83" s="890"/>
-      <c r="D83" s="890"/>
-      <c r="E83" s="890"/>
-      <c r="F83" s="890"/>
-      <c r="G83" s="890"/>
-      <c r="H83" s="890"/>
-      <c r="I83" s="890"/>
-      <c r="J83" s="890"/>
-      <c r="K83" s="890"/>
-      <c r="L83" s="890"/>
-      <c r="M83" s="890"/>
-      <c r="N83" s="890"/>
+      <c r="B83" s="842"/>
+      <c r="C83" s="842"/>
+      <c r="D83" s="842"/>
+      <c r="E83" s="842"/>
+      <c r="F83" s="842"/>
+      <c r="G83" s="842"/>
+      <c r="H83" s="842"/>
+      <c r="I83" s="842"/>
+      <c r="J83" s="842"/>
+      <c r="K83" s="842"/>
+      <c r="L83" s="842"/>
+      <c r="M83" s="842"/>
+      <c r="N83" s="842"/>
       <c r="O83" s="428"/>
       <c r="P83" s="428"/>
       <c r="AA83" s="513"/>
@@ -26041,44 +26041,44 @@
       <c r="AD83" s="513"/>
     </row>
     <row r="84" spans="1:30" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="890" t="s">
+      <c r="A84" s="842" t="s">
         <v>571</v>
       </c>
-      <c r="B84" s="890"/>
-      <c r="C84" s="890"/>
-      <c r="D84" s="890"/>
-      <c r="E84" s="890"/>
-      <c r="F84" s="890"/>
-      <c r="G84" s="890"/>
-      <c r="H84" s="890"/>
-      <c r="I84" s="890"/>
-      <c r="J84" s="890"/>
-      <c r="K84" s="890"/>
-      <c r="L84" s="890"/>
-      <c r="M84" s="890"/>
-      <c r="N84" s="890"/>
+      <c r="B84" s="842"/>
+      <c r="C84" s="842"/>
+      <c r="D84" s="842"/>
+      <c r="E84" s="842"/>
+      <c r="F84" s="842"/>
+      <c r="G84" s="842"/>
+      <c r="H84" s="842"/>
+      <c r="I84" s="842"/>
+      <c r="J84" s="842"/>
+      <c r="K84" s="842"/>
+      <c r="L84" s="842"/>
+      <c r="M84" s="842"/>
+      <c r="N84" s="842"/>
       <c r="AA84" s="513"/>
       <c r="AB84" s="513"/>
       <c r="AC84" s="513"/>
       <c r="AD84" s="513"/>
     </row>
     <row r="85" spans="1:30" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="887" t="s">
+      <c r="A85" s="840" t="s">
         <v>572</v>
       </c>
-      <c r="B85" s="887"/>
-      <c r="C85" s="887"/>
-      <c r="D85" s="887"/>
-      <c r="E85" s="887"/>
-      <c r="F85" s="887"/>
-      <c r="G85" s="887"/>
-      <c r="H85" s="887"/>
-      <c r="I85" s="887"/>
-      <c r="J85" s="887"/>
-      <c r="K85" s="887"/>
-      <c r="L85" s="887"/>
-      <c r="M85" s="887"/>
-      <c r="N85" s="887"/>
+      <c r="B85" s="840"/>
+      <c r="C85" s="840"/>
+      <c r="D85" s="840"/>
+      <c r="E85" s="840"/>
+      <c r="F85" s="840"/>
+      <c r="G85" s="840"/>
+      <c r="H85" s="840"/>
+      <c r="I85" s="840"/>
+      <c r="J85" s="840"/>
+      <c r="K85" s="840"/>
+      <c r="L85" s="840"/>
+      <c r="M85" s="840"/>
+      <c r="N85" s="840"/>
       <c r="AA85" s="513"/>
       <c r="AB85" s="513"/>
       <c r="AC85" s="513"/>
@@ -26254,57 +26254,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="67">
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A85:N85"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="A83:N83"/>
-    <mergeCell ref="A81:N81"/>
-    <mergeCell ref="A82:N82"/>
-    <mergeCell ref="A84:N84"/>
-    <mergeCell ref="Q5:V5"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A15:N15"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="Q16:V16"/>
-    <mergeCell ref="Q11:V11"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="Q41:T42"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="Q45:Q47"/>
-    <mergeCell ref="R45:R47"/>
     <mergeCell ref="L75:N75"/>
     <mergeCell ref="E27:H27"/>
     <mergeCell ref="I27:J27"/>
@@ -26321,6 +26270,57 @@
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I71:K71"/>
     <mergeCell ref="I37:J37"/>
+    <mergeCell ref="Q41:T42"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="Q45:Q47"/>
+    <mergeCell ref="R45:R47"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A15:N15"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="Q16:V16"/>
+    <mergeCell ref="Q11:V11"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="A85:N85"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="A83:N83"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I38:J38"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="AA24">
@@ -32990,35 +32990,35 @@
       <c r="K7" s="150"/>
     </row>
     <row r="8" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="936" t="s">
+      <c r="A8" s="958" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="936"/>
-      <c r="C8" s="936"/>
-      <c r="D8" s="936"/>
-      <c r="E8" s="936"/>
-      <c r="F8" s="936"/>
-      <c r="G8" s="936"/>
-      <c r="H8" s="936"/>
-      <c r="I8" s="936"/>
-      <c r="J8" s="936"/>
-      <c r="K8" s="936"/>
+      <c r="B8" s="958"/>
+      <c r="C8" s="958"/>
+      <c r="D8" s="958"/>
+      <c r="E8" s="958"/>
+      <c r="F8" s="958"/>
+      <c r="G8" s="958"/>
+      <c r="H8" s="958"/>
+      <c r="I8" s="958"/>
+      <c r="J8" s="958"/>
+      <c r="K8" s="958"/>
     </row>
     <row r="9" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="937">
+      <c r="A9" s="959">
         <f>+K13</f>
         <v>10</v>
       </c>
-      <c r="B9" s="937"/>
-      <c r="C9" s="937"/>
-      <c r="D9" s="937"/>
-      <c r="E9" s="937"/>
-      <c r="F9" s="937"/>
-      <c r="G9" s="937"/>
-      <c r="H9" s="937"/>
-      <c r="I9" s="937"/>
-      <c r="J9" s="937"/>
-      <c r="K9" s="937"/>
+      <c r="B9" s="959"/>
+      <c r="C9" s="959"/>
+      <c r="D9" s="959"/>
+      <c r="E9" s="959"/>
+      <c r="F9" s="959"/>
+      <c r="G9" s="959"/>
+      <c r="H9" s="959"/>
+      <c r="I9" s="959"/>
+      <c r="J9" s="959"/>
+      <c r="K9" s="959"/>
       <c r="O9" s="151"/>
     </row>
     <row r="10" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -33041,15 +33041,15 @@
       <c r="B11" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="938">
+      <c r="C11" s="960">
         <f>+A.Granul!F10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="938"/>
-      <c r="E11" s="938"/>
-      <c r="F11" s="938"/>
-      <c r="G11" s="938"/>
-      <c r="H11" s="938"/>
+      <c r="D11" s="960"/>
+      <c r="E11" s="960"/>
+      <c r="F11" s="960"/>
+      <c r="G11" s="960"/>
+      <c r="H11" s="960"/>
       <c r="I11" s="153" t="s">
         <v>31</v>
       </c>
@@ -33070,15 +33070,15 @@
       <c r="B12" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="938">
+      <c r="C12" s="960">
         <f>+A.Granul!F11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="938"/>
-      <c r="E12" s="938"/>
-      <c r="F12" s="938"/>
-      <c r="G12" s="938"/>
-      <c r="H12" s="938"/>
+      <c r="D12" s="960"/>
+      <c r="E12" s="960"/>
+      <c r="F12" s="960"/>
+      <c r="G12" s="960"/>
+      <c r="H12" s="960"/>
       <c r="I12" s="15" t="s">
         <v>19</v>
       </c>
@@ -33103,15 +33103,15 @@
       <c r="B13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="938">
+      <c r="C13" s="960">
         <f>+A.Granul!F12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="938"/>
-      <c r="E13" s="938"/>
-      <c r="F13" s="938"/>
-      <c r="G13" s="938"/>
-      <c r="H13" s="938"/>
+      <c r="D13" s="960"/>
+      <c r="E13" s="960"/>
+      <c r="F13" s="960"/>
+      <c r="G13" s="960"/>
+      <c r="H13" s="960"/>
       <c r="I13" s="15" t="s">
         <v>20</v>
       </c>
@@ -33125,8 +33125,8 @@
       <c r="M13" s="156"/>
       <c r="P13" s="159"/>
       <c r="Q13" s="159"/>
-      <c r="R13" s="935"/>
-      <c r="S13" s="935"/>
+      <c r="R13" s="957"/>
+      <c r="S13" s="957"/>
     </row>
     <row r="14" spans="1:19" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
@@ -33148,19 +33148,19 @@
       <c r="S14" s="164"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="940" t="s">
+      <c r="A15" s="943" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="941"/>
-      <c r="C15" s="941"/>
-      <c r="D15" s="941"/>
-      <c r="E15" s="941"/>
-      <c r="F15" s="941"/>
-      <c r="G15" s="941"/>
-      <c r="H15" s="941"/>
-      <c r="I15" s="941"/>
-      <c r="J15" s="941"/>
-      <c r="K15" s="942"/>
+      <c r="B15" s="944"/>
+      <c r="C15" s="944"/>
+      <c r="D15" s="944"/>
+      <c r="E15" s="944"/>
+      <c r="F15" s="944"/>
+      <c r="G15" s="944"/>
+      <c r="H15" s="944"/>
+      <c r="I15" s="944"/>
+      <c r="J15" s="944"/>
+      <c r="K15" s="945"/>
       <c r="L15" s="156"/>
       <c r="M15" s="156"/>
       <c r="P15" s="159"/>
@@ -33169,19 +33169,19 @@
       <c r="S15" s="164"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="943" t="s">
+      <c r="A16" s="946" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="944"/>
-      <c r="C16" s="944"/>
-      <c r="D16" s="944"/>
-      <c r="E16" s="944"/>
-      <c r="F16" s="944"/>
-      <c r="G16" s="944"/>
-      <c r="H16" s="944"/>
-      <c r="I16" s="944"/>
-      <c r="J16" s="944"/>
-      <c r="K16" s="945"/>
+      <c r="B16" s="947"/>
+      <c r="C16" s="947"/>
+      <c r="D16" s="947"/>
+      <c r="E16" s="947"/>
+      <c r="F16" s="947"/>
+      <c r="G16" s="947"/>
+      <c r="H16" s="947"/>
+      <c r="I16" s="947"/>
+      <c r="J16" s="947"/>
+      <c r="K16" s="948"/>
       <c r="L16" s="156"/>
       <c r="M16" s="156"/>
       <c r="P16" s="159"/>
@@ -33209,19 +33209,19 @@
       <c r="S17" s="164"/>
     </row>
     <row r="18" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="946" t="s">
+      <c r="A18" s="949" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="947"/>
-      <c r="C18" s="947"/>
-      <c r="D18" s="947"/>
-      <c r="E18" s="947"/>
-      <c r="F18" s="947"/>
-      <c r="G18" s="947"/>
-      <c r="H18" s="947"/>
-      <c r="I18" s="947"/>
-      <c r="J18" s="947"/>
-      <c r="K18" s="948"/>
+      <c r="B18" s="950"/>
+      <c r="C18" s="950"/>
+      <c r="D18" s="950"/>
+      <c r="E18" s="950"/>
+      <c r="F18" s="950"/>
+      <c r="G18" s="950"/>
+      <c r="H18" s="950"/>
+      <c r="I18" s="950"/>
+      <c r="J18" s="950"/>
+      <c r="K18" s="951"/>
       <c r="M18" s="156"/>
       <c r="P18" s="159"/>
       <c r="Q18" s="159"/>
@@ -33346,8 +33346,8 @@
     </row>
     <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="176"/>
-      <c r="I23" s="949"/>
-      <c r="J23" s="949"/>
+      <c r="I23" s="952"/>
+      <c r="J23" s="952"/>
       <c r="K23" s="177"/>
       <c r="L23" s="156"/>
       <c r="M23" s="178"/>
@@ -33355,41 +33355,41 @@
     </row>
     <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
-      <c r="D24" s="950" t="s">
+      <c r="D24" s="953" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="951"/>
-      <c r="F24" s="951"/>
-      <c r="G24" s="952" t="s">
+      <c r="E24" s="954"/>
+      <c r="F24" s="954"/>
+      <c r="G24" s="955" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="953"/>
-      <c r="I24" s="954"/>
-      <c r="J24" s="954"/>
+      <c r="H24" s="956"/>
+      <c r="I24" s="940"/>
+      <c r="J24" s="940"/>
       <c r="K24" s="181"/>
       <c r="L24" s="156"/>
       <c r="M24" s="182"/>
-      <c r="O24" s="955" t="s">
+      <c r="O24" s="935" t="s">
         <v>174</v>
       </c>
-      <c r="P24" s="956"/>
+      <c r="P24" s="936"/>
       <c r="Q24" s="183" t="s">
         <v>173</v>
       </c>
-      <c r="R24" s="955" t="s">
+      <c r="R24" s="935" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="957"/>
+      <c r="S24" s="937"/>
       <c r="T24" s="183" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
-      <c r="B25" s="958" t="s">
+      <c r="B25" s="938" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="959"/>
+      <c r="C25" s="939"/>
       <c r="D25" s="184" t="str">
         <f>IF($Q$24="NO","",O25)</f>
         <v/>
@@ -33410,8 +33410,8 @@
         <f>IF($T$24="NO","",S25)</f>
         <v/>
       </c>
-      <c r="I25" s="954"/>
-      <c r="J25" s="954"/>
+      <c r="I25" s="940"/>
+      <c r="J25" s="940"/>
       <c r="K25" s="181"/>
       <c r="L25" s="156"/>
       <c r="M25" s="182"/>
@@ -33460,8 +33460,8 @@
         <f>IF($T$24="NO","",S26)</f>
         <v/>
       </c>
-      <c r="I26" s="960"/>
-      <c r="J26" s="960"/>
+      <c r="I26" s="941"/>
+      <c r="J26" s="941"/>
       <c r="K26" s="194"/>
       <c r="L26" s="195"/>
       <c r="M26" s="182"/>
@@ -34239,19 +34239,19 @@
       <c r="Q49"/>
     </row>
     <row r="50" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="939" t="s">
+      <c r="A50" s="942" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="939"/>
-      <c r="C50" s="939"/>
-      <c r="D50" s="939"/>
-      <c r="E50" s="939"/>
-      <c r="F50" s="939"/>
-      <c r="G50" s="939"/>
-      <c r="H50" s="939"/>
-      <c r="I50" s="939"/>
-      <c r="J50" s="939"/>
-      <c r="K50" s="939"/>
+      <c r="B50" s="942"/>
+      <c r="C50" s="942"/>
+      <c r="D50" s="942"/>
+      <c r="E50" s="942"/>
+      <c r="F50" s="942"/>
+      <c r="G50" s="942"/>
+      <c r="H50" s="942"/>
+      <c r="I50" s="942"/>
+      <c r="J50" s="942"/>
+      <c r="K50" s="942"/>
     </row>
     <row r="51" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:17" ht="15.9" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -34261,11 +34261,12 @@
     <protectedRange sqref="C11" name="Rango3_3_1_1_1_1_1_2_1"/>
   </protectedRanges>
   <mergeCells count="19">
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="A50:K50"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A16:K16"/>
@@ -34274,12 +34275,11 @@
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q24 T24" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -34316,15 +34316,15 @@
       <c r="A1" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="961" t="s">
+      <c r="B1" s="980" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="961"/>
-      <c r="D1" s="961"/>
-      <c r="E1" s="961"/>
-      <c r="F1" s="961"/>
-      <c r="G1" s="961"/>
-      <c r="H1" s="961"/>
+      <c r="C1" s="980"/>
+      <c r="D1" s="980"/>
+      <c r="E1" s="980"/>
+      <c r="F1" s="980"/>
+      <c r="G1" s="980"/>
+      <c r="H1" s="980"/>
       <c r="I1" s="94"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -34462,29 +34462,29 @@
     </row>
     <row r="8" spans="1:17" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="94"/>
-      <c r="B8" s="962" t="s">
+      <c r="B8" s="981" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="962"/>
-      <c r="D8" s="962"/>
+      <c r="C8" s="981"/>
+      <c r="D8" s="981"/>
       <c r="E8" s="103" t="s">
         <v>111</v>
       </c>
       <c r="F8" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="963" t="s">
+      <c r="G8" s="982" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="963"/>
+      <c r="H8" s="982"/>
       <c r="I8" s="94"/>
       <c r="L8" s="247" t="s">
         <v>114</v>
       </c>
-      <c r="M8" s="964" t="s">
+      <c r="M8" s="983" t="s">
         <v>115</v>
       </c>
-      <c r="N8" s="964"/>
+      <c r="N8" s="983"/>
       <c r="O8" s="248" t="s">
         <v>116</v>
       </c>
@@ -34497,13 +34497,13 @@
     </row>
     <row r="9" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="94"/>
-      <c r="B9" s="965" t="s">
+      <c r="B9" s="984" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="967" t="s">
+      <c r="C9" s="986" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="969" t="s">
+      <c r="D9" s="988" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="106" t="s">
@@ -34512,10 +34512,10 @@
       <c r="F9" s="107" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="970" t="s">
+      <c r="G9" s="989" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="971"/>
+      <c r="H9" s="990"/>
       <c r="I9" s="94"/>
       <c r="L9" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,CU&gt;=4,CC&gt;=1,CC&lt;=3),"GW","")</f>
@@ -34544,19 +34544,19 @@
     </row>
     <row r="10" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="94"/>
-      <c r="B10" s="965"/>
-      <c r="C10" s="967"/>
-      <c r="D10" s="969"/>
+      <c r="B10" s="984"/>
+      <c r="C10" s="986"/>
+      <c r="D10" s="988"/>
       <c r="E10" s="108" t="s">
         <v>125</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="972" t="s">
+      <c r="G10" s="991" t="s">
         <v>127</v>
       </c>
-      <c r="H10" s="973"/>
+      <c r="H10" s="992"/>
       <c r="I10" s="94"/>
       <c r="L10" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&lt;5,OR(CU&lt;4,CC&lt;1,CC&gt;3)),"GP","")</f>
@@ -34581,9 +34581,9 @@
     </row>
     <row r="11" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94"/>
-      <c r="B11" s="965"/>
-      <c r="C11" s="967"/>
-      <c r="D11" s="969" t="s">
+      <c r="B11" s="984"/>
+      <c r="C11" s="986"/>
+      <c r="D11" s="988" t="s">
         <v>128</v>
       </c>
       <c r="E11" s="108" t="s">
@@ -34595,7 +34595,7 @@
       <c r="G11" s="111" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="974" t="s">
+      <c r="H11" s="993" t="s">
         <v>132</v>
       </c>
       <c r="I11" s="94"/>
@@ -34616,9 +34616,9 @@
     </row>
     <row r="12" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="94"/>
-      <c r="B12" s="965"/>
-      <c r="C12" s="968"/>
-      <c r="D12" s="969"/>
+      <c r="B12" s="984"/>
+      <c r="C12" s="987"/>
+      <c r="D12" s="988"/>
       <c r="E12" s="112" t="s">
         <v>133</v>
       </c>
@@ -34628,7 +34628,7 @@
       <c r="G12" s="111" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="975"/>
+      <c r="H12" s="994"/>
       <c r="I12" s="94"/>
       <c r="L12" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&gt;=0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"GC","")</f>
@@ -34644,11 +34644,11 @@
     </row>
     <row r="13" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="94"/>
-      <c r="B13" s="965"/>
-      <c r="C13" s="967" t="s">
+      <c r="B13" s="984"/>
+      <c r="C13" s="986" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="969" t="s">
+      <c r="D13" s="988" t="s">
         <v>137</v>
       </c>
       <c r="E13" s="113" t="s">
@@ -34657,10 +34657,10 @@
       <c r="F13" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="976" t="s">
+      <c r="G13" s="995" t="s">
         <v>140</v>
       </c>
-      <c r="H13" s="977"/>
+      <c r="H13" s="996"/>
       <c r="I13" s="94"/>
       <c r="L13" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,CU&gt;=6,CC&gt;=1,CC&lt;=3),"SW","")</f>
@@ -34685,19 +34685,19 @@
     </row>
     <row r="14" spans="1:17" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="94"/>
-      <c r="B14" s="965"/>
-      <c r="C14" s="967"/>
-      <c r="D14" s="969"/>
+      <c r="B14" s="984"/>
+      <c r="C14" s="986"/>
+      <c r="D14" s="988"/>
       <c r="E14" s="113" t="s">
         <v>141</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>142</v>
       </c>
-      <c r="G14" s="976" t="s">
+      <c r="G14" s="995" t="s">
         <v>143</v>
       </c>
-      <c r="H14" s="977"/>
+      <c r="H14" s="996"/>
       <c r="I14" s="94"/>
       <c r="L14" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&lt;5,OR(CU&lt;6,CC&lt;1,CC&gt;3)),"SP","")</f>
@@ -34722,9 +34722,9 @@
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="94"/>
-      <c r="B15" s="965"/>
-      <c r="C15" s="967"/>
-      <c r="D15" s="969" t="s">
+      <c r="B15" s="984"/>
+      <c r="C15" s="986"/>
+      <c r="D15" s="988" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="113" t="s">
@@ -34736,7 +34736,7 @@
       <c r="G15" s="116" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="980" t="s">
+      <c r="H15" s="963" t="s">
         <v>148</v>
       </c>
       <c r="I15" s="94"/>
@@ -34757,9 +34757,9 @@
     </row>
     <row r="16" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="94"/>
-      <c r="B16" s="966"/>
-      <c r="C16" s="967"/>
-      <c r="D16" s="969"/>
+      <c r="B16" s="985"/>
+      <c r="C16" s="986"/>
+      <c r="D16" s="988"/>
       <c r="E16" s="117" t="s">
         <v>149</v>
       </c>
@@ -34769,7 +34769,7 @@
       <c r="G16" s="114" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="981"/>
+      <c r="H16" s="964"/>
       <c r="I16" s="94"/>
       <c r="L16" s="249" t="e">
         <f>IF(AND(N_200&lt;50,(100-N_40)&lt;0.5*(100-N_200),N_200&gt;=12,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"SC","")</f>
@@ -34785,23 +34785,23 @@
     </row>
     <row r="17" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="94"/>
-      <c r="B17" s="982" t="s">
+      <c r="B17" s="965" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="985" t="s">
+      <c r="C17" s="968" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="986"/>
+      <c r="D17" s="969"/>
       <c r="E17" s="118" t="s">
         <v>154</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>155</v>
       </c>
-      <c r="G17" s="991" t="s">
+      <c r="G17" s="974" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="992"/>
+      <c r="H17" s="975"/>
       <c r="I17" s="94"/>
       <c r="L17" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,OR(IP&lt;4,AND(IP&lt;0.73*(Ll-20)))),"ML","")</f>
@@ -34817,17 +34817,17 @@
     </row>
     <row r="18" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="94"/>
-      <c r="B18" s="983"/>
-      <c r="C18" s="987"/>
-      <c r="D18" s="988"/>
+      <c r="B18" s="966"/>
+      <c r="C18" s="970"/>
+      <c r="D18" s="971"/>
       <c r="E18" s="118" t="s">
         <v>157</v>
       </c>
       <c r="F18" s="119" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="993"/>
-      <c r="H18" s="994"/>
+      <c r="G18" s="976"/>
+      <c r="H18" s="977"/>
       <c r="I18" s="94"/>
       <c r="L18" s="249" t="e">
         <f>IF(AND(OR(L2="Inorganico"),N_200&gt;=50,Ll&lt;50,IP&gt;=7,IP&gt;=0.73*(Ll-20)),"CL","")</f>
@@ -34843,9 +34843,9 @@
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94"/>
-      <c r="B19" s="983"/>
-      <c r="C19" s="989"/>
-      <c r="D19" s="990"/>
+      <c r="B19" s="966"/>
+      <c r="C19" s="972"/>
+      <c r="D19" s="973"/>
       <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
@@ -34869,11 +34869,11 @@
     </row>
     <row r="20" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="94"/>
-      <c r="B20" s="983"/>
-      <c r="C20" s="987" t="s">
+      <c r="B20" s="966"/>
+      <c r="C20" s="970" t="s">
         <v>161</v>
       </c>
-      <c r="D20" s="995"/>
+      <c r="D20" s="978"/>
       <c r="E20" s="122" t="s">
         <v>162</v>
       </c>
@@ -34897,9 +34897,9 @@
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="94"/>
-      <c r="B21" s="983"/>
-      <c r="C21" s="987"/>
-      <c r="D21" s="995"/>
+      <c r="B21" s="966"/>
+      <c r="C21" s="970"/>
+      <c r="D21" s="978"/>
       <c r="E21" s="122" t="s">
         <v>164</v>
       </c>
@@ -34923,9 +34923,9 @@
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="94"/>
-      <c r="B22" s="983"/>
-      <c r="C22" s="989"/>
-      <c r="D22" s="996"/>
+      <c r="B22" s="966"/>
+      <c r="C22" s="972"/>
+      <c r="D22" s="979"/>
       <c r="E22" s="124" t="s">
         <v>166</v>
       </c>
@@ -34949,11 +34949,11 @@
     </row>
     <row r="23" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
-      <c r="B23" s="983"/>
-      <c r="C23" s="985" t="s">
+      <c r="B23" s="966"/>
+      <c r="C23" s="968" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="986"/>
+      <c r="D23" s="969"/>
       <c r="E23" s="125" t="s">
         <v>169</v>
       </c>
@@ -34977,7 +34977,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="94"/>
-      <c r="B24" s="984"/>
+      <c r="B24" s="967"/>
       <c r="C24" s="127"/>
       <c r="D24" s="128"/>
       <c r="E24" s="129"/>
@@ -35073,10 +35073,10 @@
       <c r="F31" s="135"/>
     </row>
     <row r="32" spans="1:16" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="978" t="s">
+      <c r="A32" s="961" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="979"/>
+      <c r="B32" s="962"/>
       <c r="F32" s="135"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -35627,13 +35627,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="G17:H18"/>
-    <mergeCell ref="C20:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="G8:H8"/>
@@ -35650,6 +35643,13 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="D15:D16"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="G17:H18"/>
+    <mergeCell ref="C20:D22"/>
+    <mergeCell ref="C23:D23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
+++ b/app/templates/informes/GranSuelo/1-INF.-N-000-26-SU24-GRA.-S.-V09.xlsx
@@ -21694,7 +21694,11 @@
       <c r="G11" s="780"/>
       <c r="H11" s="779"/>
       <c r="I11" s="780"/>
-      <c r="J11" s="682"/>
+      <c r="J11" s="682" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K11" s="386"/>
       <c r="L11" s="681"/>
       <c r="M11" s="681"/>
@@ -22776,8 +22780,10 @@
       <c r="Q2" s="323" t="s">
         <v>362</v>
       </c>
-      <c r="R2" s="529" t="s">
-        <v>442</v>
+      <c r="R2" s="529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S2" s="385"/>
       <c r="T2" s="279"/>
@@ -22801,15 +22807,19 @@
       <c r="Q3" s="323" t="s">
         <v>363</v>
       </c>
-      <c r="R3" s="529" t="s">
-        <v>442</v>
+      <c r="R3" s="529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S3" s="385"/>
       <c r="U3" s="560" t="s">
         <v>467</v>
       </c>
-      <c r="V3" s="540" t="s">
-        <v>442</v>
+      <c r="V3" s="540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="W3" s="284">
         <f>+FORMATO!J11</f>
